--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -814,22 +814,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,33012000</t>
+          <t>2,33114400</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>8,48</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>401,490</t>
+          <t>401,806</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,66003800</t>
+          <t>5,66253100</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>8,32</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.628,017</t>
+          <t>6.629,182</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,85783800</t>
+          <t>2,85909700</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>748,915</t>
+          <t>825,664</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1593,42 +1593,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>20,55457000</t>
+          <t>20,55803800</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,138</t>
+          <t>0,016</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>11,29</t>
+          <t>11,19</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>115,299</t>
+          <t>115,704</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,10172900</t>
+          <t>3,10342100</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>9,75</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1.712,722</t>
+          <t>1.715,260</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2113,22 +2113,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.900,48782900</t>
+          <t>1.901,56818200</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>9,67</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>97,818</t>
+          <t>97,983</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,46820900</t>
+          <t>3,46995400</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>9,43</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>13,99</t>
+          <t>13,98</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>65,010</t>
+          <t>65,140</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,00857900</t>
+          <t>10,01330800</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>8,80</t>
+          <t>8,85</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2902,17 +2902,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>589,696</t>
+          <t>590,118</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3253,42 +3253,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,90442900</t>
+          <t>13,92511000</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0,217</t>
+          <t>0,148</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>8,12</t>
+          <t>8,28</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>11,52</t>
+          <t>11,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,931</t>
+          <t>27,964</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3517,42 +3517,42 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>3,60395900</t>
+          <t>3,60581000</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>9,48</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>14,08</t>
+          <t>14,07</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>121,392</t>
+          <t>121,196</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -3780,22 +3780,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,44302300</t>
+          <t>3,44480400</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>9,32</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -3805,17 +3805,17 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,273</t>
+          <t>12,316</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>20,82807100</t>
+          <t>20,83745800</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>8,59</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>59,451</t>
+          <t>59,469</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4300,22 +4300,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>47,59595500</t>
+          <t>47,61838000</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,418</t>
+          <t>41,436</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4561,42 +4561,42 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,24946700</t>
+          <t>3,25435700</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,219</t>
+          <t>0,150</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>9,40</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>12,72</t>
+          <t>12,79</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>77,195</t>
+          <t>77,268</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4825,42 +4825,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15,42260000</t>
+          <t>15,42991700</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>13,17</t>
+          <t>13,16</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,020</t>
+          <t>28,033</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5085,42 +5085,42 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,09055700</t>
+          <t>3,09197900</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>8,60</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>12,77</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1,658</t>
+          <t>1,659</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -5341,22 +5341,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,14540000</t>
+          <t>3,14708900</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1.796,822</t>
+          <t>1.793,575</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5595,42 +5595,42 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,43410200</t>
+          <t>3,43478400</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,133</t>
+          <t>0,019</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>7,75</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>11,89</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>125,356</t>
+          <t>125,388</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33,84668400</t>
+          <t>33,86320000</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>9,14</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5884,17 +5884,17 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2.236,780</t>
+          <t>2.233,300</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -6119,22 +6119,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3,41220100</t>
+          <t>3,41386800</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>9,10</t>
+          <t>9,16</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -6144,17 +6144,17 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12,993</t>
+          <t>12,999</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -6384,42 +6384,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,44458700</t>
+          <t>3,45343600</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0,434</t>
+          <t>0,256</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>12,04</t>
+          <t>12,20</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64,693</t>
+          <t>64,664</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -6644,22 +6644,22 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>19,66780800</t>
+          <t>19,67780500</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -6669,17 +6669,17 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>967,357</t>
+          <t>967,558</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,28421400</t>
+          <t>1,28490800</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6914,32 +6914,32 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>9,70</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,31</t>
+          <t>14,32</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,037</t>
+          <t>75,184</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,15054425</t>
+          <t>1,15410962</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -7166,32 +7166,32 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>199,177</t>
+          <t>199,848</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,21357500</t>
+          <t>1,21424800</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -7422,32 +7422,32 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>13,88</t>
+          <t>13,87</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,069</t>
+          <t>63,997</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,10604168</t>
+          <t>1,10523055</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -7672,14 +7672,14 @@
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>0,07</t>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>0,00</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>6,96</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -7689,17 +7689,17 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>307,014</t>
+          <t>306,707</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -7916,22 +7916,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,31472200</t>
+          <t>1,31544600</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>9,91</t>
+          <t>9,97</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>478,802</t>
+          <t>480,446</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8176,22 +8176,22 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.897,18177100</t>
+          <t>1.898,22777000</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -8201,17 +8201,17 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>182,154</t>
+          <t>182,348</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -8436,42 +8436,42 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,24382000</t>
+          <t>1,24407100</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,093</t>
+          <t>0,020</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>10,67</t>
+          <t>10,69</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,335</t>
+          <t>41,343</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8696,42 +8696,42 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>5,11881200</t>
+          <t>5,12158400</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.467,798</t>
+          <t>3.474,973</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9204,42 +9204,42 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>5,71118000</t>
+          <t>5,71415900</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>9,81</t>
+          <t>9,87</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,64</t>
+          <t>14,63</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>569,872</t>
+          <t>570,190</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -9465,42 +9465,42 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10,96176600</t>
+          <t>10,96752800</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>9,72</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>14,43</t>
+          <t>14,42</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2.431,437</t>
+          <t>2.436,008</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1,07469200</t>
+          <t>1,07527100</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -9750,17 +9750,17 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>22,443</t>
+          <t>22,456</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -9973,42 +9973,42 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5,31997700</t>
+          <t>5,32286600</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>856,479</t>
+          <t>856,236</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>30,16034800</t>
+          <t>30,17439100</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,80</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -10258,17 +10258,17 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>21,569</t>
+          <t>21,574</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3,33438200</t>
+          <t>3,33608500</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -10491,32 +10491,32 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,50</t>
+          <t>14,49</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>662,394</t>
+          <t>662,928</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -10741,42 +10741,42 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.827,77701500</t>
+          <t>1.828,76920100</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>8,51</t>
+          <t>8,56</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>12,89</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>118,216</t>
+          <t>118,183</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -10997,42 +10997,42 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>31,65671100</t>
+          <t>31,67312000</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>9,52</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3.144,284</t>
+          <t>3.143,910</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -11253,42 +11253,42 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>6,39629400</t>
+          <t>6,39955300</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>9,35</t>
+          <t>9,41</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>13,97</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>122,253</t>
+          <t>122,076</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -11514,22 +11514,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3,69558300</t>
+          <t>3,69761300</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -11539,17 +11539,17 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16.767,711</t>
+          <t>16.786,666</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>5,49480200</t>
+          <t>5,49780300</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -11788,12 +11788,12 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -11803,17 +11803,17 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>1.516,028</t>
+          <t>1.516,854</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>31,26839000</t>
+          <t>31,28249200</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -12049,12 +12049,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -12064,17 +12064,17 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>167,952</t>
+          <t>168,060</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -12555,22 +12555,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3,72742400</t>
+          <t>3,72934700</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -12580,17 +12580,17 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2.312,147</t>
+          <t>2.313,925</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2,89444900</t>
+          <t>2,89574700</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>8,60</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -12844,17 +12844,17 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>6.085,878</t>
+          <t>6.066,563</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1,33510600</t>
+          <t>1,33577800</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -13089,32 +13089,32 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>14,41</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>73,321</t>
+          <t>73,739</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -13339,42 +13339,42 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>3,29956600</t>
+          <t>3,30134000</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>9,90</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>14,70</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>14.691,149</t>
+          <t>14.713,913</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -13599,22 +13599,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10,01645300</t>
+          <t>10,02165800</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>9,50</t>
+          <t>9,56</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -13624,17 +13624,17 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>823,941</t>
+          <t>823,745</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -13864,22 +13864,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4,60841700</t>
+          <t>4,61071000</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,59</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -13889,17 +13889,17 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>17.128,368</t>
+          <t>17.132,799</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -14124,42 +14124,42 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>5,28075500</t>
+          <t>5,28353700</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>14,56</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23.394,087</t>
+          <t>23.420,045</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -14384,22 +14384,22 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4,94165300</t>
+          <t>4,94428100</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -14409,17 +14409,17 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>9.847,302</t>
+          <t>9.899,120</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.787,67052100</t>
+          <t>1.788,55569900</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -14658,12 +14658,12 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -14673,17 +14673,17 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>294,374</t>
+          <t>293,966</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1,46544900</t>
+          <t>1,46614700</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -14778,32 +14778,32 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>9,50</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>14,08</t>
+          <t>14,07</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>65,556</t>
+          <t>65,587</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -15020,27 +15020,27 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>13,19420300</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>0,355</t>
+          <t>13,17794600</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>-0,123</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>11,15</t>
+          <t>11,01</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>18,39</t>
+          <t>17,98</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -15050,12 +15050,12 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -15284,42 +15284,42 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.690,01152100</t>
+          <t>1.689,90671600</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>-0,056</t>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>7,84</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>12,27</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>111,962</t>
+          <t>111,870</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -15540,42 +15540,42 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.534,07620100</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>0,275</t>
+          <t>2.520,78997800</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>-0,524</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>23,37</t>
+          <t>22,72</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>29,22</t>
+          <t>28,04</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14,421</t>
+          <t>14,345</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,28316500</t>
+          <t>1,28563000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -16058,32 +16058,32 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>9,81</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4,974</t>
+          <t>4,984</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -16304,42 +16304,42 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1,18142600</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>2,146</t>
+          <t>1,17470400</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>-0,568</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>15,37</t>
+          <t>13,65</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>3,520</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -16590,12 +16590,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1,42767000</t>
+          <t>1,43795800</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -16822,32 +16822,32 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>12,10</t>
+          <t>11,98</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>11,443</t>
+          <t>11,524</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -17098,12 +17098,12 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -17320,42 +17320,42 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1,12293400</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>-0,341</t>
+          <t>1,12795400</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>0,447</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-6,86</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>-4,61</t>
+          <t>-4,14</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>3,263</t>
+          <t>3,280</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -17576,12 +17576,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>5,53034771</t>
+          <t>5,53015105</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>-0,012</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -17591,27 +17591,27 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>7,78</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>12,44</t>
+          <t>12,31</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>32,766</t>
+          <t>32,682</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1.246,82140300</t>
+          <t>1.235,76920500</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -17846,32 +17846,32 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>-3,24</t>
+          <t>-4,09</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>37,435</t>
+          <t>37,101</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -18106,42 +18106,42 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>4,66573000</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>-1,105</t>
+          <t>4,66829800</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5,00</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>26,64</t>
+          <t>26,98</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>533,612</t>
+          <t>533,528</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2,93595000</t>
+          <t>2,94039500</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -18376,32 +18376,32 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>9,18</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>68,993</t>
+          <t>68,924</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -18622,42 +18622,42 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1.685,05554400</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>-0,392</t>
+          <t>1.688,50231500</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>0,204</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>-1,80</t>
+          <t>-1,60</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>10,79</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>30,148</t>
+          <t>30,204</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -18882,42 +18882,42 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>3,92694300</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>-0,536</t>
+          <t>3,96024100</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>0,847</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>-1,00</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>16,73</t>
+          <t>17,72</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>26,52</t>
+          <t>26,47</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2.425,678</t>
+          <t>2.446,470</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -19142,42 +19142,42 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1,96486800</t>
+          <t>1,96588300</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>12,23</t>
+          <t>12,21</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20,307</t>
+          <t>20,317</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -19402,42 +19402,42 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1.715,93114100</t>
+          <t>1.715,87876500</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>-0,052</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>8,50</t>
+          <t>8,49</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>13,25</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>14,925</t>
+          <t>14,901</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -19658,42 +19658,42 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>5,82086400</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>-0,010</t>
+          <t>5,82874700</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>0,135</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>9,24</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>14,12</t>
+          <t>14,17</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>903,617</t>
+          <t>903,211</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -19918,22 +19918,22 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0,57147221</t>
+          <t>0,56277684</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>-0,004</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-3,40</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-20,85</t>
+          <t>-22,06</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -19943,17 +19943,17 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>11,568</t>
+          <t>11,499</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -20185,42 +20185,42 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3,76907700</t>
+          <t>3,77107800</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>12,64</t>
+          <t>12,62</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>709,374</t>
+          <t>709,345</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -20441,17 +20441,17 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,41350800</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>0,095</t>
+          <t>1,41345400</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -20461,22 +20461,22 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>72,435</t>
+          <t>72,432</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -20709,12 +20709,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1,52969600</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>0,047</t>
+          <t>1,52963600</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -20729,22 +20729,22 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>11,55</t>
+          <t>11,53</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>119,753</t>
+          <t>116,750</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -20977,12 +20977,12 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,38073100</t>
+          <t>3,38053200</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>-0,143</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -20997,22 +20997,22 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>8,60</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>161,019</t>
+          <t>161,010</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -21243,17 +21243,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1,60540100</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>0,054</t>
+          <t>1,60532900</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -21263,22 +21263,22 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>21,02</t>
+          <t>20,48</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>15,124</t>
+          <t>15,123</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>6,92451000</t>
+          <t>6,94853900</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -21519,32 +21519,32 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>8,04</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>13,22</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>125,873</t>
+          <t>126,058</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,84277500</t>
+          <t>1,84487900</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -21775,32 +21775,32 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>4,31</t>
+          <t>4,43</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>9,44</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>170,119</t>
+          <t>169,985</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1,45193200</t>
+          <t>1,44031500</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -22029,34 +22029,34 @@
           <t>-0,003</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>0,04</t>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>10,68</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>280,899</t>
+          <t>278,651</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1,41785900</t>
+          <t>1,41244100</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -22292,32 +22292,32 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,40</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>9,97</t>
+          <t>9,69</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>12,611</t>
+          <t>12,563</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -22542,42 +22542,42 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3,84312700</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>-0,176</t>
+          <t>3,86681600</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>0,616</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>-1,50</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>-3,80</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>96,512</t>
+          <t>97,129</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -22832,12 +22832,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -22922,42 +22922,42 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1,32298500</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>0,318</t>
+          <t>1,32231400</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>-0,050</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>9,32</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>18,88</t>
+          <t>17,58</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>4,046</t>
+          <t>4,044</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -23178,42 +23178,42 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2,79094200</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>1,376</t>
+          <t>2,77552500</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-0,552</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>5,90</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>15,99</t>
+          <t>15,35</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>30,86</t>
+          <t>29,43</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>13,697</t>
+          <t>13,637</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -23438,42 +23438,42 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2.030,29806800</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>2,459</t>
+          <t>2.015,39755100</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>-0,733</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>7,90</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>15,64</t>
+          <t>13,75</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>9,920</t>
+          <t>9,743</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -23687,42 +23687,42 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>10,28556400</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>-0,801</t>
+          <t>10,43531400</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>1,455</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>-2,20</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>13,35</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>268,102</t>
+          <t>270,720</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -23947,42 +23947,42 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1,44430100</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>1,500</t>
+          <t>1,42469000</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>-1,357</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>4,70</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>-5,25</t>
+          <t>-6,54</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>421,083</t>
+          <t>415,227</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -24207,42 +24207,42 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1,09817600</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>1,866</t>
+          <t>1,08451400</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-1,244</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>4,90</t>
+          <t>3,60</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>-5,65</t>
+          <t>-6,82</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>-0,60</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>54,077</t>
+          <t>53,294</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -24467,42 +24467,42 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,80493400</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>1,635</t>
+          <t>1,78885700</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>-0,890</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>2,114</t>
+          <t>2,095</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -24727,42 +24727,42 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>5,45592600</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>1,703</t>
+          <t>5,44401800</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>-0,218</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>73,25</t>
+          <t>72,87</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>68,04</t>
+          <t>69,40</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>89,177</t>
+          <t>88,929</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -24987,42 +24987,42 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>9,32336800</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>1,371</t>
+          <t>9,27148100</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>-0,556</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>15,15</t>
+          <t>14,51</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>29,49</t>
+          <t>28,07</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>93,401</t>
+          <t>92,851</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -25247,42 +25247,42 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,32181800</t>
+          <t>1,34503600</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>-0,015</t>
+          <t>-0,018</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>10,59</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>294,902</t>
+          <t>300,082</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -25507,42 +25507,42 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1,81447300</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>2,204</t>
+          <t>1,77776600</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>-2,023</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>2,10</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-4,57</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>1,11</t>
+          <t>-6,50</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>-2,60</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>107,977</t>
+          <t>105,439</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -25767,42 +25767,42 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2,99635900</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>1,806</t>
+          <t>2,96698800</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>-0,980</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>8,86</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>19,10</t>
+          <t>16,84</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>124,433</t>
+          <t>122,732</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -26027,42 +26027,42 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1,96595700</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>2,441</t>
+          <t>1,95152800</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>-0,733</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>7,83</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>14,30</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>51,081</t>
+          <t>50,581</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -26291,42 +26291,42 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>7,81939000</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>1,392</t>
+          <t>7,80081300</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>-0,237</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>8,72</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>66,71</t>
+          <t>66,31</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>67,75</t>
+          <t>67,97</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>141,297</t>
+          <t>140,677</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -26551,42 +26551,42 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1.443,02603000</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>2,782</t>
+          <t>1.423,39146800</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>-1,360</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>10,55</t>
+          <t>9,05</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>45,655</t>
+          <t>45,009</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -26811,42 +26811,42 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>37,78142500</t>
+          <t>37,76408100</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>-1,103</t>
+          <t>-0,045</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>9,36</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>45,06</t>
+          <t>43,88</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>626,833</t>
+          <t>625,262</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -27071,42 +27071,42 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>3,13238100</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>2,719</t>
+          <t>3,05708100</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>-2,403</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>29,31</t>
+          <t>26,20</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>53,79</t>
+          <t>53,86</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>516,687</t>
+          <t>504,230</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -27335,42 +27335,42 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,14302700</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>1,274</t>
+          <t>5,10740600</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>-0,692</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>14,60</t>
+          <t>13,80</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>28,73</t>
+          <t>26,89</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>24,470</t>
+          <t>24,300</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -27595,42 +27595,42 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1.655,23697400</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>2,279</t>
+          <t>1.648,12251100</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>-0,429</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>7,80</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>13,73</t>
+          <t>13,24</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>25,70</t>
+          <t>24,23</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>32,542</t>
+          <t>32,451</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -27855,42 +27855,42 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2,06495600</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>1,696</t>
+          <t>2,03651800</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>-1,377</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>4,81</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>1,50</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>1,821</t>
+          <t>1,795</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -28107,42 +28107,42 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>6,34458200</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>1,479</t>
+          <t>6,30749800</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>-0,584</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>17,94</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>33,19</t>
+          <t>31,62</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>45,902</t>
+          <t>45,633</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -28359,42 +28359,42 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2,35097700</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>1,518</t>
+          <t>2,34195300</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>-0,383</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>12,04</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>25,49</t>
+          <t>24,06</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>35,668</t>
+          <t>35,525</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -28619,42 +28619,42 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>50,61442400</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>1,704</t>
+          <t>50,50414900</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>-0,217</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>73,36</t>
+          <t>72,98</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>68,19</t>
+          <t>69,55</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>961,576</t>
+          <t>958,504</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -28879,42 +28879,42 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,54833900</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>2,719</t>
+          <t>1,51110300</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>-2,404</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>29,30</t>
+          <t>26,19</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>53,74</t>
+          <t>53,81</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>20,322</t>
+          <t>19,833</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -29139,42 +29139,42 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1,88580800</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>1,117</t>
+          <t>1,85547000</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>-1,608</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>9,70</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>56,95</t>
+          <t>52,20</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>281,907</t>
+          <t>277,043</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -29403,42 +29403,42 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>0,92051800</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>1,798</t>
+          <t>0,91158000</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>-0,970</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>3,61</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>-4,37</t>
+          <t>-5,30</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>-7,10</t>
+          <t>-8,97</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2,880</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -29659,42 +29659,42 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>7,21432000</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>1,478</t>
+          <t>7,15844800</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>-0,774</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,00</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>12,86</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>26,11</t>
+          <t>24,86</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>347,961</t>
+          <t>344,866</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1.048,54136300</t>
+          <t>1.063,37786900</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
@@ -29929,32 +29929,32 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>18,46</t>
+          <t>19,03</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>8,415</t>
+          <t>8,544</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -30179,42 +30179,42 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1.546,66260900</t>
+          <t>1.573,10395700</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>4,70</t>
+          <t>6,49</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>3,40</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>11,66</t>
+          <t>12,23</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>22,074</t>
+          <t>22,453</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -30435,42 +30435,42 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>183,33557404</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>1,366</t>
+          <t>182,32370783</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>-0,551</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>16,34</t>
+          <t>15,70</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>31,47</t>
+          <t>30,03</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>18,335</t>
+          <t>18,234</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -30695,42 +30695,42 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1,92435600</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>1,115</t>
+          <t>1,89347800</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>-1,604</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>7,84</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>56,99</t>
+          <t>52,25</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>5,556</t>
+          <t>5,467</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -30952,42 +30952,42 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1,87942800</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>1,122</t>
+          <t>1,84911500</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>-1,612</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>57,22</t>
+          <t>52,46</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>1.683,690</t>
+          <t>1.656,470</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -31205,42 +31205,42 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>56,37291800</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>1,704</t>
+          <t>56,25124000</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>-0,215</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>74,05</t>
+          <t>73,68</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>69,11</t>
+          <t>70,47</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>789,161</t>
+          <t>787,457</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -31449,42 +31449,42 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>41,92298600</t>
+          <t>41,90465100</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>-1,102</t>
+          <t>-0,043</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>9,75</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>45,85</t>
+          <t>44,67</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>734,825</t>
+          <t>734,503</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -31693,42 +31693,42 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>17,33054400</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>2,163</t>
+          <t>17,23386700</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>-0,557</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,14</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>17,13</t>
+          <t>15,39</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>114,861</t>
+          <t>114,212</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -31946,42 +31946,42 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>35,08655700</t>
+          <t>35,07065100</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>-1,098</t>
+          <t>-0,045</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>9,34</t>
+          <t>9,29</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>44,89</t>
+          <t>43,72</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>11,781</t>
+          <t>11,775</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -32195,42 +32195,42 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>49,76764600</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>1,708</t>
+          <t>49,65937400</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>-0,217</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>8,30</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>73,58</t>
+          <t>73,20</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>68,43</t>
+          <t>69,78</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>683,428</t>
+          <t>681,637</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -32444,42 +32444,42 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>36,04571100</t>
+          <t>36,02941500</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>-1,103</t>
+          <t>-0,045</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>45,12</t>
+          <t>43,95</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>444,364</t>
+          <t>444,046</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -32688,42 +32688,42 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>52,93652700</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>1,708</t>
+          <t>52,82149700</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>-0,217</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>8,30</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>73,83</t>
+          <t>73,45</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>68,76</t>
+          <t>70,12</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>776,081</t>
+          <t>774,394</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1,16071900</t>
+          <t>1,16124600</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -32946,12 +32946,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>8,48</t>
+          <t>8,53</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -32961,17 +32961,17 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>64,922</t>
+          <t>64,064</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -33197,7 +33197,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1,40094700</t>
+          <t>1,40158600</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -33207,12 +33207,12 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>8,60</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -33222,17 +33222,17 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>238,181</t>
+          <t>245,923</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -33462,22 +33462,22 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>6,09071200</t>
+          <t>6,09376100</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
@@ -33487,17 +33487,17 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>42,883</t>
+          <t>42,956</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -33713,52 +33713,52 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF SAUDE SUPLEMENTAR ANS RF LP - RESP LTDA</t>
+          <t>CAIXA FIC FIF TITULO PUBLICO MPE RF LP RESP LTDA</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>15/07/2008</t>
+          <t>05/10/2012</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>5,30650400</t>
+          <t>3,33279800</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,35</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>13,74</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>808,514</t>
+          <t>23,703</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -33783,17 +33783,17 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-saude-suplementar-anf-rf</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-tp-mpe-rf-lp/</t>
         </is>
       </c>
       <c r="Q131" s="4" t="inlineStr">
         <is>
-          <t>09.181.268/0001-41</t>
+          <t>15.154.429/0001-00</t>
         </is>
       </c>
       <c r="R131" s="4" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="S131" s="4" t="inlineStr">
@@ -33803,7 +33803,7 @@
       </c>
       <c r="T131" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="U131" s="4" t="inlineStr">
@@ -33813,12 +33813,12 @@
       </c>
       <c r="V131" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="X131" s="4" t="inlineStr">
@@ -33891,8 +33891,16 @@
           <t>90.0</t>
         </is>
       </c>
-      <c r="AL131" s="4" t="inlineStr"/>
-      <c r="AM131" s="4" t="inlineStr"/>
+      <c r="AL131" s="4" t="inlineStr">
+        <is>
+          <t>["PJ Varejo"]</t>
+        </is>
+      </c>
+      <c r="AM131" s="4" t="inlineStr">
+        <is>
+          <t>["PJ Varejo"]</t>
+        </is>
+      </c>
       <c r="AN131" s="4" t="inlineStr">
         <is>
           <t>Não</t>
@@ -33911,10 +33919,264 @@
       </c>
       <c r="AR131" s="4" t="inlineStr">
         <is>
+          <t>CAIXA TÍTULO PÚBLICO MPE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS131" s="4" t="inlineStr">
+        <is>
+          <t>Fundo reaberto para novas aplicações a partir de 15/01/2024 (inclusive).
+Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).
+Nome alterado de CAIXA FIC EXPANDIR RF LP para CAIXA FIC TITULO PUBLICO MPE RF LP, em 15 JAN 2024, conforme aprovado em Assembleia Geral de Cotistas.</t>
+        </is>
+      </c>
+      <c r="AT131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5833.pdf</t>
+        </is>
+      </c>
+      <c r="AU131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5833.pdf</t>
+        </is>
+      </c>
+      <c r="AV131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5833.pdf</t>
+        </is>
+      </c>
+      <c r="AW131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5833.pdf</t>
+        </is>
+      </c>
+      <c r="AX131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5833.pdf</t>
+        </is>
+      </c>
+      <c r="AY131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5833.pdf</t>
+        </is>
+      </c>
+      <c r="AZ131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5833.pdf</t>
+        </is>
+      </c>
+      <c r="BA131" s="4" t="inlineStr"/>
+      <c r="BB131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>RENDA FIXA</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA FIF SAUDE SUPLEMENTAR ANS RF LP - RESP LTDA</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>15/07/2008</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>5,30912400</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>0,049</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>9,59</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>14,24</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>808,913</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>PJ | TODOS</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-saude-suplementar-anf-rf</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>09.181.268/0001-41</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Z132" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="AB132" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="AC132" s="2" t="inlineStr">
+        <is>
+          <t>RF 100% TPF - Longo Prazo</t>
+        </is>
+      </c>
+      <c r="AD132" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="AE132" s="2" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AF132" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AG132" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AH132" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AI132" s="2" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 90%</t>
+        </is>
+      </c>
+      <c r="AJ132" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AK132" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AL132" s="2" t="inlineStr"/>
+      <c r="AM132" s="2" t="inlineStr"/>
+      <c r="AN132" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AO132" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AP132" s="2" t="inlineStr"/>
+      <c r="AQ132" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AR132" s="2" t="inlineStr">
+        <is>
           <t>CAIXA SAÚDE SUPLEMENTAR - ANS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
-      <c r="AS131" s="4" t="inlineStr">
+      <c r="AS132" s="2" t="inlineStr">
         <is>
           <t>¹Condições excepcionais de estorno e movimentação retroativa estão descritas no TE099.
 1.	Para providenciar o resgate, a unidade de relacionamento deverá acessar o endereço:  
@@ -33924,301 +34186,39 @@
 4.	Efetuar o comando de resgate no SIART em D+1 do dia do desbloqueio das cotas, conforme TE099.</t>
         </is>
       </c>
-      <c r="AT131" s="4" t="inlineStr">
+      <c r="AT132" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5080.pdf</t>
         </is>
       </c>
-      <c r="AU131" s="4" t="inlineStr">
+      <c r="AU132" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5080.pdf</t>
         </is>
       </c>
-      <c r="AV131" s="4" t="inlineStr">
+      <c r="AV132" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5080.pdf</t>
         </is>
       </c>
-      <c r="AW131" s="4" t="inlineStr">
+      <c r="AW132" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5080.pdf</t>
         </is>
       </c>
-      <c r="AX131" s="4" t="inlineStr">
+      <c r="AX132" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5080.pdf</t>
         </is>
       </c>
-      <c r="AY131" s="4" t="inlineStr">
+      <c r="AY132" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5080.pdf</t>
         </is>
       </c>
-      <c r="AZ131" s="4" t="inlineStr">
+      <c r="AZ132" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5080.pdf</t>
-        </is>
-      </c>
-      <c r="BA131" s="4" t="inlineStr"/>
-      <c r="BB131" s="4" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>RENDA FIXA</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>CAIXA FIC FIF TITULO PUBLICO MPE RF LP RESP LTDA</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>05/10/2012</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>3,33116800</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>0,049</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr">
-        <is>
-          <t>9,30</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>13,74</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>24,159</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="M132" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N132" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O132" s="2" t="inlineStr">
-        <is>
-          <t>PJ | TODOS</t>
-        </is>
-      </c>
-      <c r="P132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-tp-mpe-rf-lp/</t>
-        </is>
-      </c>
-      <c r="Q132" s="2" t="inlineStr">
-        <is>
-          <t>15.154.429/0001-00</t>
-        </is>
-      </c>
-      <c r="R132" s="2" t="inlineStr">
-        <is>
-          <t>5833</t>
-        </is>
-      </c>
-      <c r="S132" s="2" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="T132" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="U132" s="2" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="V132" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="W132" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="X132" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Y132" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="Z132" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="AA132" s="2" t="inlineStr">
-        <is>
-          <t>D+00 (du)</t>
-        </is>
-      </c>
-      <c r="AB132" s="2" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="AC132" s="2" t="inlineStr">
-        <is>
-          <t>RF 100% TPF - Longo Prazo</t>
-        </is>
-      </c>
-      <c r="AD132" s="2" t="inlineStr">
-        <is>
-          <t>Aberto para captação</t>
-        </is>
-      </c>
-      <c r="AE132" s="2" t="inlineStr">
-        <is>
-          <t>LONGO PRAZO</t>
-        </is>
-      </c>
-      <c r="AF132" s="2" t="inlineStr">
-        <is>
-          <t>GERAL</t>
-        </is>
-      </c>
-      <c r="AG132" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AH132" s="2" t="inlineStr">
-        <is>
-          <t>17h00</t>
-        </is>
-      </c>
-      <c r="AI132" s="2" t="inlineStr">
-        <is>
-          <t>Sim · Automatico · 90%</t>
-        </is>
-      </c>
-      <c r="AJ132" s="2" t="inlineStr">
-        <is>
-          <t>AUTOMATICO</t>
-        </is>
-      </c>
-      <c r="AK132" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="AL132" s="2" t="inlineStr">
-        <is>
-          <t>["PJ Varejo"]</t>
-        </is>
-      </c>
-      <c r="AM132" s="2" t="inlineStr">
-        <is>
-          <t>["PJ Varejo"]</t>
-        </is>
-      </c>
-      <c r="AN132" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AO132" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AP132" s="2" t="inlineStr"/>
-      <c r="AQ132" s="2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AR132" s="2" t="inlineStr">
-        <is>
-          <t>CAIXA TÍTULO PÚBLICO MPE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS132" s="2" t="inlineStr">
-        <is>
-          <t>Fundo reaberto para novas aplicações a partir de 15/01/2024 (inclusive).
-Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).
-Nome alterado de CAIXA FIC EXPANDIR RF LP para CAIXA FIC TITULO PUBLICO MPE RF LP, em 15 JAN 2024, conforme aprovado em Assembleia Geral de Cotistas.</t>
-        </is>
-      </c>
-      <c r="AT132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5833.pdf</t>
-        </is>
-      </c>
-      <c r="AU132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5833.pdf</t>
-        </is>
-      </c>
-      <c r="AV132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5833.pdf</t>
-        </is>
-      </c>
-      <c r="AW132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5833.pdf</t>
-        </is>
-      </c>
-      <c r="AX132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5833.pdf</t>
-        </is>
-      </c>
-      <c r="AY132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5833.pdf</t>
-        </is>
-      </c>
-      <c r="AZ132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5833.pdf</t>
         </is>
       </c>
       <c r="BA132" s="2" t="inlineStr"/>
@@ -34242,42 +34242,42 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>24,61133200</t>
+          <t>24,64904300</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,222</t>
+          <t>0,153</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>13,51</t>
+          <t>13,58</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>96,306</t>
+          <t>96,438</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -34506,7 +34506,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>3,38821500</t>
+          <t>3,38988200</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -34516,32 +34516,32 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>9,36</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>14,00</t>
+          <t>13,99</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>7.983,586</t>
+          <t>8.040,416</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -34767,22 +34767,22 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1.958,06844100</t>
+          <t>1.959,13587700</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>9,99</t>
+          <t>10,05</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -34792,17 +34792,17 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>16.927,384</t>
+          <t>16.976,273</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -35027,42 +35027,42 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>5,05548800</t>
+          <t>5,05804900</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>9,70</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>14,40</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.203,884</t>
+          <t>3.183,397</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -35287,22 +35287,22 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1,60556680</t>
+          <t>1,60638024</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>9,67</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -35312,17 +35312,17 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>386,094</t>
+          <t>384,360</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>5,31202700</t>
+          <t>5,31469000</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -35541,12 +35541,12 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -35556,17 +35556,17 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>296,511</t>
+          <t>296,659</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -35788,42 +35788,42 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>18,56773200</t>
+          <t>18,57711200</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>9,67</t>
+          <t>9,72</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,46</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>4.867,992</t>
+          <t>4.870,304</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -36032,42 +36032,42 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>9,02678800</t>
+          <t>9,03140300</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>14,39</t>
+          <t>14,38</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.882,435</t>
+          <t>3.884,411</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -36310,12 +36310,12 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -36536,7 +36536,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2,91756500</t>
+          <t>2,91889700</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -36546,32 +36546,32 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>8,70</t>
+          <t>8,75</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>12,99</t>
+          <t>12,98</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>13.852,931</t>
+          <t>13.876,483</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -36787,52 +36787,52 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC ESMERALDA CORP RF REF DI CRED PRIV LP - RESP LTDA</t>
+          <t>CAIXA FIF TOPAZIO CORP RF REFERENC DI - RESP LTDA</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>03/11/2023</t>
+          <t>22/06/2010</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>1,42556600</t>
+          <t>4,59319600</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,80</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>14,78</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>3.433,122</t>
+          <t>16.795,835</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -36852,22 +36852,22 @@
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>GOV | PJ | RPPS</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-esmeralda-corp-ref-di/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/referenciados/fic-topazio-rf-ref-di-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q143" s="4" t="inlineStr">
         <is>
-          <t>52.699.555/0001-77</t>
+          <t>11.061.230/0001-87</t>
         </is>
       </c>
       <c r="R143" s="4" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="S143" s="4" t="inlineStr">
@@ -36877,7 +36877,7 @@
       </c>
       <c r="T143" s="4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U143" s="4" t="inlineStr">
@@ -36917,12 +36917,12 @@
       </c>
       <c r="AB143" s="4" t="inlineStr">
         <is>
-          <t>OUTROS</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="AC143" s="4" t="inlineStr">
         <is>
-          <t>RF Crédito Privado sem Risco Mercado</t>
+          <t>RF REF DI 100% TPF</t>
         </is>
       </c>
       <c r="AD143" s="4" t="inlineStr">
@@ -36952,7 +36952,7 @@
       </c>
       <c r="AI143" s="4" t="inlineStr">
         <is>
-          <t>Não disponível</t>
+          <t>Sim · Automatico · 95%</t>
         </is>
       </c>
       <c r="AJ143" s="4" t="inlineStr">
@@ -36967,12 +36967,12 @@
       </c>
       <c r="AL143" s="4" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AM143" s="4" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AN143" s="4" t="inlineStr">
@@ -36993,47 +36993,51 @@
       </c>
       <c r="AR143" s="4" t="inlineStr">
         <is>
-          <t>CAIXA ESMERALDA CORPORATIVO FIC DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI CRÉDITO PRIVADO LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA TOPÁZIO CORPORATIVO FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS143" s="4" t="inlineStr"/>
       <c r="AT143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6996.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5189.pdf</t>
         </is>
       </c>
       <c r="AU143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6996.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5189.pdf</t>
         </is>
       </c>
       <c r="AV143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6996.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5189.pdf</t>
         </is>
       </c>
       <c r="AW143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6996.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5189.pdf</t>
         </is>
       </c>
       <c r="AX143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6996.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5189.pdf</t>
         </is>
       </c>
       <c r="AY143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6996.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5189.pdf</t>
         </is>
       </c>
       <c r="AZ143" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6996.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5189.pdf</t>
         </is>
       </c>
       <c r="BA143" s="4" t="inlineStr"/>
-      <c r="BB143" s="4" t="inlineStr"/>
+      <c r="BB143" s="4" t="inlineStr">
+        <is>
+          <t>https://web.microsoftstream.com/video/6e74c0e2-b2c6-4bd6-9b53-5982d3f1b8e1?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -37043,52 +37047,52 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF TOPAZIO CORP RF REFERENC DI - RESP LTDA</t>
+          <t>CAIXA FIC ESMERALDA CORP RF REF DI CRED PRIV LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>22/06/2010</t>
+          <t>03/11/2023</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>4,59086800</t>
+          <t>1,42630200</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>9,74</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.784,544</t>
+          <t>3.452,476</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -37108,22 +37112,22 @@
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>GOV | PJ | RPPS</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/referenciados/fic-topazio-rf-ref-di-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-esmeralda-corp-ref-di/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>11.061.230/0001-87</t>
+          <t>52.699.555/0001-77</t>
         </is>
       </c>
       <c r="R144" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="S144" s="2" t="inlineStr">
@@ -37133,7 +37137,7 @@
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="U144" s="2" t="inlineStr">
@@ -37173,12 +37177,12 @@
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>OUTROS</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>RF REF DI 100% TPF</t>
+          <t>RF Crédito Privado sem Risco Mercado</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
@@ -37208,7 +37212,7 @@
       </c>
       <c r="AI144" s="2" t="inlineStr">
         <is>
-          <t>Sim · Automatico · 95%</t>
+          <t>Não disponível</t>
         </is>
       </c>
       <c r="AJ144" s="2" t="inlineStr">
@@ -37223,12 +37227,12 @@
       </c>
       <c r="AL144" s="2" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado"]</t>
+          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
         </is>
       </c>
       <c r="AM144" s="2" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado"]</t>
+          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
         </is>
       </c>
       <c r="AN144" s="2" t="inlineStr">
@@ -37249,51 +37253,47 @@
       </c>
       <c r="AR144" s="2" t="inlineStr">
         <is>
-          <t>CAIXA TOPÁZIO CORPORATIVO FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA ESMERALDA CORPORATIVO FIC DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI CRÉDITO PRIVADO LONGO PRAZO - RESP LIMITADA</t>
         </is>
       </c>
       <c r="AS144" s="2" t="inlineStr"/>
       <c r="AT144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5189.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6996.pdf</t>
         </is>
       </c>
       <c r="AU144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5189.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6996.pdf</t>
         </is>
       </c>
       <c r="AV144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5189.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6996.pdf</t>
         </is>
       </c>
       <c r="AW144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5189.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6996.pdf</t>
         </is>
       </c>
       <c r="AX144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5189.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6996.pdf</t>
         </is>
       </c>
       <c r="AY144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5189.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6996.pdf</t>
         </is>
       </c>
       <c r="AZ144" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5189.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6996.pdf</t>
         </is>
       </c>
       <c r="BA144" s="2" t="inlineStr"/>
-      <c r="BB144" s="2" t="inlineStr">
-        <is>
-          <t>https://web.microsoftstream.com/video/6e74c0e2-b2c6-4bd6-9b53-5982d3f1b8e1?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
-        </is>
-      </c>
+      <c r="BB144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -37313,7 +37313,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1.836,80289500</t>
+          <t>1.837,74088300</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -37323,12 +37323,12 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -37338,17 +37338,17 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>1.526,337</t>
+          <t>1.526,997</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -37573,7 +37573,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1,34657400</t>
+          <t>1,34712800</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -37583,32 +37583,32 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>7,80</t>
+          <t>7,84</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>11,59</t>
+          <t>11,58</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>32.758,347</t>
+          <t>33.408,141</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -37832,7 +37832,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>9,70205200</t>
+          <t>9,70635100</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -37842,12 +37842,12 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>8,39</t>
+          <t>8,44</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -37857,17 +37857,17 @@
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>2.694,847</t>
+          <t>2.766,242</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -38091,7 +38091,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2,55494100</t>
+          <t>2,55608600</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -38101,12 +38101,12 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>8,43</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -38116,17 +38116,17 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>17.255,698</t>
+          <t>17.297,373</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -38352,22 +38352,22 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,64837100</t>
+          <t>4,65074900</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>9,60</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -38377,17 +38377,17 @@
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.776,962</t>
+          <t>11.853,871</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -38615,42 +38615,42 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,77338300</t>
+          <t>3,77422200</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>0,135</t>
+          <t>0,022</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,20</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,50</t>
+          <t>12,41</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>1.657,880</t>
+          <t>1.658,500</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -38878,42 +38878,42 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>2,48270600</t>
+          <t>2,48387000</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>0,062</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>7,80</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>3.308,146</t>
+          <t>3.310,702</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -39143,42 +39143,42 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>3,09011000</t>
+          <t>3,09488200</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,223</t>
+          <t>0,154</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,74</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>13,29</t>
+          <t>13,36</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>37,479</t>
+          <t>37,537</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -39399,42 +39399,42 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1.696,68429200</t>
+          <t>1.697,53868000</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>8,16</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,51</t>
+          <t>12,48</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>449,862</t>
+          <t>450,089</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -39659,22 +39659,22 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>3,95201500</t>
+          <t>3,95570400</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,176</t>
+          <t>0,093</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>9,88</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
@@ -39684,17 +39684,17 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>3.144,217</t>
+          <t>3.147,713</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -39922,42 +39922,42 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>5,32247200</t>
+          <t>5,33542800</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,438</t>
+          <t>0,243</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>8,50</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>12,45</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>2.338,676</t>
+          <t>2.349,436</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -40184,42 +40184,42 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>5,37371500</t>
+          <t>5,38155400</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>0,236</t>
+          <t>0,145</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>10,07</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>13,71</t>
+          <t>13,77</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>5.795,455</t>
+          <t>5.811,144</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -40446,22 +40446,22 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>4,91667500</t>
+          <t>4,92089600</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>0,150</t>
+          <t>0,085</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>8,92</t>
+          <t>9,02</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -40471,17 +40471,17 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>484,668</t>
+          <t>485,083</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -40708,42 +40708,42 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>8,23127100</t>
+          <t>8,23540100</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,60</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>14,26</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>165,444</t>
+          <t>165,498</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -40828,42 +40828,42 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>3,55994600</t>
+          <t>3,57040200</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>0,547</t>
+          <t>0,293</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>6,70</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>11,09</t>
+          <t>11,24</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>696,251</t>
+          <t>693,527</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -41090,42 +41090,42 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>3,91169100</t>
+          <t>3,91221400</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>0,165</t>
+          <t>0,013</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>11,89</t>
+          <t>11,75</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>634,097</t>
+          <t>635,239</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -41353,22 +41353,22 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>2,70331200</t>
+          <t>2,70474500</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -41378,17 +41378,17 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>8.728,064</t>
+          <t>8.711,814</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -41617,42 +41617,42 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>7,43103900</t>
+          <t>7,43477400</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>12.776,842</t>
+          <t>12.915,263</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -41882,7 +41882,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>7,76127700</t>
+          <t>7,76521800</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -41892,12 +41892,12 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>9,60</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -41907,17 +41907,17 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>3.728,174</t>
+          <t>3.777,896</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -42142,42 +42142,42 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1,50494500</t>
+          <t>1,50545800</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>0,089</t>
+          <t>0,034</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,96</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>12,30</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>163,541</t>
+          <t>163,596</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -42398,22 +42398,22 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,24619400</t>
+          <t>3,24776300</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>9,04</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -42423,17 +42423,17 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>1.913,295</t>
+          <t>1.922,988</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -42686,12 +42686,12 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -42942,12 +42942,12 @@
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -43158,12 +43158,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL 2029 SEM CUPOM TP FIF RF - RL</t>
+          <t>CAIXA BRASIL 2033 SEM CUPOM TP FIF RF - RESP LTDA</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -43198,12 +43198,12 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -43229,12 +43229,12 @@
       <c r="P168" s="2" t="inlineStr"/>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t>68.692.739/0001-45</t>
+          <t>68.785.726/0001-10</t>
         </is>
       </c>
       <c r="R168" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="S168" s="2" t="inlineStr">
@@ -43284,7 +43284,7 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>IPCA + 5,5%</t>
+          <t>IPCA + 5,5</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
@@ -43350,7 +43350,7 @@
       </c>
       <c r="AP168" s="2" t="inlineStr">
         <is>
-          <t>2029-05-15T00:00:00Z</t>
+          <t>2033-05-16T00:00:00Z</t>
         </is>
       </c>
       <c r="AQ168" s="2" t="inlineStr">
@@ -43360,47 +43360,47 @@
       </c>
       <c r="AR168" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL 2029 SEM CUPOM TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA BRASIL 2033 SEM CUPOM TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS168" s="2" t="inlineStr">
         <is>
-          <t>Fundo com prazo de carência, resgates podem ser solicitados a partir de 15/05/2029, conforme Regulamento.</t>
+          <t>Fundo com prazo de carência, resgates podem ser solicitados a partir de 16/05/2033, conforme Regulamento.</t>
         </is>
       </c>
       <c r="AT168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_8527.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7928.pdf</t>
         </is>
       </c>
       <c r="AU168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_8527.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7928.pdf</t>
         </is>
       </c>
       <c r="AV168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_8527.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7928.pdf</t>
         </is>
       </c>
       <c r="AW168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_8527.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7928.pdf</t>
         </is>
       </c>
       <c r="AX168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_8527.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7928.pdf</t>
         </is>
       </c>
       <c r="AY168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8527.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7928.pdf</t>
         </is>
       </c>
       <c r="AZ168" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_8527.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7928.pdf</t>
         </is>
       </c>
       <c r="BA168" s="2" t="inlineStr"/>
@@ -43414,12 +43414,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL 2033 SEM CUPOM TP FIF RF - RESP LTDA</t>
+          <t>CAIXA BRASIL 2037 SEM CUPOM TP FIF RF - RESP LTDA</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -43454,12 +43454,12 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -43485,12 +43485,12 @@
       <c r="P169" s="4" t="inlineStr"/>
       <c r="Q169" s="4" t="inlineStr">
         <is>
-          <t>68.785.726/0001-10</t>
+          <t>68.786.122/0001-99</t>
         </is>
       </c>
       <c r="R169" s="4" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="S169" s="4" t="inlineStr">
@@ -43584,16 +43584,8 @@
         </is>
       </c>
       <c r="AK169" s="4" t="inlineStr"/>
-      <c r="AL169" s="4" t="inlineStr">
-        <is>
-          <t>["GOV", "RPPS"]</t>
-        </is>
-      </c>
-      <c r="AM169" s="4" t="inlineStr">
-        <is>
-          <t>["GOV", "RPPS"]</t>
-        </is>
-      </c>
+      <c r="AL169" s="4" t="inlineStr"/>
+      <c r="AM169" s="4" t="inlineStr"/>
       <c r="AN169" s="4" t="inlineStr">
         <is>
           <t>Não</t>
@@ -43606,7 +43598,7 @@
       </c>
       <c r="AP169" s="4" t="inlineStr">
         <is>
-          <t>2033-05-16T00:00:00Z</t>
+          <t>2037-05-15T00:00:00Z</t>
         </is>
       </c>
       <c r="AQ169" s="4" t="inlineStr">
@@ -43616,47 +43608,47 @@
       </c>
       <c r="AR169" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL 2033 SEM CUPOM TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA BRASIL 2037 SEM CUPOM TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS169" s="4" t="inlineStr">
         <is>
-          <t>Fundo com prazo de carência, resgates podem ser solicitados a partir de 16/05/2033, conforme Regulamento.</t>
+          <t>Fundo com prazo de carência, resgates podem ser solicitados a partir de 15/05/2037, conforme Regulamento.</t>
         </is>
       </c>
       <c r="AT169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7928.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7932.pdf</t>
         </is>
       </c>
       <c r="AU169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7928.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7932.pdf</t>
         </is>
       </c>
       <c r="AV169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7928.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7932.pdf</t>
         </is>
       </c>
       <c r="AW169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7928.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7932.pdf</t>
         </is>
       </c>
       <c r="AX169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7928.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7932.pdf</t>
         </is>
       </c>
       <c r="AY169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7928.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7932.pdf</t>
         </is>
       </c>
       <c r="AZ169" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7928.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7932.pdf</t>
         </is>
       </c>
       <c r="BA169" s="4" t="inlineStr"/>
@@ -43670,12 +43662,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL 2037 SEM CUPOM TP FIF RF - RESP LTDA</t>
+          <t>CAIXA BRASIL 2029 SEM CUPOM TP FIF RF - RL</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -43710,12 +43702,12 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -43741,12 +43733,12 @@
       <c r="P170" s="2" t="inlineStr"/>
       <c r="Q170" s="2" t="inlineStr">
         <is>
-          <t>68.786.122/0001-99</t>
+          <t>68.692.739/0001-45</t>
         </is>
       </c>
       <c r="R170" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="S170" s="2" t="inlineStr">
@@ -43796,7 +43788,7 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>IPCA + 5,5</t>
+          <t>IPCA + 5,5%</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
@@ -43840,8 +43832,16 @@
         </is>
       </c>
       <c r="AK170" s="2" t="inlineStr"/>
-      <c r="AL170" s="2" t="inlineStr"/>
-      <c r="AM170" s="2" t="inlineStr"/>
+      <c r="AL170" s="2" t="inlineStr">
+        <is>
+          <t>["GOV", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AM170" s="2" t="inlineStr">
+        <is>
+          <t>["GOV", "RPPS"]</t>
+        </is>
+      </c>
       <c r="AN170" s="2" t="inlineStr">
         <is>
           <t>Não</t>
@@ -43854,7 +43854,7 @@
       </c>
       <c r="AP170" s="2" t="inlineStr">
         <is>
-          <t>2037-05-15T00:00:00Z</t>
+          <t>2029-05-15T00:00:00Z</t>
         </is>
       </c>
       <c r="AQ170" s="2" t="inlineStr">
@@ -43864,47 +43864,47 @@
       </c>
       <c r="AR170" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL 2037 SEM CUPOM TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA BRASIL 2029 SEM CUPOM TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS170" s="2" t="inlineStr">
         <is>
-          <t>Fundo com prazo de carência, resgates podem ser solicitados a partir de 15/05/2037, conforme Regulamento.</t>
+          <t>Fundo com prazo de carência, resgates podem ser solicitados a partir de 15/05/2029, conforme Regulamento.</t>
         </is>
       </c>
       <c r="AT170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7932.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_8527.pdf</t>
         </is>
       </c>
       <c r="AU170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7932.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_8527.pdf</t>
         </is>
       </c>
       <c r="AV170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7932.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_8527.pdf</t>
         </is>
       </c>
       <c r="AW170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7932.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_8527.pdf</t>
         </is>
       </c>
       <c r="AX170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7932.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_8527.pdf</t>
         </is>
       </c>
       <c r="AY170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7932.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8527.pdf</t>
         </is>
       </c>
       <c r="AZ170" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7932.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_8527.pdf</t>
         </is>
       </c>
       <c r="BA170" s="2" t="inlineStr"/>
@@ -43958,12 +43958,12 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -44184,42 +44184,42 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>6,96887400</t>
+          <t>6,97260800</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>9,80</t>
+          <t>9,86</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,62</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>22.411,207</t>
+          <t>22.509,990</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -44304,42 +44304,42 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>5,70548800</t>
+          <t>5,72028500</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>0,437</t>
+          <t>0,259</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>8,54</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>12,73</t>
+          <t>12,90</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>591,185</t>
+          <t>592,718</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -44595,12 +44595,12 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -44817,42 +44817,42 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>4,21406700</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>1,384</t>
+          <t>4,19072900</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>-0,553</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>16,39</t>
+          <t>15,74</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>31,53</t>
+          <t>30,08</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>309,071</t>
+          <t>307,345</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -45077,42 +45077,42 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>3,86814400</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>1,352</t>
+          <t>3,84698200</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>-0,547</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>16,01</t>
+          <t>15,38</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>30,96</t>
+          <t>29,42</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>8,063</t>
+          <t>8,019</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -45337,42 +45337,42 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>11,55351856</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>-0,803</t>
+          <t>11,72314035</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>1,468</t>
         </is>
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>-2,20</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>12,71</t>
+          <t>14,24</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>2.311,283</t>
+          <t>2.343,957</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -45597,42 +45597,42 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>2,14828400</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>1,336</t>
+          <t>2,13468400</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>-0,633</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>5,80</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>12,62</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>25,86</t>
+          <t>24,21</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>209,922</t>
+          <t>208,593</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -45853,42 +45853,42 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>2,10406500</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>2,443</t>
+          <t>2,08861000</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>-0,734</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>12,48</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>765,154</t>
+          <t>759,533</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -46113,42 +46113,42 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>3,67935932</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>1,550</t>
+          <t>3,65120105</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>-0,765</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>13,09</t>
+          <t>12,23</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>24,25</t>
+          <t>22,50</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>1.394,633</t>
+          <t>1.383,960</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -46365,42 +46365,42 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>2,65723004</t>
-        </is>
-      </c>
-      <c r="E181" s="5" t="inlineStr">
-        <is>
-          <t>1,573</t>
+          <t>2,64009430</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>-0,644</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>12,42</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>24,38</t>
+          <t>22,47</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>812,290</t>
+          <t>807,051</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -46617,22 +46617,22 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>3,88909700</t>
+          <t>3,89109900</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>9,52</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
@@ -46642,17 +46642,17 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>4.532,260</t>
+          <t>4.513,780</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -814,42 +814,42 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,33114400</t>
+          <t>2,33218200</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>8,48</t>
+          <t>8,53</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,59</t>
+          <t>12,58</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>401,806</t>
+          <t>401,104</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1074,42 +1074,42 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,66253100</t>
+          <t>5,66501600</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>8,32</t>
+          <t>8,37</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>12,35</t>
+          <t>12,34</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.629,182</t>
+          <t>6.596,357</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -1334,22 +1334,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,85909700</t>
+          <t>2,86035100</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>825,664</t>
+          <t>828,000</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1593,42 +1593,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>20,55803800</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>0,016</t>
+          <t>20,54322600</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>-0,072</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,18</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>11,19</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>115,704</t>
+          <t>115,598</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,10342100</t>
+          <t>3,10499500</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>9,81</t>
+          <t>9,87</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1.715,260</t>
+          <t>1.713,020</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2113,42 +2113,42 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.901,56818200</t>
+          <t>1.902,53720000</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,41</t>
+          <t>14,40</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>97,983</t>
+          <t>98,041</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2621,22 +2621,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,46995400</t>
+          <t>3,47162100</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>65,140</t>
+          <t>64,825</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,01330800</t>
+          <t>10,01781000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>8,90</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2902,17 +2902,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>590,118</t>
+          <t>590,180</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,92511000</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>0,148</t>
+          <t>13,92462900</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3273,22 +3273,22 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>11,57</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,964</t>
+          <t>27,921</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3517,22 +3517,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>3,60581000</t>
+          <t>3,60756600</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>9,54</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -3542,17 +3542,17 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>121,196</t>
+          <t>120,845</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -3780,22 +3780,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,44480400</t>
+          <t>3,44647300</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>9,32</t>
+          <t>9,38</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -3805,17 +3805,17 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,316</t>
+          <t>12,305</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>20,83745800</t>
+          <t>20,84697300</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -4050,32 +4050,32 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>8,64</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>12,78</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>59,469</t>
+          <t>59,470</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4300,22 +4300,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>47,61838000</t>
+          <t>47,63972900</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>8,83</t>
+          <t>8,87</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,436</t>
+          <t>41,455</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,25435700</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>0,150</t>
+          <t>3,25433100</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -4581,22 +4581,22 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>77,268</t>
+          <t>77,266</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4825,22 +4825,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15,42991700</t>
+          <t>15,43688600</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -4850,17 +4850,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,033</t>
+          <t>28,045</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5085,22 +5085,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,09197900</t>
+          <t>3,09333100</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>8,60</t>
+          <t>8,65</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -5341,42 +5341,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,14708900</t>
+          <t>3,14869200</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>14,53</t>
+          <t>14,52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1.793,575</t>
+          <t>1.789,552</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5595,42 +5595,42 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,43478400</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>0,019</t>
+          <t>3,43260100</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>-0,063</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>7,70</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>11,89</t>
+          <t>11,82</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>125,388</t>
+          <t>125,252</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33,86320000</t>
+          <t>33,87895200</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>9,20</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5884,17 +5884,17 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2.233,300</t>
+          <t>2.232,268</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -6119,42 +6119,42 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3,41386800</t>
+          <t>3,41545800</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>9,21</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>13,57</t>
+          <t>13,56</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12,999</t>
+          <t>12,980</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -6384,42 +6384,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,45343600</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>0,256</t>
+          <t>3,44723100</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>-0,179</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>8,16</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>12,20</t>
+          <t>11,92</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64,664</t>
+          <t>64,491</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -6644,42 +6644,42 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>19,67780500</t>
+          <t>19,68728500</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>9,44</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>13,93</t>
+          <t>13,92</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>967,558</t>
+          <t>967,549</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -6904,22 +6904,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,28490800</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,28559300</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>9,70</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -6929,17 +6929,17 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,184</t>
+          <t>75,224</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,15410962</t>
+          <t>1,15433338</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -7166,32 +7166,32 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>9,64</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>199,848</t>
+          <t>198,552</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -7412,42 +7412,42 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,21424800</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,21475000</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>9,34</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>13,87</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,997</t>
+          <t>64,074</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,10523055</t>
+          <t>1,10389587</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -7672,34 +7672,34 @@
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>6,83</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>6,96</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>306,707</t>
+          <t>306,872</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -7916,22 +7916,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,31544600</t>
+          <t>1,31612800</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>9,97</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>480,446</t>
+          <t>481,004</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8176,42 +8176,42 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.898,22777000</t>
+          <t>1.899,19447500</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>9,90</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>182,348</t>
+          <t>182,434</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -8436,42 +8436,42 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,24407100</t>
+          <t>1,24447000</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,020</t>
+          <t>0,032</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>10,69</t>
+          <t>10,73</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,43</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,343</t>
+          <t>41,356</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8696,42 +8696,42 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>5,12158400</t>
+          <t>5,12418800</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>14,53</t>
+          <t>14,52</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.474,973</t>
+          <t>3.475,740</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9204,22 +9204,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>5,71415900</t>
+          <t>5,71695500</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -9229,17 +9229,17 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>570,190</t>
+          <t>570,272</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -9465,22 +9465,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10,96752800</t>
+          <t>10,97300200</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,77</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -9490,17 +9490,17 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2.436,008</t>
+          <t>2.436,530</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1,07527100</t>
+          <t>1,07581400</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -9750,17 +9750,17 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>22,456</t>
+          <t>22,467</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -9973,22 +9973,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5,32286600</t>
+          <t>5,32546800</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -9998,17 +9998,17 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>856,236</t>
+          <t>856,407</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>30,17439100</t>
+          <t>30,18844200</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>8,80</t>
+          <t>8,85</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -10258,17 +10258,17 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>21,574</t>
+          <t>21,585</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3,33608500</t>
+          <t>3,33780900</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -10491,12 +10491,12 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>9,83</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -10506,17 +10506,17 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>662,928</t>
+          <t>666,689</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -10741,42 +10741,42 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.828,76920100</t>
+          <t>1.829,49055600</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>8,56</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>12,87</t>
+          <t>12,89</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>118,183</t>
+          <t>117,451</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>31,67312000</t>
+          <t>31,68869700</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -11022,17 +11022,17 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3.143,910</t>
+          <t>3.140,856</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -11253,22 +11253,22 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>6,39955300</t>
+          <t>6,40264400</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>9,41</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -11278,17 +11278,17 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>122,076</t>
+          <t>122,108</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -11514,22 +11514,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3,69761300</t>
+          <t>3,69952300</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>9,94</t>
+          <t>10,00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -11539,17 +11539,17 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16.786,666</t>
+          <t>16.782,873</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -11778,22 +11778,22 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>5,49780300</t>
+          <t>5,50064300</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>10,10</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -11803,17 +11803,17 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>1.516,854</t>
+          <t>1.517,634</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>31,28249200</t>
+          <t>31,29678600</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -12049,32 +12049,32 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>8,71</t>
+          <t>8,76</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>12,93</t>
+          <t>12,92</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>168,060</t>
+          <t>168,198</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -12555,22 +12555,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3,72934700</t>
+          <t>3,73119800</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>9,54</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -12580,17 +12580,17 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2.313,925</t>
+          <t>2.313,577</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12819,42 +12819,42 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2,89574700</t>
+          <t>2,89705500</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>8,60</t>
+          <t>8,65</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>6.066,563</t>
+          <t>6.048,078</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1,33577800</t>
+          <t>1,33645900</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>9,71</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -13104,17 +13104,17 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>73,739</t>
+          <t>74,272</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -13339,22 +13339,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>3,30134000</t>
+          <t>3,30305000</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>9,90</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>14.713,913</t>
+          <t>14.722,167</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -13599,42 +13599,42 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10,02165800</t>
+          <t>10,02667100</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>14,18</t>
+          <t>14,17</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>823,745</t>
+          <t>823,813</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -13864,42 +13864,42 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4,61071000</t>
+          <t>4,61303100</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>9,59</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,25</t>
+          <t>14,24</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>17.132,799</t>
+          <t>17.105,001</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -14124,22 +14124,22 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>5,28353700</t>
+          <t>5,28625400</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,87</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -14149,17 +14149,17 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23.420,045</t>
+          <t>23.423,422</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -14384,22 +14384,22 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4,94428100</t>
+          <t>4,94681300</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -14409,17 +14409,17 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>9.899,120</t>
+          <t>9.903,384</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.788,55569900</t>
+          <t>1.789,44126200</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -14658,32 +14658,32 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>9,36</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>13,92</t>
+          <t>13,91</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>293,966</t>
+          <t>293,174</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -14768,42 +14768,42 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1,46614700</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,46674300</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>-0,007</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>9,50</t>
+          <t>9,55</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>14,07</t>
+          <t>14,05</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>65,587</t>
+          <t>65,615</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -15020,27 +15020,27 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>13,17794600</t>
+          <t>13,15674200</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>-0,123</t>
+          <t>-0,160</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>11,01</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>17,98</t>
+          <t>17,99</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -15050,12 +15050,12 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.689,90671600</t>
+          <t>1.692,57819400</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -15294,32 +15294,32 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>12,27</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>111,870</t>
+          <t>112,028</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -15540,42 +15540,42 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.520,78997800</t>
+          <t>2.513,43300800</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>-0,524</t>
+          <t>-0,291</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>22,72</t>
+          <t>22,36</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>28,04</t>
+          <t>26,72</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14,345</t>
+          <t>14,306</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,28563000</t>
+          <t>1,28627000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -16058,32 +16058,32 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>9,77</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4,984</t>
+          <t>4,986</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -16304,42 +16304,42 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1,17470400</t>
+          <t>1,16195100</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>-0,568</t>
+          <t>-1,085</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>13,65</t>
+          <t>12,77</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>3,462</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -16590,12 +16590,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -16812,42 +16812,42 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1,43795800</t>
+          <t>1,43116300</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>-0,004</t>
+          <t>-0,019</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>11,98</t>
+          <t>11,58</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>11,524</t>
+          <t>11,470</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -17098,12 +17098,12 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -17320,42 +17320,42 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1,12795400</t>
+          <t>1,12841700</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>0,447</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,10</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>-6,44</t>
+          <t>-6,41</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>3,280</t>
+          <t>3,279</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>5,53015105</t>
+          <t>5,53792979</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -17586,32 +17586,32 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>7,92</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>32,682</t>
+          <t>32,727</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1.235,76920500</t>
+          <t>1.249,58233100</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -17846,32 +17846,32 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>-4,09</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>37,101</t>
+          <t>37,514</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -18106,42 +18106,42 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>4,66829800</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>0,055</t>
+          <t>4,61471200</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-1,147</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-2,47</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>26,98</t>
+          <t>25,07</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>533,528</t>
+          <t>527,189</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2,94039500</t>
+          <t>2,94048700</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>-0,003</t>
+          <t>-0,011</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -18386,22 +18386,22 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>9,27</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>68,924</t>
+          <t>68,838</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -18622,42 +18622,42 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1.688,50231500</t>
+          <t>1.696,09383200</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,204</t>
+          <t>0,449</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>-1,60</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>30,204</t>
+          <t>30,339</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -18882,42 +18882,42 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>3,96024100</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>0,847</t>
+          <t>3,94368900</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>-0,417</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>17,72</t>
+          <t>17,23</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>26,47</t>
+          <t>26,00</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2.446,470</t>
+          <t>2.436,015</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -19142,42 +19142,42 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1,96588300</t>
+          <t>1,96651800</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,032</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>8,17</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>12,21</t>
+          <t>12,22</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20,317</t>
+          <t>20,327</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1.715,87876500</t>
+          <t>1.718,63270100</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -19412,32 +19412,32 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>8,49</t>
+          <t>8,67</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>13,25</t>
+          <t>13,40</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>14,901</t>
+          <t>14,924</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -19658,42 +19658,42 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>5,82874700</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>0,135</t>
+          <t>5,82790900</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-0,014</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>14,17</t>
+          <t>14,11</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>903,211</t>
+          <t>903,057</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0,56277684</t>
+          <t>0,56803087</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -19928,12 +19928,12 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>-3,40</t>
+          <t>-2,50</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-22,06</t>
+          <t>-21,33</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -19943,17 +19943,17 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>11,499</t>
+          <t>11,561</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -20185,42 +20185,42 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3,77107800</t>
+          <t>3,77235300</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>8,42</t>
+          <t>8,45</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>12,62</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>709,345</t>
+          <t>711,082</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,41345400</t>
+          <t>1,41292000</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -20451,32 +20451,32 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>72,432</t>
+          <t>72,405</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -20709,7 +20709,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1,52963600</t>
+          <t>1,53035500</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -20719,32 +20719,32 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>11,53</t>
+          <t>11,57</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>116,750</t>
+          <t>109,917</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,38053200</t>
+          <t>3,38354800</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -20987,32 +20987,32 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>8,64</t>
+          <t>8,70</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>161,010</t>
+          <t>161,153</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1,60532900</t>
+          <t>1,60658500</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -21253,32 +21253,32 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,59</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>20,48</t>
+          <t>21,15</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>15,123</t>
+          <t>15,135</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>6,94853900</t>
+          <t>6,93915600</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -21519,32 +21519,32 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>8,04</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>13,22</t>
+          <t>13,26</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>126,058</t>
+          <t>125,907</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,84487900</t>
+          <t>1,84894200</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -21775,32 +21775,32 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>4,43</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>9,38</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>169,985</t>
+          <t>170,215</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1,44031500</t>
+          <t>1,43802000</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -22031,32 +22031,32 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>9,41</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>278,651</t>
+          <t>278,212</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1,41244100</t>
+          <t>1,41093300</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -22292,32 +22292,32 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>-0,40</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>9,69</t>
+          <t>9,48</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>12,563</t>
+          <t>12,550</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -22542,42 +22542,42 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3,86681600</t>
+          <t>3,88184500</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>0,616</t>
+          <t>0,388</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>-3,80</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>-0,59</t>
+          <t>-3,43</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>0,43</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>97,129</t>
+          <t>97,528</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -22832,12 +22832,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -22922,42 +22922,42 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1,32231400</t>
+          <t>1,31239500</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>-0,050</t>
+          <t>-0,750</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>8,44</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>17,82</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>4,044</t>
+          <t>4,013</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -23178,42 +23178,42 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2,77552500</t>
+          <t>2,75083100</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>-0,552</t>
+          <t>-0,889</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>15,35</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>29,43</t>
+          <t>29,06</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>13,637</t>
+          <t>13,515</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -23438,42 +23438,42 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2.015,39755100</t>
+          <t>1.990,62027100</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>-0,733</t>
+          <t>-1,229</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>7,11</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>13,75</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>9,743</t>
+          <t>9,622</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -23687,42 +23687,42 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>10,43531400</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>1,455</t>
+          <t>10,41728400</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>-0,172</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,20</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>13,35</t>
+          <t>13,69</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>270,720</t>
+          <t>270,206</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -23947,42 +23947,42 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1,42469000</t>
+          <t>1,41372600</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>-1,357</t>
+          <t>-0,769</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>-6,54</t>
+          <t>-7,26</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-5,19</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>415,227</t>
+          <t>412,031</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -24207,42 +24207,42 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1,08451400</t>
+          <t>1,07943000</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>-1,244</t>
+          <t>-0,468</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>3,60</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>-6,82</t>
+          <t>-7,26</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>-3,15</t>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>53,294</t>
+          <t>53,042</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -24467,42 +24467,42 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,78885700</t>
+          <t>1,77442600</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-0,890</t>
+          <t>-0,806</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>11,36</t>
+          <t>10,78</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>2,095</t>
+          <t>2,078</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -24727,42 +24727,42 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>5,44401800</t>
+          <t>5,41857600</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>-0,218</t>
+          <t>-0,467</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>72,87</t>
+          <t>72,06</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>69,40</t>
+          <t>70,06</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>88,929</t>
+          <t>88,510</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -24987,42 +24987,42 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>9,27148100</t>
+          <t>9,18862400</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>-0,556</t>
+          <t>-0,893</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>13,48</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>28,07</t>
+          <t>27,71</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>92,851</t>
+          <t>91,837</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -25247,42 +25247,42 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,34503600</t>
+          <t>1,33215400</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>-0,018</t>
+          <t>-0,122</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>3,50</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>10,59</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>300,082</t>
+          <t>297,023</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -25507,42 +25507,42 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1,77776600</t>
+          <t>1,74088200</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>-2,023</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>2,10</t>
+          <t>-2,074</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-6,50</t>
+          <t>-8,44</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>-2,60</t>
+          <t>-4,91</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>105,439</t>
+          <t>103,207</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -25767,42 +25767,42 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2,96698800</t>
+          <t>2,96164300</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>-0,980</t>
+          <t>-0,180</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>8,66</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>16,84</t>
+          <t>17,09</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>122,732</t>
+          <t>122,511</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -26027,42 +26027,42 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1,95152800</t>
+          <t>1,92759500</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>-0,733</t>
+          <t>-1,226</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>7,03</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>0,71</t>
+          <t>5,72</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>12,44</t>
+          <t>11,34</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>50,581</t>
+          <t>49,656</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -26291,42 +26291,42 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>7,80081300</t>
+          <t>7,78839900</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>-0,237</t>
+          <t>-0,159</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>8,29</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>66,31</t>
+          <t>66,05</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>67,97</t>
+          <t>68,80</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>140,677</t>
+          <t>140,425</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -26551,42 +26551,42 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1.423,39146800</t>
+          <t>1.399,95804000</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>-1,360</t>
+          <t>-1,646</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>45,009</t>
+          <t>44,233</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -26811,42 +26811,42 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>37,76408100</t>
+          <t>36,45112300</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>-0,045</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>0,35</t>
+          <t>-3,476</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>-3,13</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>43,88</t>
+          <t>38,94</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>625,262</t>
+          <t>603,411</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -27071,42 +27071,42 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>3,05708100</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>-2,403</t>
+          <t>3,09393700</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>1,205</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>3,70</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>26,20</t>
+          <t>27,72</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>53,86</t>
+          <t>55,27</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>504,230</t>
+          <t>510,286</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -27335,42 +27335,42 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,10740600</t>
+          <t>5,05284700</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>-0,692</t>
+          <t>-1,068</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>13,80</t>
+          <t>12,59</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>26,89</t>
+          <t>26,18</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>24,300</t>
+          <t>24,035</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -27595,42 +27595,42 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1.648,12251100</t>
+          <t>1.638,10793100</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>-0,429</t>
+          <t>-0,607</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>13,24</t>
+          <t>12,56</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>24,23</t>
+          <t>24,74</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>32,451</t>
+          <t>32,254</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -27855,42 +27855,42 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2,03651800</t>
+          <t>2,01115200</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>-1,377</t>
+          <t>-1,245</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>4,81</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>0,10</t>
+          <t>3,50</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>7,54</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>1,795</t>
+          <t>1,765</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -28107,42 +28107,42 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>6,30749800</t>
+          <t>6,25450000</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>-0,584</t>
+          <t>-0,840</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>16,26</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>31,62</t>
+          <t>31,36</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>45,633</t>
+          <t>45,247</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -28359,42 +28359,42 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2,34195300</t>
+          <t>2,31709900</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>-0,383</t>
+          <t>-1,061</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>11,61</t>
+          <t>10,43</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>24,06</t>
+          <t>23,34</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>35,525</t>
+          <t>35,141</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -28619,42 +28619,42 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>50,50414900</t>
+          <t>50,26838600</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>-0,217</t>
+          <t>-0,466</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>72,98</t>
+          <t>72,18</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>69,55</t>
+          <t>70,21</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>958,504</t>
+          <t>953,701</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -28879,42 +28879,42 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,51110300</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>-2,404</t>
+          <t>1,52931300</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>1,205</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>26,19</t>
+          <t>27,71</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>53,81</t>
+          <t>55,22</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>19,833</t>
+          <t>20,072</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -29139,42 +29139,42 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1,85547000</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>-1,608</t>
+          <t>1,86454500</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>0,489</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>52,20</t>
+          <t>52,95</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>277,043</t>
+          <t>278,405</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -29403,42 +29403,42 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>0,91158000</t>
+          <t>0,89771900</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>-0,970</t>
+          <t>-1,520</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>-5,30</t>
+          <t>-6,74</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>-8,97</t>
+          <t>-9,99</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>2,808</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -29659,42 +29659,42 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>7,15844800</t>
+          <t>7,10264600</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>-0,774</t>
+          <t>-0,779</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>5,00</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>11,98</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>24,86</t>
+          <t>24,20</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>344,866</t>
+          <t>342,117</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -29919,42 +29919,42 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1.063,37786900</t>
+          <t>1.055,69632900</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>4,72</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>19,03</t>
+          <t>18,72</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>8,544</t>
+          <t>8,483</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -30179,42 +30179,42 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1.573,10395700</t>
+          <t>1.561,60669700</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>-0,001</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>12,23</t>
+          <t>12,16</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>22,453</t>
+          <t>22,289</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -30435,42 +30435,42 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>182,32370783</t>
+          <t>180,70455464</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>-0,551</t>
+          <t>-0,888</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>15,70</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>30,03</t>
+          <t>29,66</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>18,234</t>
+          <t>18,072</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -30695,42 +30695,42 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1,89347800</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>-1,604</t>
+          <t>1,90270900</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>0,487</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>8,37</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>52,25</t>
+          <t>53,00</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>5,467</t>
+          <t>5,493</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -30952,42 +30952,42 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1,84911500</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>-1,612</t>
+          <t>1,85820100</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>0,491</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>52,46</t>
+          <t>53,21</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>1.656,470</t>
+          <t>1.664,457</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -31205,42 +31205,42 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>56,25124000</t>
+          <t>55,98994900</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>-0,215</t>
+          <t>-0,464</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>8,07</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>73,68</t>
+          <t>72,87</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>70,47</t>
+          <t>71,14</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>787,457</t>
+          <t>783,790</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -31449,42 +31449,42 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>41,90465100</t>
+          <t>40,44681500</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>-0,043</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>0,37</t>
+          <t>-3,478</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>-3,11</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>9,71</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>44,67</t>
+          <t>39,69</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>734,503</t>
+          <t>708,943</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -31693,42 +31693,42 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>17,23386700</t>
+          <t>17,04749700</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>-0,557</t>
+          <t>-1,081</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>7,14</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>15,39</t>
+          <t>14,50</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>114,212</t>
+          <t>112,977</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -31946,42 +31946,42 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>35,07065100</t>
+          <t>33,85620600</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>-0,045</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>0,36</t>
+          <t>-3,462</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>-3,11</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>9,29</t>
+          <t>5,50</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>43,72</t>
+          <t>38,80</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>11,775</t>
+          <t>11,367</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -32195,42 +32195,42 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>49,65937400</t>
+          <t>49,42767500</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>-0,217</t>
+          <t>-0,466</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>8,07</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>73,20</t>
+          <t>72,40</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>69,78</t>
+          <t>70,45</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>681,637</t>
+          <t>678,457</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -32444,42 +32444,42 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>36,02941500</t>
+          <t>34,77711800</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>-0,045</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>0,36</t>
+          <t>-3,475</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>-3,12</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>9,34</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>43,95</t>
+          <t>39,00</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>444,046</t>
+          <t>428,536</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -32688,42 +32688,42 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>52,82149700</t>
+          <t>52,57513800</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>-0,217</t>
+          <t>-0,466</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>8,07</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>73,45</t>
+          <t>72,65</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>70,12</t>
+          <t>70,79</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>774,394</t>
+          <t>770,377</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1,16124600</t>
+          <t>1,16177100</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -32946,32 +32946,32 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>12,70</t>
+          <t>12,69</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>64,064</t>
+          <t>66,276</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -33197,7 +33197,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1,40158600</t>
+          <t>1,40222200</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -33207,32 +33207,32 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>8,60</t>
+          <t>8,65</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>12,77</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>245,923</t>
+          <t>215,509</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -33462,42 +33462,42 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>6,09376100</t>
+          <t>6,09665000</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>9,24</t>
+          <t>9,29</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>13,71</t>
+          <t>13,70</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>42,956</t>
+          <t>43,000</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -33723,22 +33723,22 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,33279800</t>
+          <t>3,33444900</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>9,35</t>
+          <t>9,41</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -33748,17 +33748,17 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>23,703</t>
+          <t>23,658</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -33985,42 +33985,42 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>5,30912400</t>
+          <t>5,31178400</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>9,59</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>808,913</t>
+          <t>809,319</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -34242,12 +34242,12 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>24,64904300</t>
+          <t>24,64952800</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,153</t>
+          <t>0,001</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -34262,22 +34262,22 @@
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>13,58</t>
+          <t>13,54</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>96,438</t>
+          <t>96,440</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -34506,7 +34506,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>3,38988200</t>
+          <t>3,39156000</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -34516,12 +34516,12 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>9,42</t>
+          <t>9,47</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -34531,17 +34531,17 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>8.040,416</t>
+          <t>7.980,186</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -34767,22 +34767,22 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1.959,13587700</t>
+          <t>1.960,15881300</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>10,05</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -34792,17 +34792,17 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>16.976,273</t>
+          <t>16.975,823</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -35027,42 +35027,42 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>5,05804900</t>
+          <t>5,06052300</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>9,70</t>
+          <t>9,75</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>14,40</t>
+          <t>14,41</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.183,397</t>
+          <t>3.145,599</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -35287,7 +35287,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1,60638024</t>
+          <t>1,60719039</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -35297,32 +35297,32 @@
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,46</t>
+          <t>14,45</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>384,360</t>
+          <t>382,954</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -35531,42 +35531,42 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>5,31469000</t>
+          <t>5,31740300</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>9,83</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,51</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>296,659</t>
+          <t>296,811</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -35788,22 +35788,22 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>18,57711200</t>
+          <t>18,58633400</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -35813,17 +35813,17 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>4.870,304</t>
+          <t>4.871,184</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -36032,22 +36032,22 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>9,03140300</t>
+          <t>9,03593700</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>9,67</t>
+          <t>9,72</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -36057,17 +36057,17 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.884,411</t>
+          <t>3.884,468</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -36310,12 +36310,12 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -36536,7 +36536,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2,91889700</t>
+          <t>2,92023900</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -36546,12 +36546,12 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,80</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -36561,17 +36561,17 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>13.876,483</t>
+          <t>13.785,702</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -36797,42 +36797,42 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>4,59319600</t>
+          <t>4,59555100</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>9,80</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>16.795,835</t>
+          <t>16.847,630</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -37057,7 +37057,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1,42630200</t>
+          <t>1,42703600</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -37067,12 +37067,12 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>9,94</t>
+          <t>10,00</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -37082,17 +37082,17 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>3.452,476</t>
+          <t>3.449,010</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -37313,7 +37313,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1.837,74088300</t>
+          <t>1.838,67936500</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -37323,32 +37323,32 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>9,72</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,37</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>1.526,997</t>
+          <t>1.529,668</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -37573,22 +37573,22 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1,34712800</t>
+          <t>1,34767400</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,040</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>7,88</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -37598,17 +37598,17 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>33.408,141</t>
+          <t>33.582,487</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -37832,22 +37832,22 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>9,70635100</t>
+          <t>9,71058600</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>8,48</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -37857,17 +37857,17 @@
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>2.766,242</t>
+          <t>2.760,522</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -38091,7 +38091,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2,55608600</t>
+          <t>2,55721700</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -38101,12 +38101,12 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>8,47</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -38116,17 +38116,17 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>17.297,373</t>
+          <t>17.227,108</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -38352,42 +38352,42 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,65074900</t>
+          <t>4,65296900</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.853,871</t>
+          <t>11.863,527</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -38615,42 +38615,42 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,77422200</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>0,022</t>
+          <t>3,77190000</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>-0,061</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>1,20</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>8,04</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>12,34</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>1.658,500</t>
+          <t>1.656,354</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -38878,42 +38878,42 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>2,48387000</t>
+          <t>2,48471100</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>7,88</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>12,06</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>3.310,702</t>
+          <t>3.309,824</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -39143,12 +39143,12 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>3,09488200</t>
+          <t>3,09494100</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,154</t>
+          <t>0,001</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -39158,12 +39158,12 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>9,74</t>
+          <t>9,75</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,34</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -39173,12 +39173,12 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -39399,42 +39399,42 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1.697,53868000</t>
+          <t>1.698,37465500</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>8,21</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,48</t>
+          <t>12,51</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>450,089</t>
+          <t>450,311</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -39659,42 +39659,42 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>3,95570400</t>
+          <t>3,95673600</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,093</t>
+          <t>0,026</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>9,91</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,48</t>
+          <t>13,43</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>3.147,713</t>
+          <t>3.149,520</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -39922,42 +39922,42 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>5,33542800</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>0,243</t>
+          <t>5,32628500</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>-0,171</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>8,50</t>
+          <t>8,32</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>12,45</t>
+          <t>12,18</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>2.349,436</t>
+          <t>2.345,383</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -40184,12 +40184,12 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>5,38155400</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>0,145</t>
+          <t>5,38135800</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -40204,22 +40204,22 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>13,77</t>
+          <t>13,72</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>5.811,144</t>
+          <t>5.811,192</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -40446,42 +40446,42 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>4,92089600</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>0,085</t>
+          <t>4,91985500</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>-0,021</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>9,02</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>13,44</t>
+          <t>13,36</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>485,083</t>
+          <t>484,980</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -40708,42 +40708,42 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>8,23540100</t>
+          <t>8,23939400</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>14,27</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>165,498</t>
+          <t>168,540</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -40828,42 +40828,42 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>3,57040200</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>0,293</t>
+          <t>3,56133400</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>-0,253</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>7,01</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>11,24</t>
+          <t>10,86</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>693,527</t>
+          <t>691,766</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -41090,42 +41090,42 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>3,91221400</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>0,013</t>
+          <t>3,90844800</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>-0,096</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>11,75</t>
+          <t>11,67</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>635,239</t>
+          <t>634,628</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -41353,42 +41353,42 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>2,70474500</t>
+          <t>2,70611200</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,88</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>14,56</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>8.711,814</t>
+          <t>8.676,678</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -41617,22 +41617,22 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>7,43477400</t>
+          <t>7,43841700</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -41642,17 +41642,17 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>12.915,263</t>
+          <t>12.796,810</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -41882,7 +41882,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>7,76521800</t>
+          <t>7,76916100</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -41892,32 +41892,32 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>14,27</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>3.777,896</t>
+          <t>3.754,361</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -42142,22 +42142,22 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1,50545800</t>
+          <t>1,50567100</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>0,034</t>
+          <t>0,014</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,98</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
@@ -42167,17 +42167,17 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>163,596</t>
+          <t>163,620</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -42398,22 +42398,22 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,24776300</t>
+          <t>3,24931600</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>9,15</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -42423,17 +42423,17 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>1.922,988</t>
+          <t>1.963,678</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -42686,12 +42686,12 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -42942,12 +42942,12 @@
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -43198,12 +43198,12 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -43454,12 +43454,12 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -43702,12 +43702,12 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -43958,12 +43958,12 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -44184,22 +44184,22 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>6,97260800</t>
+          <t>6,97620700</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
@@ -44209,17 +44209,17 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>22.509,990</t>
+          <t>22.470,593</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -44304,42 +44304,42 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>5,72028500</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>0,259</t>
+          <t>5,71015000</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>-0,177</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>8,83</t>
+          <t>8,63</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>12,90</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>592,718</t>
+          <t>591,668</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -44595,12 +44595,12 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -44817,42 +44817,42 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>4,19072900</t>
+          <t>4,15331400</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>-0,553</t>
+          <t>-0,892</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>4,42</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>15,74</t>
+          <t>14,71</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>30,08</t>
+          <t>29,71</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>307,345</t>
+          <t>304,427</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -45077,42 +45077,42 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>3,84698200</t>
+          <t>3,81264900</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>-0,547</t>
+          <t>-0,892</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>15,38</t>
+          <t>14,35</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>29,42</t>
+          <t>29,05</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>8,019</t>
+          <t>7,947</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -45337,42 +45337,42 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>11,72314035</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>1,468</t>
+          <t>11,70310690</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>-0,170</t>
         </is>
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,59</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>2.343,957</t>
+          <t>2.339,909</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -45597,42 +45597,42 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>2,13468400</t>
+          <t>2,11474200</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>-0,633</t>
+          <t>-0,934</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>12,62</t>
+          <t>11,57</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>24,21</t>
+          <t>23,75</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>208,593</t>
+          <t>206,644</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -45853,42 +45853,42 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>2,08861000</t>
+          <t>2,06297000</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>-0,734</t>
+          <t>-1,227</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr">
-        <is>
-          <t>0,74</t>
+          <t>5,73</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>12,48</t>
+          <t>11,38</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>759,533</t>
+          <t>750,210</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -46113,42 +46113,42 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>3,65120105</t>
+          <t>3,62201562</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>-0,765</t>
+          <t>-0,799</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>12,23</t>
+          <t>11,33</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>22,50</t>
+          <t>22,09</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>1.383,960</t>
+          <t>1.372,897</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -46365,42 +46365,42 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>2,64009430</t>
+          <t>2,61535836</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>-0,644</t>
+          <t>-0,936</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>10,65</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>22,47</t>
+          <t>22,00</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>807,051</t>
+          <t>799,490</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -46617,22 +46617,22 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>3,89109900</t>
+          <t>3,89305800</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,64</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
@@ -46642,17 +46642,17 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>4.513,780</t>
+          <t>4.617,418</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -94,10 +94,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +814,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,33218200</t>
+          <t>2,33425100</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -824,32 +824,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>8,63</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>12,57</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>401,104</t>
+          <t>401,927</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,66501600</t>
+          <t>5,67000100</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.596,357</t>
+          <t>6.567,062</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,86035100</t>
+          <t>2,86286700</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1344,32 +1344,32 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>12,34</t>
+          <t>12,33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>828,000</t>
+          <t>769,941</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1593,42 +1593,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>20,54322600</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>-0,072</t>
+          <t>20,55711200</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0,188</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,20</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,76</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>115,598</t>
+          <t>115,524</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1857,42 +1857,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,10499500</t>
+          <t>3,10826200</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>9,98</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1.713,020</t>
+          <t>1.711,581</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2113,42 +2113,42 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.902,53720000</t>
+          <t>1.904,53022900</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>9,90</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,40</t>
+          <t>14,37</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>98,041</t>
+          <t>98,171</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,47162100</t>
+          <t>3,47503700</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>9,60</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>13,98</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>64,825</t>
+          <t>64,746</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2877,42 +2877,42 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,01781000</t>
+          <t>10,02704900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>8,90</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>13,11</t>
+          <t>13,08</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>590,180</t>
+          <t>590,549</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3253,42 +3253,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,92462900</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>13,93206900</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0,091</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>8,28</t>
+          <t>8,34</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>11,57</t>
+          <t>11,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,921</t>
+          <t>27,929</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3517,42 +3517,42 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>3,60756600</t>
+          <t>3,61117700</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>14,07</t>
+          <t>14,05</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>120,845</t>
+          <t>120,573</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -3780,42 +3780,42 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,44647300</t>
+          <t>3,44992000</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>13,81</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,305</t>
+          <t>12,303</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>20,84697300</t>
+          <t>20,86617300</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>8,69</t>
+          <t>8,79</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>59,470</t>
+          <t>59,444</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4300,42 +4300,42 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>47,63972900</t>
+          <t>47,68354200</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>8,87</t>
+          <t>8,97</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>13,07</t>
+          <t>13,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,455</t>
+          <t>41,470</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4561,42 +4561,42 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,25433100</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>3,25630000</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0,093</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>12,62</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>77,266</t>
+          <t>77,291</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15,43688600</t>
+          <t>15,45118400</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -4835,32 +4835,32 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>9,04</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>13,14</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,045</t>
+          <t>28,064</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5085,42 +5085,42 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,09333100</t>
+          <t>3,09610700</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>8,65</t>
+          <t>8,75</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>12,74</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1,659</t>
+          <t>1,661</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -5341,42 +5341,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,14869200</t>
+          <t>3,15198400</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1.789,552</t>
+          <t>1.792,467</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5595,42 +5595,42 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,43260100</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>-0,063</t>
+          <t>3,43521400</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0,182</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>7,70</t>
+          <t>7,78</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>11,82</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>125,252</t>
+          <t>125,050</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33,87895200</t>
+          <t>33,91124800</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>9,20</t>
+          <t>9,30</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>13,55</t>
+          <t>13,52</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2.232,268</t>
+          <t>2.229,079</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3,41545800</t>
+          <t>3,41871700</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6129,32 +6129,32 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>9,21</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>13,56</t>
+          <t>13,54</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12,980</t>
+          <t>12,985</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -6384,42 +6384,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,44723100</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>-0,179</t>
+          <t>3,44686200</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>0,208</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>11,92</t>
+          <t>11,43</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64,491</t>
+          <t>64,478</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>19,68728500</t>
+          <t>19,70678500</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6654,32 +6654,32 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>9,55</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>13,92</t>
+          <t>13,91</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>967,549</t>
+          <t>968,306</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -6904,42 +6904,42 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,28559300</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+          <t>1,28677300</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>9,86</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>14,28</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,224</t>
+          <t>75,299</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -7156,42 +7156,42 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,15433338</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+          <t>1,14907813</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>7,01</t>
+          <t>6,52</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>198,552</t>
+          <t>196,711</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,21475000</t>
+          <t>1,21587700</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -7422,32 +7422,32 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>13,85</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,074</t>
+          <t>63,880</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7664,22 +7664,22 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,10389587</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+          <t>1,10226800</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>-0,11</t>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -7689,17 +7689,17 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>306,872</t>
+          <t>305,539</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -7916,42 +7916,42 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,31612800</t>
+          <t>1,31753300</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>10,14</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>14,79</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>481,004</t>
+          <t>482,599</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8176,42 +8176,42 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.899,19447500</t>
+          <t>1.901,19264000</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>9,90</t>
+          <t>10,01</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>14,60</t>
+          <t>14,58</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>182,434</t>
+          <t>182,513</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -8436,42 +8436,42 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,24447000</t>
+          <t>1,24691200</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,032</t>
+          <t>0,076</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>10,73</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>14,42</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,356</t>
+          <t>41,437</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8696,42 +8696,42 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>5,12418800</t>
+          <t>5,12956000</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,50</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.475,740</t>
+          <t>3.486,877</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9204,42 +9204,42 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>5,71695500</t>
+          <t>5,72268100</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,61</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>570,272</t>
+          <t>570,763</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -9465,42 +9465,42 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10,97300200</t>
+          <t>10,98425200</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>9,88</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>14,40</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2.436,530</t>
+          <t>2.435,921</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1,07581400</t>
+          <t>1,07687300</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>9,71</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -9750,17 +9750,17 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>22,467</t>
+          <t>22,484</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -9973,42 +9973,42 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5,32546800</t>
+          <t>5,33088300</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,54</t>
+          <t>14,52</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>856,407</t>
+          <t>856,768</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>30,18844200</t>
+          <t>30,21657000</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10243,32 +10243,32 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>28,65</t>
+          <t>28,64</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>21,585</t>
+          <t>21,593</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3,33780900</t>
+          <t>3,34128500</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -10491,32 +10491,32 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>14,48</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>666,689</t>
+          <t>671,994</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -10741,42 +10741,42 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.829,49055600</t>
+          <t>1.831,23161700</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>8,61</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>12,89</t>
+          <t>12,78</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>117,451</t>
+          <t>117,961</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>31,68869700</t>
+          <t>31,72072400</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -11007,32 +11007,32 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>9,63</t>
+          <t>9,74</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>14,21</t>
+          <t>14,19</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3.140,856</t>
+          <t>3.142,015</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>6,40264400</t>
+          <t>6,40900200</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>13,94</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>122,108</t>
+          <t>122,215</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -11514,42 +11514,42 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3,69952300</t>
+          <t>3,70346000</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>14,75</t>
+          <t>14,73</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16.782,873</t>
+          <t>16.793,630</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -11778,42 +11778,42 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>5,50064300</t>
+          <t>5,50648900</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>10,10</t>
+          <t>10,22</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>14,91</t>
+          <t>14,88</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>1.517,634</t>
+          <t>1.572,083</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>31,29678600</t>
+          <t>31,32562800</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -12049,12 +12049,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>8,86</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -12064,17 +12064,17 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>168,198</t>
+          <t>168,391</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -12555,42 +12555,42 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3,73119800</t>
+          <t>3,73496800</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>14,07</t>
+          <t>14,06</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2.313,577</t>
+          <t>2.314,164</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2,89705500</t>
+          <t>2,89967100</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -12829,32 +12829,32 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>8,65</t>
+          <t>8,74</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>12,74</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>6.048,078</t>
+          <t>6.027,682</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -13079,42 +13079,42 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1,33645900</t>
+          <t>1,33783200</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>9,88</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>14,41</t>
+          <t>14,40</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>74,272</t>
+          <t>75,262</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -13339,42 +13339,42 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>3,30305000</t>
+          <t>3,30653100</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>10,08</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>14,69</t>
+          <t>14,68</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>14.722,167</t>
+          <t>14.734,469</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -13599,42 +13599,42 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10,02667100</t>
+          <t>10,03687600</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>14,17</t>
+          <t>14,16</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>823,813</t>
+          <t>824,286</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4,61303100</t>
+          <t>4,61771200</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -13874,32 +13874,32 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>17.105,001</t>
+          <t>17.122,420</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -14124,42 +14124,42 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>5,28625400</t>
+          <t>5,29174000</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23.423,422</t>
+          <t>23.462,932</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -14384,42 +14384,42 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4,94681300</t>
+          <t>4,95196700</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,51</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>9.903,384</t>
+          <t>9.882,102</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.789,44126200</t>
+          <t>1.791,21363500</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -14658,12 +14658,12 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>9,42</t>
+          <t>9,53</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -14673,17 +14673,17 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>293,174</t>
+          <t>288,891</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -14768,42 +14768,42 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1,46674300</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>-0,007</t>
+          <t>1,46817500</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>14,05</t>
+          <t>14,02</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>65,615</t>
+          <t>65,651</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -15020,12 +15020,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>13,15674200</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>-0,160</t>
+          <t>13,15587100</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>-0,127</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -15035,12 +15035,12 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,82</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>17,99</t>
+          <t>17,43</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -15050,12 +15050,12 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -15284,42 +15284,42 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.692,57819400</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>-0,006</t>
+          <t>1.690,07637600</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-0,040</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>12,43</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>112,028</t>
+          <t>111,721</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -15540,42 +15540,42 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.513,43300800</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>-0,291</t>
+          <t>2.513,28638200</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>-0,039</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>22,36</t>
+          <t>22,35</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>26,72</t>
+          <t>25,32</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14,306</t>
+          <t>14,349</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -16048,22 +16048,22 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,28627000</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
+          <t>1,28832900</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>-0,005</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -16073,17 +16073,17 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4,986</t>
+          <t>4,994</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -16304,42 +16304,42 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1,16195100</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>-1,085</t>
+          <t>1,16704600</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>-0,160</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>12,77</t>
+          <t>11,24</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>3,462</t>
+          <t>3,478</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -16590,12 +16590,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -16812,42 +16812,42 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1,43116300</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>-0,019</t>
+          <t>1,42471000</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>11,470</t>
+          <t>11,418</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -17098,12 +17098,12 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -17320,42 +17320,42 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1,12841700</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>0,041</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>-1,10</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-6,41</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>-3,54</t>
+          <t>1,12290500</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-0,434</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>-1,58</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>-6,86</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>-4,12</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>3,279</t>
+          <t>3,242</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -17576,42 +17576,42 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>5,53792979</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>5,53689606</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>7,92</t>
+          <t>7,90</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>12,43</t>
+          <t>12,21</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>32,727</t>
+          <t>32,241</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -17836,42 +17836,42 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1.249,58233100</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
+          <t>1.247,75718900</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>-3,02</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-0,41</t>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>37,514</t>
+          <t>37,455</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -18106,42 +18106,42 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>4,61471200</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>-1,147</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>-2,47</t>
+          <t>4,65572200</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>1,297</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>25,07</t>
+          <t>24,88</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>527,189</t>
+          <t>530,679</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -18366,42 +18366,42 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2,94048700</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>-0,011</t>
+          <t>2,93097400</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>8,37</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>68,838</t>
+          <t>68,397</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -18622,42 +18622,42 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1.696,09383200</t>
+          <t>1.700,95367400</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,449</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>-1,16</t>
+          <t>0,400</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>7,96</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,51</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>30,339</t>
+          <t>30,419</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -18882,42 +18882,42 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>3,94368900</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>-0,417</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>-0,58</t>
+          <t>3,91242700</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>-0,382</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>17,23</t>
+          <t>16,30</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>26,00</t>
+          <t>24,47</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2.436,015</t>
+          <t>2.416,356</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -19142,42 +19142,42 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1,96651800</t>
+          <t>1,96819000</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0,032</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>8,17</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>12,22</t>
+          <t>12,11</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20,327</t>
+          <t>20,321</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -19402,42 +19402,42 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1.718,63270100</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1.716,24330400</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>-0,036</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>8,52</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>13,40</t>
+          <t>13,02</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>14,924</t>
+          <t>15,004</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -19658,42 +19658,42 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>5,82790900</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>-0,014</t>
+          <t>5,82529100</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>-0,016</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>9,33</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>14,11</t>
+          <t>13,86</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>903,057</t>
+          <t>902,563</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -19918,22 +19918,22 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0,56803087</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
+          <t>0,55782040</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>-2,50</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>-21,33</t>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>-4,25</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>-22,74</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -19943,17 +19943,17 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>11,561</t>
+          <t>11,364</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -20185,42 +20185,42 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3,77235300</t>
+          <t>3,77567100</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>0,033</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>8,45</t>
+          <t>8,55</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>12,63</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>711,082</t>
+          <t>708,030</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -20441,42 +20441,42 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,41292000</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>-0,003</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>-1,08</t>
+          <t>1,41138600</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>0,068</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>72,405</t>
+          <t>72,326</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -20709,42 +20709,42 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1,53035500</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1,53298000</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>0,066</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>6,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>11,57</t>
+          <t>11,44</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>109,917</t>
+          <t>84,952</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -20977,42 +20977,42 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,38354800</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>-0,005</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>-0,15</t>
+          <t>3,39639100</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>0,166</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>0,22</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>6,60</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>8,70</t>
+          <t>8,85</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>161,153</t>
+          <t>161,765</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -21243,42 +21243,42 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1,60658500</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>-0,004</t>
+          <t>1,60789300</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>7,59</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>21,15</t>
+          <t>20,05</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>15,135</t>
+          <t>15,147</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -21509,17 +21509,17 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>6,93915600</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
+          <t>6,93886900</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -21529,22 +21529,22 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>12,91</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>125,907</t>
+          <t>124,658</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -21765,42 +21765,42 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,84894200</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
+          <t>1,85088100</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>8,86</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>170,215</t>
+          <t>170,206</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -22021,42 +22021,42 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1,43802000</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
+          <t>1,43242400</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>-0,003</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>-0,91</t>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>9,41</t>
+          <t>8,65</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>278,212</t>
+          <t>277,136</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -22282,42 +22282,42 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1,41093300</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
+          <t>1,41228500</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>-0,001</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>-0,51</t>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>8,92</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>12,550</t>
+          <t>12,496</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -22542,42 +22542,42 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3,88184500</t>
+          <t>3,88955200</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>0,388</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>-3,43</t>
+          <t>0,136</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>-3,24</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>97,528</t>
+          <t>97,709</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -22832,12 +22832,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -22922,42 +22922,42 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1,31239500</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>-0,750</t>
+          <t>1,30853800</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>-0,026</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>17,82</t>
+          <t>16,80</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>4,013</t>
+          <t>3,984</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -23178,17 +23178,17 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2,75083100</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>-0,889</t>
+          <t>2,75097600</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>-0,519</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>4,38</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -23198,22 +23198,22 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>29,06</t>
+          <t>27,50</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>13,515</t>
+          <t>13,504</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -23438,42 +23438,42 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1.990,62027100</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>-1,229</t>
+          <t>2.000,18428000</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>-0,059</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>5,79</t>
+          <t>6,30</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>12,63</t>
+          <t>11,34</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>9,622</t>
+          <t>9,688</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -23687,42 +23687,42 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>10,41728400</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>-0,172</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>-0,95</t>
+          <t>10,35270300</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>-0,209</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>5,20</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>13,69</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>270,206</t>
+          <t>268,130</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -23947,42 +23947,42 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1,41372600</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>-0,769</t>
+          <t>1,41528700</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>-0,151</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>-7,26</t>
-        </is>
-      </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>-5,19</t>
+          <t>2,60</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>-7,16</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>-6,55</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>412,031</t>
+          <t>408,851</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -24207,42 +24207,42 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1,07943000</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>-0,468</t>
+          <t>1,08647100</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>0,803</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>3,11</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>-7,26</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>-3,29</t>
+          <t>3,78</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>-6,65</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>-4,26</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>53,042</t>
+          <t>53,376</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -24467,42 +24467,42 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,77442600</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>-0,806</t>
+          <t>1,78854700</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>0,602</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>10,78</t>
+          <t>10,29</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>2,078</t>
+          <t>2,095</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -24727,42 +24727,42 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>5,41857600</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>-0,467</t>
+          <t>5,37636200</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>-4,140</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>7,55</t>
+          <t>6,71</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>72,06</t>
+          <t>70,72</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>70,06</t>
+          <t>66,71</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>88,510</t>
+          <t>87,792</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -24987,12 +24987,12 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>9,18862400</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>-0,893</t>
+          <t>9,18829000</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>-0,523</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -25007,22 +25007,22 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>27,71</t>
+          <t>26,17</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>91,837</t>
+          <t>91,831</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -25247,42 +25247,42 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,33215400</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>-0,122</t>
+          <t>1,32742400</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>-0,023</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>4,80</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>3,50</t>
+          <t>3,13</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>10,13</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>297,023</t>
+          <t>295,939</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -25507,42 +25507,42 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1,74088200</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>-2,074</t>
-        </is>
-      </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>-8,44</t>
-        </is>
-      </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>-4,91</t>
+          <t>1,75465400</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>-0,258</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>-7,71</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>-5,69</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>103,207</t>
+          <t>104,047</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -25767,42 +25767,42 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2,96164300</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>-0,180</t>
+          <t>2,97111700</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>-0,365</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>9,01</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>17,09</t>
+          <t>15,96</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>122,511</t>
+          <t>122,886</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -26027,42 +26027,42 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1,92759500</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>-1,226</t>
+          <t>1,93664400</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>-0,062</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>5,72</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>-0,51</t>
+          <t>6,22</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>11,34</t>
+          <t>10,07</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>49,656</t>
+          <t>49,830</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -26291,42 +26291,42 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>7,78839900</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>-0,159</t>
+          <t>7,74480000</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>-3,422</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>66,05</t>
+          <t>65,12</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>68,80</t>
+          <t>66,06</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>140,425</t>
+          <t>124,223</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -26551,42 +26551,42 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1.399,95804000</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>-1,646</t>
+          <t>1.436,99811300</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>3,024</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>44,233</t>
+          <t>44,955</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -26811,42 +26811,42 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>36,45112300</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>-3,476</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>-3,13</t>
+          <t>35,25070800</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>-2,147</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>-6,32</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>38,94</t>
+          <t>32,76</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>603,411</t>
+          <t>583,386</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -27071,42 +27071,42 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>3,09393700</t>
+          <t>3,17072600</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>1,205</t>
+          <t>1,925</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>3,70</t>
+          <t>6,27</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>27,72</t>
+          <t>30,89</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>55,27</t>
+          <t>57,55</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>510,286</t>
+          <t>522,778</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -27335,42 +27335,42 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,05284700</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>-1,068</t>
+          <t>5,04480200</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>-0,749</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>12,59</t>
+          <t>12,41</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>26,18</t>
+          <t>24,64</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>24,035</t>
+          <t>23,963</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -27595,42 +27595,42 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1.638,10793100</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>-0,607</t>
+          <t>1.650,07655600</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>0,735</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>12,56</t>
+          <t>13,38</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>24,74</t>
+          <t>24,26</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>32,254</t>
+          <t>32,499</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -27855,42 +27855,42 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2,01115200</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>-1,245</t>
+          <t>2,01558800</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>-0,115</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>3,50</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>-1,14</t>
+          <t>3,73</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>-0,92</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>6,56</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>1,765</t>
+          <t>1,789</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -28107,42 +28107,42 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>6,25450000</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>-0,840</t>
+          <t>6,24510200</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>-0,673</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>4,50</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>16,26</t>
+          <t>16,09</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>31,36</t>
+          <t>29,56</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>45,247</t>
+          <t>45,160</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -28359,42 +28359,42 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2,31709900</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>-1,061</t>
+          <t>2,31305700</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>-0,383</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>10,24</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>23,34</t>
+          <t>21,82</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>35,141</t>
+          <t>34,984</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -28619,42 +28619,42 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>50,26838600</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>-0,466</t>
+          <t>49,87978300</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>-4,132</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>7,55</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>72,18</t>
+          <t>70,85</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>70,21</t>
+          <t>66,87</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>953,701</t>
+          <t>944,329</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -28879,42 +28879,42 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,52931300</t>
+          <t>1,56725000</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>1,205</t>
+          <t>1,925</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>27,71</t>
+          <t>30,88</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>55,22</t>
+          <t>57,50</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>20,072</t>
+          <t>20,570</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -29139,42 +29139,42 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1,86454500</t>
+          <t>1,86988500</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>0,489</t>
+          <t>0,524</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>8,77</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>52,95</t>
+          <t>48,09</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>278,405</t>
+          <t>277,484</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -29403,42 +29403,42 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>0,89771900</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>-1,520</t>
+          <t>0,90243600</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>0,245</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>-6,74</t>
-        </is>
-      </c>
-      <c r="H114" s="7" t="inlineStr">
-        <is>
-          <t>-9,99</t>
+          <t>2,57</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>-6,25</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>-10,66</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2,808</t>
+          <t>2,823</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -29659,42 +29659,42 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>7,10264600</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>-0,779</t>
+          <t>7,12582400</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>-0,254</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>11,98</t>
+          <t>12,35</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>24,20</t>
+          <t>23,68</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>342,117</t>
+          <t>343,203</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -29919,42 +29919,42 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1.055,69632900</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>1.051,30697500</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>7,23</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>18,72</t>
+          <t>16,79</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>8,483</t>
+          <t>8,478</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -30179,42 +30179,42 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1.561,60669700</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
+          <t>1.556,38505600</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>-0,002</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>12,16</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>22,289</t>
+          <t>22,214</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -30435,42 +30435,42 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>180,70455464</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>-0,888</t>
+          <t>180,74083972</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>-0,500</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>29,66</t>
+          <t>28,11</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>18,072</t>
+          <t>18,075</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -30695,42 +30695,42 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1,90270900</t>
+          <t>1,90814500</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>0,487</t>
+          <t>0,522</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>8,67</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>53,00</t>
+          <t>48,15</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>5,493</t>
+          <t>5,689</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -30952,42 +30952,42 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1,85820100</t>
+          <t>1,86357400</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>0,491</t>
+          <t>0,526</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>8,54</t>
+          <t>8,86</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>53,21</t>
+          <t>48,35</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>1.664,457</t>
+          <t>1.669,187</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -31205,42 +31205,42 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>55,98994900</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>-0,464</t>
+          <t>55,55685100</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>-4,133</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>72,87</t>
+          <t>71,53</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>71,14</t>
+          <t>67,77</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>783,790</t>
+          <t>777,668</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -31449,42 +31449,42 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>40,44681500</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>-3,478</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>-3,11</t>
+          <t>39,11821900</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>-2,142</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>-6,29</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>39,69</t>
+          <t>33,48</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>708,943</t>
+          <t>685,541</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -31693,42 +31693,42 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>17,04749700</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>-1,081</t>
+          <t>17,12628400</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>-0,153</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,47</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>14,50</t>
+          <t>12,92</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>112,977</t>
+          <t>113,505</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -31946,42 +31946,42 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>33,85620600</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>-3,462</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>-3,11</t>
+          <t>32,74634700</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>-2,137</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>-6,28</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>38,80</t>
+          <t>32,65</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>11,367</t>
+          <t>11,114</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -32195,42 +32195,42 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>49,42767500</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>-0,466</t>
+          <t>49,04356200</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>-4,139</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>72,40</t>
+          <t>71,06</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>70,45</t>
+          <t>67,09</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>678,457</t>
+          <t>672,393</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -32444,42 +32444,42 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>34,77711800</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>-3,475</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>-3,12</t>
+          <t>33,63256900</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>-2,146</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>-6,31</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>39,00</t>
+          <t>32,82</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>428,536</t>
+          <t>414,432</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -32688,42 +32688,42 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>52,57513800</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>-0,466</t>
+          <t>52,16756000</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>-4,133</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>72,65</t>
+          <t>71,31</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>70,79</t>
+          <t>67,42</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>770,377</t>
+          <t>764,239</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1,16177100</t>
+          <t>1,16282500</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -32946,32 +32946,32 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>8,68</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>12,69</t>
+          <t>12,68</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>66,276</t>
+          <t>65,734</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -33197,7 +33197,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1,40222200</t>
+          <t>1,40349800</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -33207,12 +33207,12 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>8,65</t>
+          <t>8,75</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -33222,17 +33222,17 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>215,509</t>
+          <t>235,464</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -33462,7 +33462,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>6,09665000</t>
+          <t>6,10259600</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -33472,32 +33472,32 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>9,29</t>
+          <t>9,40</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>13,70</t>
+          <t>13,69</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>43,000</t>
+          <t>43,083</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -33723,7 +33723,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,33444900</t>
+          <t>3,33777900</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -33733,12 +33733,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>9,41</t>
+          <t>9,52</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -33748,17 +33748,17 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>23,658</t>
+          <t>23,600</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -33985,22 +33985,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>5,31178400</t>
+          <t>5,31707300</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -34010,17 +34010,17 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>809,319</t>
+          <t>810,124</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -34242,42 +34242,42 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>24,64952800</t>
+          <t>24,66580500</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,001</t>
+          <t>0,096</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>10,17</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>13,54</t>
+          <t>13,40</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>96,440</t>
+          <t>96,503</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -34506,7 +34506,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>3,39156000</t>
+          <t>3,39491700</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -34516,32 +34516,32 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>13,99</t>
+          <t>13,98</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>7.980,186</t>
+          <t>7.997,626</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -34767,7 +34767,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1.960,15881300</t>
+          <t>1.962,24210100</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -34777,32 +34777,32 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>14,91</t>
+          <t>14,89</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>16.975,823</t>
+          <t>17.003,005</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -35027,42 +35027,42 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>5,06052300</t>
+          <t>5,06553900</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>9,75</t>
+          <t>9,86</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>14,41</t>
+          <t>14,38</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.145,599</t>
+          <t>3.198,527</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -35287,42 +35287,42 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1,60719039</t>
+          <t>1,60883589</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>9,90</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,45</t>
+          <t>14,44</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>382,954</t>
+          <t>382,365</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -35531,22 +35531,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>5,31740300</t>
+          <t>5,32283100</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -35556,17 +35556,17 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>296,811</t>
+          <t>297,114</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -35788,7 +35788,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>18,58633400</t>
+          <t>18,60505100</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -35798,32 +35798,32 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>14,46</t>
+          <t>14,44</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>4.871,184</t>
+          <t>4.880,152</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -36032,7 +36032,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>9,03593700</t>
+          <t>9,04503400</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -36042,32 +36042,32 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,83</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>14,38</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.884,468</t>
+          <t>3.862,160</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -36310,12 +36310,12 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -36536,7 +36536,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2,92023900</t>
+          <t>2,92292200</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -36546,32 +36546,32 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,50</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>8,80</t>
+          <t>8,90</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>12,98</t>
+          <t>12,97</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>13.785,702</t>
+          <t>13.703,520</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -36797,7 +36797,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>4,59555100</t>
+          <t>4,60027700</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -36807,12 +36807,12 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -36822,17 +36822,17 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>16.847,630</t>
+          <t>16.998,313</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -37057,7 +37057,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1,42703600</t>
+          <t>1,42852600</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -37067,32 +37067,32 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>14,78</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>3.449,010</t>
+          <t>3.419,589</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -37313,7 +37313,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1.838,67936500</t>
+          <t>1.840,55768200</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -37323,32 +37323,32 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,83</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>14,35</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>1.529,668</t>
+          <t>1.522,584</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -37573,22 +37573,22 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1,34767400</t>
+          <t>1,34878900</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>0,040</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>7,88</t>
+          <t>7,97</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -37598,17 +37598,17 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>33.582,487</t>
+          <t>33.733,571</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -37832,22 +37832,22 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>9,71058600</t>
+          <t>9,71923400</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>8,48</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -37857,17 +37857,17 @@
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>2.760,522</t>
+          <t>2.800,715</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -38091,7 +38091,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2,55721700</t>
+          <t>2,55950600</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -38101,12 +38101,12 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>8,47</t>
+          <t>8,57</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -38116,17 +38116,17 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>17.227,108</t>
+          <t>17.153,886</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -38352,42 +38352,42 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,65296900</t>
+          <t>4,65720500</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>14,20</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.863,527</t>
+          <t>11.893,191</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -38615,42 +38615,42 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,77190000</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>-0,061</t>
+          <t>3,77496200</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>0,185</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>8,04</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,34</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>1.656,354</t>
+          <t>1.658,382</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -38878,42 +38878,42 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>2,48471100</t>
+          <t>2,48641100</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>0,033</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>7,88</t>
+          <t>7,96</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>11,79</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>3.309,824</t>
+          <t>3.313,370</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -39143,42 +39143,42 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>3,09494100</t>
+          <t>3,09689800</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,001</t>
+          <t>0,096</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>9,75</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>13,19</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>37,537</t>
+          <t>37,561</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -39399,42 +39399,42 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1.698,37465500</t>
+          <t>1.699,88229400</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,51</t>
+          <t>12,30</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>450,311</t>
+          <t>450,710</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -39659,42 +39659,42 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>3,95673600</t>
+          <t>3,96149200</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,026</t>
+          <t>0,068</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>9,91</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,43</t>
+          <t>13,41</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>3.149,520</t>
+          <t>3.153,814</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -39922,12 +39922,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>5,32628500</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr">
-        <is>
-          <t>-0,171</t>
+          <t>5,32615700</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>0,219</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -39942,22 +39942,22 @@
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>12,18</t>
+          <t>11,67</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>2.345,383</t>
+          <t>2.345,907</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -40184,42 +40184,42 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>5,38135800</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>-0,003</t>
+          <t>5,38530500</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>0,098</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>10,31</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>13,72</t>
+          <t>13,59</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>5.811,192</t>
+          <t>5.814,707</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -40446,42 +40446,42 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>4,91985500</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>-0,021</t>
+          <t>4,92352700</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>0,116</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>9,08</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,16</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>484,980</t>
+          <t>485,342</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -40708,42 +40708,42 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>8,23939400</t>
+          <t>8,24743700</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>14,24</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>168,540</t>
+          <t>168,520</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -40828,42 +40828,42 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>3,56133400</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr">
-        <is>
-          <t>-0,253</t>
+          <t>3,55950200</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>0,285</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>10,86</t>
+          <t>10,07</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>691,766</t>
+          <t>691,410</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -41090,42 +41090,42 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>3,90844800</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>-0,096</t>
+          <t>3,91143400</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>0,229</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>11,19</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>634,628</t>
+          <t>635,112</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -41353,42 +41353,42 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>2,70611200</t>
+          <t>2,70891900</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>8.676,678</t>
+          <t>8.624,775</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -41617,42 +41617,42 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>7,43841700</t>
+          <t>7,44577300</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>9,71</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>14,31</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>12.796,810</t>
+          <t>12.594,775</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -41882,7 +41882,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>7,76916100</t>
+          <t>7,77705300</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -41892,32 +41892,32 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>9,77</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>14,26</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>3.754,361</t>
+          <t>3.756,251</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -42142,42 +42142,42 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1,50567100</t>
+          <t>1,50614200</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>0,014</t>
+          <t>0,069</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>12,30</t>
+          <t>12,04</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>163,620</t>
+          <t>163,671</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -42398,42 +42398,42 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,24931600</t>
+          <t>3,25245500</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>9,15</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>13,46</t>
+          <t>13,45</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>1.963,678</t>
+          <t>2.001,592</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -42686,12 +42686,12 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -42942,12 +42942,12 @@
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -43198,12 +43198,12 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -43454,12 +43454,12 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -43702,12 +43702,12 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -43958,12 +43958,12 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -44184,42 +44184,42 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>6,97620700</t>
+          <t>6,98353200</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,62</t>
+          <t>14,61</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>22.470,593</t>
+          <t>22.434,369</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -44304,17 +44304,17 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>5,71015000</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>-0,177</t>
+          <t>5,70982100</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>0,210</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -44324,22 +44324,22 @@
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>12,61</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>591,668</t>
+          <t>591,569</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -44595,12 +44595,12 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -44817,42 +44817,42 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>4,15331400</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>-0,892</t>
+          <t>4,15364700</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>-0,520</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,43</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>14,71</t>
+          <t>14,72</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>29,71</t>
+          <t>28,13</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>304,427</t>
+          <t>304,436</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -45077,42 +45077,42 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>3,81264900</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>-0,892</t>
+          <t>3,81761000</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>-0,393</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,50</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>29,05</t>
+          <t>27,74</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>7,947</t>
+          <t>7,957</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -45337,42 +45337,42 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>11,70310690</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>-0,170</t>
-        </is>
-      </c>
-      <c r="F177" s="6" t="inlineStr">
-        <is>
-          <t>-0,93</t>
+          <t>11,63079677</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>-0,207</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>14,59</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>2.339,909</t>
+          <t>2.324,576</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -45597,42 +45597,42 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>2,11474200</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>-0,934</t>
+          <t>2,11090100</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>-0,720</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>11,57</t>
+          <t>11,37</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>23,75</t>
+          <t>22,07</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>206,644</t>
+          <t>206,154</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -45853,42 +45853,42 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>2,06297000</t>
-        </is>
-      </c>
-      <c r="E179" s="6" t="inlineStr">
-        <is>
-          <t>-1,227</t>
+          <t>2,07266800</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>-0,062</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>5,73</t>
-        </is>
-      </c>
-      <c r="G179" s="6" t="inlineStr">
-        <is>
-          <t>-0,49</t>
+          <t>6,23</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>750,210</t>
+          <t>753,507</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -46113,42 +46113,42 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>3,62201562</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>-0,799</t>
+          <t>3,63608719</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>-0,234</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,32</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>11,33</t>
+          <t>11,76</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>22,09</t>
+          <t>21,18</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>1.372,897</t>
+          <t>1.378,231</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -46365,42 +46365,42 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>2,61535836</t>
-        </is>
-      </c>
-      <c r="E181" s="6" t="inlineStr">
-        <is>
-          <t>-0,936</t>
+          <t>2,62067199</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>-0,324</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>10,65</t>
+          <t>10,87</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>22,00</t>
+          <t>20,65</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>799,490</t>
+          <t>801,114</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -46617,42 +46617,42 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>3,89305800</t>
+          <t>3,89626300</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,19</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>4.617,418</t>
+          <t>4.627,515</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,33425100</t>
+          <t>2,33733400</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -824,32 +824,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>8,77</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,57</t>
+          <t>12,56</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>401,927</t>
+          <t>402,340</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1074,42 +1074,42 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,67000100</t>
+          <t>5,67738800</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>8,60</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>12,34</t>
+          <t>12,32</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.567,062</t>
+          <t>6.521,226</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,86286700</t>
+          <t>2,86659600</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1344,32 +1344,32 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>8,60</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>12,33</t>
+          <t>12,32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>769,941</t>
+          <t>758,324</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1593,42 +1593,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>20,55711200</t>
+          <t>20,67984600</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,188</t>
+          <t>0,326</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1,20</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>10,76</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>115,524</t>
+          <t>116,037</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1857,42 +1857,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,10826200</t>
+          <t>3,11317100</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,54</t>
+          <t>14,52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1.711,581</t>
+          <t>1.713,533</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2113,42 +2113,42 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.904,53022900</t>
+          <t>1.907,49119100</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>9,90</t>
+          <t>10,07</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,37</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>98,171</t>
+          <t>98,156</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,47503700</t>
+          <t>3,48006600</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>9,75</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>13,94</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>64,746</t>
+          <t>64,734</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,02704900</t>
+          <t>10,04063200</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2887,32 +2887,32 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>9,15</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>13,08</t>
+          <t>13,07</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>590,549</t>
+          <t>590,886</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3253,42 +3253,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,93206900</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>0,091</t>
+          <t>13,97258000</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>-0,045</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>8,34</t>
+          <t>8,65</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>11,41</t>
+          <t>11,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,929</t>
+          <t>28,022</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3517,42 +3517,42 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>3,61117700</t>
+          <t>3,61636800</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>14,05</t>
+          <t>14,04</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>120,573</t>
+          <t>119,928</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -3780,42 +3780,42 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,44992000</t>
+          <t>3,45506800</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>13,81</t>
+          <t>13,78</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,303</t>
+          <t>12,280</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4040,42 +4040,42 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>20,86617300</t>
+          <t>20,89453100</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>8,79</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>12,78</t>
+          <t>12,77</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>59,444</t>
+          <t>59,363</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>47,68354200</t>
+          <t>47,74794600</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -4310,32 +4310,32 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>8,97</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,470</t>
+          <t>41,526</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4561,42 +4561,42 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,25630000</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>0,093</t>
+          <t>3,26615300</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>-0,043</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>9,63</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>12,62</t>
+          <t>13,10</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>77,291</t>
+          <t>77,387</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15,45118400</t>
+          <t>15,47220700</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -4835,32 +4835,32 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>9,04</t>
+          <t>9,19</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>13,14</t>
+          <t>13,12</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,064</t>
+          <t>28,101</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,09610700</t>
+          <t>3,10018600</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -5095,32 +5095,32 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>12,72</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1,661</t>
+          <t>1,663</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -5341,42 +5341,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,15198400</t>
+          <t>3,15689500</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>14,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1.792,467</t>
+          <t>1.786,426</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5595,42 +5595,42 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,43521400</t>
+          <t>3,45358600</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,182</t>
+          <t>0,288</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>7,78</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>11,49</t>
+          <t>12,00</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>125,050</t>
+          <t>125,875</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -5859,42 +5859,42 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33,91124800</t>
+          <t>33,95876100</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>9,30</t>
+          <t>9,45</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>13,52</t>
+          <t>13,51</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2.229,079</t>
+          <t>2.212,758</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -6119,42 +6119,42 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3,41871700</t>
+          <t>3,42351300</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>13,54</t>
+          <t>13,52</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12,985</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -6384,42 +6384,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,44686200</t>
+          <t>3,46055500</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0,208</t>
+          <t>0,109</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>11,43</t>
+          <t>12,04</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64,478</t>
+          <t>64,649</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -6644,42 +6644,42 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>19,70678500</t>
+          <t>19,73480300</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>9,70</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>13,91</t>
+          <t>13,89</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>968,306</t>
+          <t>968,992</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,28677300</t>
+          <t>1,28881100</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -6914,32 +6914,32 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>14,26</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,299</t>
+          <t>75,246</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,14907813</t>
+          <t>1,15149435</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -7166,32 +7166,32 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>8,71</t>
+          <t>8,90</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>196,711</t>
+          <t>197,328</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -7412,42 +7412,42 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,21587700</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>1,21753700</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>9,64</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>13,82</t>
+          <t>13,77</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,880</t>
+          <t>63,583</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,10226800</t>
+          <t>1,10148539</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,59</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -7689,17 +7689,17 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>305,539</t>
+          <t>305,078</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -7916,42 +7916,42 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,31753300</t>
+          <t>1,31963300</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>10,14</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>482,599</t>
+          <t>481,517</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8176,42 +8176,42 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.901,19264000</t>
+          <t>1.904,19697800</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>10,01</t>
+          <t>10,19</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>14,58</t>
+          <t>14,56</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>182,513</t>
+          <t>183,555</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -8436,42 +8436,42 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,24691200</t>
+          <t>1,25038700</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,076</t>
+          <t>0,097</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>11,26</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>14,82</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,437</t>
+          <t>41,553</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8696,42 +8696,42 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>5,12956000</t>
+          <t>5,13758600</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>14,50</t>
+          <t>14,48</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.486,877</t>
+          <t>3.478,071</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9204,42 +9204,42 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>5,72268100</t>
+          <t>5,73098600</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>10,19</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,58</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>570,763</t>
+          <t>571,504</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -9465,42 +9465,42 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10,98425200</t>
+          <t>11,00044200</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>10,05</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>14,40</t>
+          <t>14,38</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2.435,921</t>
+          <t>2.437,798</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1,07687300</t>
+          <t>1,07860700</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>10,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -9750,17 +9750,17 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>22,484</t>
+          <t>22,521</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5,33088300</t>
+          <t>5,33903200</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -9983,32 +9983,32 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,50</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>856,768</t>
+          <t>858,021</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10233,42 +10233,42 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>30,21657000</t>
+          <t>30,25827700</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>8,96</t>
+          <t>9,11</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>28,64</t>
+          <t>28,62</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>21,593</t>
+          <t>21,622</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -10481,42 +10481,42 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3,34128500</t>
+          <t>3,34642900</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,48</t>
+          <t>14,47</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>671,994</t>
+          <t>675,645</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -10741,42 +10741,42 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.831,23161700</t>
+          <t>1.834,25415300</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,058</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>8,71</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>12,78</t>
+          <t>12,88</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>117,961</t>
+          <t>117,641</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -10997,42 +10997,42 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>31,72072400</t>
+          <t>31,76678300</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>9,74</t>
+          <t>9,90</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>14,18</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3.142,015</t>
+          <t>3.146,895</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -11253,42 +11253,42 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>6,40900200</t>
+          <t>6,41813900</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>13,94</t>
+          <t>13,92</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>122,215</t>
+          <t>122,358</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -11514,42 +11514,42 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3,70346000</t>
+          <t>3,70934200</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>10,29</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>14,73</t>
+          <t>14,70</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16.793,630</t>
+          <t>16.791,715</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -11778,42 +11778,42 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>5,50648900</t>
+          <t>5,51539400</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>10,40</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>14,88</t>
+          <t>14,87</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>1.572,083</t>
+          <t>1.573,555</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -12039,42 +12039,42 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>31,32562800</t>
+          <t>31,36822800</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>9,01</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>12,90</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>168,391</t>
+          <t>168,603</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -12555,42 +12555,42 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3,73496800</t>
+          <t>3,74051500</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>14,06</t>
+          <t>14,04</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2.314,164</t>
+          <t>2.314,123</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12819,42 +12819,42 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2,89967100</t>
+          <t>2,90352900</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>12,73</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>6.027,682</t>
+          <t>6.009,614</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -13069,52 +13069,52 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC OMEGA REF DI RF LONGO PRAZO</t>
+          <t>CAIXA FIC FIF TOP PRIVATE RF REF DI LP RESP LTDA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>13/05/2024</t>
+          <t>05/05/2014</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1,33783200</t>
+          <t>3,31165800</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>14,40</t>
+          <t>14,66</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>75,262</t>
+          <t>14.760,606</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -13134,22 +13134,22 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>PF | RPPS</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-omega-ref-di-longo-prazo/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-top-private-ref-di-longo-prazo/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>55.036.101/0001-04</t>
+          <t>19.769.018/0001-80</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>OUTROS</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>RF REF DI 100% TPF</t>
+          <t>RF DI até 49% Crédito Privado</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
@@ -13275,51 +13275,51 @@
       </c>
       <c r="AR50" s="2" t="inlineStr">
         <is>
-          <t>CAIXA ÔMEGA PRIVATE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RF REF DI LONGO PRAZO - RESP LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS50" s="2" t="inlineStr">
-        <is>
-          <t>A movimentação do fundo é feita exclusivamente pela plataforma.caixa ou IBC/APP.</t>
-        </is>
-      </c>
+          <t>CAIXA TOP PRIVATE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS50" s="2" t="inlineStr"/>
       <c r="AT50" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7914.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5969.pdf</t>
         </is>
       </c>
       <c r="AU50" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7914.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5969.pdf</t>
         </is>
       </c>
       <c r="AV50" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7914.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5969.pdf</t>
         </is>
       </c>
       <c r="AW50" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7914.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5969.pdf</t>
         </is>
       </c>
       <c r="AX50" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7914.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5969.pdf</t>
         </is>
       </c>
       <c r="AY50" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7914.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5969.pdf</t>
         </is>
       </c>
       <c r="AZ50" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7914.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5969.pdf</t>
         </is>
       </c>
       <c r="BA50" s="2" t="inlineStr"/>
-      <c r="BB50" s="2" t="inlineStr"/>
+      <c r="BB50" s="2" t="inlineStr">
+        <is>
+          <t>https://web.microsoftstream.com/video/5f0c9eff-f752-448b-8f0a-3e2fff710aa9?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -13329,52 +13329,52 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF TOP PRIVATE RF REF DI LP RESP LTDA</t>
+          <t>CAIXA SIGMA PRIVATE FIC FIF REF DI RF LONGO PRAZO</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>05/05/2014</t>
+          <t>13/05/2024</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>3,30653100</t>
+          <t>1,33986300</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>14,68</t>
+          <t>14,39</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>14.734,469</t>
+          <t>75,465</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -13394,22 +13394,22 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>PF | RPPS</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-top-private-ref-di-longo-prazo/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/referenciados/fic-sigma-ref-di-longo-prazo</t>
         </is>
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>19.769.018/0001-80</t>
+          <t>10.731.794/0001-17</t>
         </is>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="S51" s="4" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="T51" s="4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="U51" s="4" t="inlineStr">
         <is>
-          <t>10000.0</t>
+          <t>50000.0</t>
         </is>
       </c>
       <c r="V51" s="4" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="X51" s="4" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="Y51" s="4" t="inlineStr">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="AC51" s="4" t="inlineStr">
         <is>
-          <t>RF DI até 49% Crédito Privado</t>
+          <t>RF REF DI 100% TPF</t>
         </is>
       </c>
       <c r="AD51" s="4" t="inlineStr">
@@ -13509,12 +13509,12 @@
       </c>
       <c r="AL51" s="4" t="inlineStr">
         <is>
-          <t>["Private"]</t>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
         </is>
       </c>
       <c r="AM51" s="4" t="inlineStr">
         <is>
-          <t>["Private"]</t>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
         </is>
       </c>
       <c r="AN51" s="4" t="inlineStr">
@@ -13535,49 +13535,49 @@
       </c>
       <c r="AR51" s="4" t="inlineStr">
         <is>
-          <t>CAIXA TOP PRIVATE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA SIGMA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
         </is>
       </c>
       <c r="AS51" s="4" t="inlineStr"/>
       <c r="AT51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5969.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5171.pdf</t>
         </is>
       </c>
       <c r="AU51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5969.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5171.pdf</t>
         </is>
       </c>
       <c r="AV51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5969.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5171.pdf</t>
         </is>
       </c>
       <c r="AW51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5969.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5171.pdf</t>
         </is>
       </c>
       <c r="AX51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5969.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5171.pdf</t>
         </is>
       </c>
       <c r="AY51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5969.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5171.pdf</t>
         </is>
       </c>
       <c r="AZ51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5969.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5171.pdf</t>
         </is>
       </c>
       <c r="BA51" s="4" t="inlineStr"/>
       <c r="BB51" s="4" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/5f0c9eff-f752-448b-8f0a-3e2fff710aa9?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/4be15710-4acb-4afd-a959-c6ed0d090cac?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -13599,42 +13599,42 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10,03687600</t>
+          <t>10,05189400</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>14,16</t>
+          <t>14,15</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>824,286</t>
+          <t>824,591</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF SIGMA RF REF DI LP RESP LTDA</t>
+          <t>CAIXA SIGMA SINGULAR FIC FIF RF REF DI LP RESP LTDA</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -13864,42 +13864,42 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4,61771200</t>
+          <t>4,62463700</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>17.122,420</t>
+          <t>17.214,622</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-sigma-ref-di-longo-prazo</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/referenciados/fic-sigma-ref-di-longo-prazo</t>
         </is>
       </c>
       <c r="Q53" s="4" t="inlineStr">
@@ -14124,42 +14124,42 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>5,29174000</t>
+          <t>5,29989700</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>9,99</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23.462,932</t>
+          <t>23.477,728</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4,95196700</t>
+          <t>4,95955500</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14394,32 +14394,32 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>14,49</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>9.882,102</t>
+          <t>9.862,317</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -14648,42 +14648,42 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.791,21363500</t>
+          <t>1.793,84459100</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>9,53</t>
+          <t>9,69</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>13,91</t>
+          <t>13,89</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>288,891</t>
+          <t>288,250</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1,46817500</t>
+          <t>1,47014100</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -14778,32 +14778,32 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>9,80</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>14,02</t>
+          <t>13,98</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>65,651</t>
+          <t>65,714</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -15020,27 +15020,27 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>13,15587100</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>-0,127</t>
+          <t>13,21516200</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>0,354</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>10,82</t>
+          <t>11,32</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>17,43</t>
+          <t>17,52</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -15050,12 +15050,12 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -15284,42 +15284,42 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.690,07637600</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-0,040</t>
+          <t>1.700,90036100</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>0,341</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>12,05</t>
+          <t>12,66</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>111,721</t>
+          <t>112,348</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -15540,42 +15540,42 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.513,28638200</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>-0,039</t>
+          <t>2.544,59698700</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>0,834</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>2,60</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>22,35</t>
+          <t>23,88</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>25,32</t>
+          <t>26,98</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14,349</t>
+          <t>14,556</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,28832900</t>
+          <t>1,28835200</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -16078,12 +16078,12 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -16304,42 +16304,42 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1,16704600</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>-0,160</t>
+          <t>1,17572600</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>1,913</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>1,40</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>11,24</t>
+          <t>11,27</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>3,478</t>
+          <t>3,504</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -16590,12 +16590,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1,42471000</t>
+          <t>1,43073600</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -16822,32 +16822,32 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>4,81</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>11,418</t>
+          <t>11,469</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -17098,12 +17098,12 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -17320,42 +17320,42 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1,12290500</t>
+          <t>1,11078700</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>-0,434</t>
+          <t>-0,918</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-2,65</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>-6,86</t>
+          <t>-7,87</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>-4,12</t>
+          <t>-4,57</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>3,242</t>
+          <t>3,193</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -17576,42 +17576,42 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>5,53689606</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>-0,004</t>
+          <t>5,56658248</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>0,296</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>7,90</t>
+          <t>8,48</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>12,21</t>
+          <t>12,67</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>32,241</t>
+          <t>32,460</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1.247,75718900</t>
+          <t>1.248,65466700</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -17846,32 +17846,32 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-3,09</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>37,455</t>
+          <t>37,478</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -18106,42 +18106,42 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>4,65572200</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>1,297</t>
+          <t>4,65613500</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>-0,924</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>-1,61</t>
+          <t>-1,60</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>24,88</t>
+          <t>25,34</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>530,679</t>
+          <t>527,279</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2,93097400</t>
+          <t>2,94258100</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -18376,32 +18376,32 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>68,397</t>
+          <t>68,476</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -18622,42 +18622,42 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1.700,95367400</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>0,400</t>
+          <t>1.686,71474800</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>-0,734</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-1,70</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>11,51</t>
+          <t>10,62</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>30,419</t>
+          <t>30,196</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -18882,42 +18882,42 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>3,91242700</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>-0,382</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>-1,36</t>
+          <t>4,02500300</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>1,595</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>16,30</t>
+          <t>19,65</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>24,47</t>
+          <t>26,91</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2.416,356</t>
+          <t>2.481,620</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -19142,27 +19142,27 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1,96819000</t>
+          <t>1,97197000</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,079</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>8,47</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>12,11</t>
+          <t>12,24</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -19172,12 +19172,12 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -19402,42 +19402,42 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1.716,24330400</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>-0,036</t>
+          <t>1.727,36390800</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>0,343</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>1,10</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>8,52</t>
+          <t>9,22</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>13,02</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>15,004</t>
+          <t>15,104</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -19658,42 +19658,42 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>5,82529100</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>-0,016</t>
+          <t>5,85477100</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>0,257</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>9,88</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>13,86</t>
+          <t>14,27</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>902,563</t>
+          <t>906,740</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0,55782040</t>
+          <t>0,59781227</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -19926,14 +19926,14 @@
           <t>-0,003</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>-4,25</t>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>2,60</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>-22,74</t>
+          <t>-17,21</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -19943,17 +19943,17 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>11,364</t>
+          <t>12,174</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -20185,42 +20185,42 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3,77567100</t>
+          <t>3,78309100</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,081</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>8,76</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>12,53</t>
+          <t>12,65</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>708,030</t>
+          <t>708,317</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -20441,42 +20441,42 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,41138600</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>0,068</t>
+          <t>1,40979900</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>-0,059</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,30</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>6,57</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>72,326</t>
+          <t>72,245</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -20709,42 +20709,42 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1,53298000</t>
+          <t>1,53534700</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>0,066</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>6,00</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>11,13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>84,952</t>
+          <t>85,084</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -20977,42 +20977,42 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,39639100</t>
+          <t>3,40629900</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,166</t>
+          <t>0,067</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>6,60</t>
+          <t>6,91</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>161,765</t>
+          <t>162,237</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -21243,42 +21243,42 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1,60789300</t>
+          <t>1,61585900</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,252</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>8,21</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>20,05</t>
+          <t>19,45</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>15,147</t>
+          <t>15,222</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>6,93886900</t>
+          <t>6,96088500</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -21519,32 +21519,32 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>8,23</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>12,91</t>
+          <t>12,99</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>124,658</t>
+          <t>124,933</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,85088100</t>
+          <t>1,85455700</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -21775,32 +21775,32 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>170,206</t>
+          <t>169,235</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1,43242400</t>
+          <t>1,43493300</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -22031,32 +22031,32 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>8,65</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>277,136</t>
+          <t>277,542</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1,41228500</t>
+          <t>1,40820100</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -22292,32 +22292,32 @@
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,70</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>8,92</t>
+          <t>8,17</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>12,496</t>
+          <t>12,434</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -22542,42 +22542,42 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3,88955200</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>0,136</t>
+          <t>3,85229400</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>-0,743</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>-3,24</t>
+          <t>-4,16</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>97,709</t>
+          <t>96,735</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -22832,12 +22832,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -22922,42 +22922,42 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1,30853800</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>-0,026</t>
+          <t>1,33172600</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>1,625</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>16,80</t>
+          <t>17,92</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>3,984</t>
+          <t>4,054</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -23178,42 +23178,42 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2,75097600</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>-0,519</t>
+          <t>2,76566400</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>0,710</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>14,94</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>27,50</t>
+          <t>26,63</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>13,504</t>
+          <t>13,589</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -23438,42 +23438,42 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2.000,18428000</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>-0,059</t>
+          <t>2.018,70178700</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>2,147</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>6,30</t>
+          <t>7,28</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>11,34</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>9,688</t>
+          <t>9,764</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -23687,42 +23687,42 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>10,35270300</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>-0,209</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>-1,56</t>
+          <t>10,65106700</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>1,285</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>1,26</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>14,51</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>268,130</t>
+          <t>274,676</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -23947,42 +23947,42 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1,41528700</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>-0,151</t>
+          <t>1,42870300</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>1,614</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2,60</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>-7,16</t>
+          <t>-6,28</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>-6,55</t>
+          <t>-6,43</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>408,851</t>
+          <t>412,172</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -24207,42 +24207,42 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1,08647100</t>
+          <t>1,09636500</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>0,803</t>
+          <t>1,842</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-6,65</t>
+          <t>-5,80</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>-4,26</t>
+          <t>-4,37</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>53,376</t>
+          <t>53,831</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -24467,42 +24467,42 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,78854700</t>
+          <t>1,80928500</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>0,602</t>
+          <t>1,347</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>10,35</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>2,095</t>
+          <t>2,119</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -24727,42 +24727,42 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>5,37636200</t>
+          <t>5,28324600</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>-4,140</t>
+          <t>-0,969</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>70,72</t>
+          <t>67,77</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>66,71</t>
+          <t>66,23</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>87,792</t>
+          <t>86,222</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -24987,42 +24987,42 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>9,18829000</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>-0,523</t>
+          <t>9,23610200</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>0,705</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>13,48</t>
+          <t>14,07</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>26,17</t>
+          <t>25,31</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>91,831</t>
+          <t>92,301</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -25247,42 +25247,42 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,32742400</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>-0,023</t>
+          <t>1,32585000</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>0,150</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>7,28</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>295,939</t>
+          <t>295,538</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -25507,42 +25507,42 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1,75465400</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>-0,258</t>
+          <t>1,76533400</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>2,062</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>-7,71</t>
+          <t>-7,15</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>-5,69</t>
+          <t>-6,74</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>104,047</t>
+          <t>104,713</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -25767,42 +25767,42 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2,97111700</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>-0,365</t>
+          <t>3,00124000</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>1,075</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>9,01</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>15,96</t>
+          <t>15,77</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>122,886</t>
+          <t>124,101</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -26027,42 +26027,42 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1,93664400</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>-0,062</t>
+          <t>1,95423700</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>2,131</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>6,22</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>-0,04</t>
+          <t>7,18</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>0,85</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>10,07</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>49,830</t>
+          <t>50,174</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -26291,42 +26291,42 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>7,74480000</t>
+          <t>7,64438100</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>-3,422</t>
+          <t>-0,999</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>6,28</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>65,12</t>
+          <t>62,98</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>66,06</t>
+          <t>66,33</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>124,223</t>
+          <t>121,228</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -26551,42 +26551,42 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1.436,99811300</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>3,024</t>
+          <t>1.454,42340600</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>-0,906</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>11,43</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>6,39</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>44,955</t>
+          <t>45,739</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -26811,42 +26811,42 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>35,25070800</t>
+          <t>35,02634500</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>-2,147</t>
+          <t>-1,119</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>-6,32</t>
+          <t>-6,92</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>32,76</t>
+          <t>31,45</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>583,386</t>
+          <t>585,674</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -27071,42 +27071,42 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>3,17072600</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>1,925</t>
+          <t>3,17525900</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>-0,242</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>30,89</t>
+          <t>31,08</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>57,55</t>
+          <t>54,07</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>522,778</t>
+          <t>521,770</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -27335,42 +27335,42 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,04480200</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>-0,749</t>
+          <t>5,06515200</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>0,691</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>12,86</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>24,64</t>
+          <t>23,57</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>23,963</t>
+          <t>24,084</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -27595,42 +27595,42 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1.650,07655600</t>
+          <t>1.676,01122600</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>0,735</t>
+          <t>1,538</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>9,16</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>15,16</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>24,26</t>
+          <t>23,61</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>32,499</t>
+          <t>33,233</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -27855,42 +27855,42 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2,01558800</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>-0,115</t>
+          <t>2,00289700</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>0,526</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>1,789</t>
+          <t>1,778</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -28107,42 +28107,42 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>6,24510200</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>-0,673</t>
+          <t>6,28721400</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>0,695</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>16,09</t>
+          <t>16,87</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>29,56</t>
+          <t>28,83</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>45,160</t>
+          <t>45,490</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -28359,42 +28359,42 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2,31305700</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>-0,383</t>
+          <t>2,32745800</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>0,965</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>10,24</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>21,82</t>
+          <t>21,18</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>34,984</t>
+          <t>35,222</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -28619,42 +28619,42 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>49,87978300</t>
+          <t>49,01643000</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>-4,132</t>
+          <t>-0,968</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>70,85</t>
+          <t>67,89</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>66,87</t>
+          <t>66,39</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>944,329</t>
+          <t>925,798</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -28879,42 +28879,42 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,56725000</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>1,925</t>
+          <t>1,56947000</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>-0,242</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>30,88</t>
+          <t>31,07</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>57,50</t>
+          <t>54,02</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>20,570</t>
+          <t>20,590</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -29139,42 +29139,42 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1,86988500</t>
+          <t>1,86707300</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>0,524</t>
+          <t>2,496</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>48,09</t>
+          <t>40,32</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>277,484</t>
+          <t>276,796</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -29403,42 +29403,42 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>0,90243600</t>
+          <t>0,91031400</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>0,245</t>
+          <t>0,898</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>-6,25</t>
+          <t>-5,43</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>-10,66</t>
+          <t>-8,63</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2,823</t>
+          <t>2,848</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -29659,42 +29659,42 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>7,12582400</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>-0,254</t>
+          <t>7,10976300</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>0,254</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>12,35</t>
+          <t>12,09</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>23,68</t>
+          <t>22,21</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>343,203</t>
+          <t>342,394</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -29919,42 +29919,42 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1.051,30697500</t>
+          <t>1.050,02569700</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>4,29</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>7,10</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>16,79</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>8,478</t>
+          <t>8,468</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -30179,7 +30179,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1.556,38505600</t>
+          <t>1.552,24968300</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -30189,32 +30189,32 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>4,05</t>
+          <t>3,77</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>10,66</t>
+          <t>8,99</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>22,214</t>
+          <t>22,137</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -30435,42 +30435,42 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>180,74083972</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>-0,500</t>
+          <t>181,70190051</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>0,708</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>4,38</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>14,69</t>
+          <t>15,30</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>28,11</t>
+          <t>27,23</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>18,075</t>
+          <t>18,172</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -30695,42 +30695,42 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1,90814500</t>
+          <t>1,90518200</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>0,522</t>
+          <t>2,485</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>8,51</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>48,15</t>
+          <t>40,38</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>5,689</t>
+          <t>5,680</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -30952,42 +30952,42 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1,86357400</t>
+          <t>1,86086600</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>0,526</t>
+          <t>2,499</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>3,80</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>8,70</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>48,35</t>
+          <t>40,56</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>1.669,187</t>
+          <t>1.666,385</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -31205,42 +31205,42 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>55,55685100</t>
+          <t>54,59867500</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>-4,133</t>
+          <t>-0,966</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>4,90</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>71,53</t>
+          <t>68,57</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>67,77</t>
+          <t>67,29</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>777,668</t>
+          <t>763,249</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -31449,42 +31449,42 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>39,11821900</t>
+          <t>38,87145500</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>-2,142</t>
+          <t>-1,119</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-6,88</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>33,48</t>
+          <t>32,16</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>685,541</t>
+          <t>681,217</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -31693,42 +31693,42 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>17,12628400</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t>-0,153</t>
+          <t>17,25890600</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>1,940</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>7,30</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>12,93</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>113,505</t>
+          <t>114,384</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -31946,42 +31946,42 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>32,74634700</t>
+          <t>32,53238800</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>-2,137</t>
+          <t>-1,116</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>-6,28</t>
+          <t>-6,89</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>32,65</t>
+          <t>31,31</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>11,114</t>
+          <t>11,028</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -32195,42 +32195,42 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>49,04356200</t>
+          <t>48,19526500</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>-4,139</t>
+          <t>-0,968</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>71,06</t>
+          <t>68,10</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>67,09</t>
+          <t>66,61</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>672,393</t>
+          <t>660,762</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -32444,42 +32444,42 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>33,63256900</t>
+          <t>33,41863000</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>-2,146</t>
+          <t>-1,121</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-6,91</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>32,82</t>
+          <t>31,51</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>414,432</t>
+          <t>411,796</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -32688,42 +32688,42 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>52,16756000</t>
+          <t>51,26588500</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>-4,133</t>
+          <t>-0,967</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>71,31</t>
+          <t>68,35</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>67,42</t>
+          <t>66,94</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>764,239</t>
+          <t>750,799</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -32936,42 +32936,42 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1,16282500</t>
+          <t>1,16438800</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>8,68</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>12,68</t>
+          <t>12,67</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>65,734</t>
+          <t>65,273</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -33197,42 +33197,42 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1,40349800</t>
+          <t>1,40539100</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>12,74</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>235,464</t>
+          <t>205,130</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -33462,42 +33462,42 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>6,10259600</t>
+          <t>6,11113400</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>9,40</t>
+          <t>9,55</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>13,69</t>
+          <t>13,67</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>43,083</t>
+          <t>42,949</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -33723,42 +33723,42 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,33777900</t>
+          <t>3,34270400</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>9,52</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>13,73</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>23,600</t>
+          <t>23,686</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -33985,42 +33985,42 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>5,31707300</t>
+          <t>5,32493100</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>810,124</t>
+          <t>811,322</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -34242,42 +34242,42 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>24,66580500</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>0,096</t>
+          <t>24,74247500</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>-0,040</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>10,51</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>13,40</t>
+          <t>13,88</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>96,503</t>
+          <t>96,798</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -34506,42 +34506,42 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>3,39491700</t>
+          <t>3,39987600</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,74</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>13,98</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>7.997,626</t>
+          <t>7.750,835</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -34757,52 +34757,52 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FIF DIAMANTE CORP RF CRED PRIV LP - RESP LTDA</t>
+          <t>CAIXA SAFIRA CORPORATIVO FIF RF LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>06/11/2019</t>
+          <t>11/05/2009</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1.962,24210100</t>
+          <t>5,07268100</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>14,89</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>17.003,005</t>
+          <t>3.177,450</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -34822,22 +34822,22 @@
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>PJ | TODOS</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/empresa/renda-fixa/credito-privado/caixa-fi-diamante-corporativo-rf-cred-priv-lp</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/referenciados/fi-safira-corporativo-rf-lp</t>
         </is>
       </c>
       <c r="Q135" s="4" t="inlineStr">
         <is>
-          <t>29.157.520/0001-94</t>
+          <t>10.384.413/0001-70</t>
         </is>
       </c>
       <c r="R135" s="4" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="S135" s="4" t="inlineStr">
@@ -34847,7 +34847,7 @@
       </c>
       <c r="T135" s="4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U135" s="4" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="AC135" s="4" t="inlineStr">
         <is>
-          <t>RF Crédito Privado permite Risco Mercado</t>
+          <t>RF 100% TPF - Longo Prazo</t>
         </is>
       </c>
       <c r="AD135" s="4" t="inlineStr">
@@ -34907,7 +34907,7 @@
       </c>
       <c r="AF135" s="4" t="inlineStr">
         <is>
-          <t>PROFISSIONAL</t>
+          <t>GERAL</t>
         </is>
       </c>
       <c r="AG135" s="4" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AI135" s="4" t="inlineStr">
         <is>
-          <t>Sim · Automatico · 95%</t>
+          <t>Sim · Automatico · 90%</t>
         </is>
       </c>
       <c r="AJ135" s="4" t="inlineStr">
@@ -34932,17 +34932,17 @@
       </c>
       <c r="AK135" s="4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AL135" s="4" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado"]</t>
+          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
         </is>
       </c>
       <c r="AM135" s="4" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado"]</t>
+          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
         </is>
       </c>
       <c r="AN135" s="4" t="inlineStr">
@@ -34963,49 +34963,49 @@
       </c>
       <c r="AR135" s="4" t="inlineStr">
         <is>
-          <t>CAIXA DIAMANTE CORPORATIVO FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CRÉDITO PRIVADO LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA SAFIRA CORPORATIVO FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS135" s="4" t="inlineStr"/>
       <c r="AT135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6445.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5148.pdf</t>
         </is>
       </c>
       <c r="AU135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6445.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5148.pdf</t>
         </is>
       </c>
       <c r="AV135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6445.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5148.pdf</t>
         </is>
       </c>
       <c r="AW135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6445.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5148.pdf</t>
         </is>
       </c>
       <c r="AX135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6445.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5148.pdf</t>
         </is>
       </c>
       <c r="AY135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6445.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5148.pdf</t>
         </is>
       </c>
       <c r="AZ135" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6445.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5148.pdf</t>
         </is>
       </c>
       <c r="BA135" s="4" t="inlineStr"/>
       <c r="BB135" s="4" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/513ae285-b3cb-42e6-a51a-984face9af08?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/edcf6e85-7c1c-4dd4-9cc1-599dd69841dc?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -35017,52 +35017,52 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIF SAFIRA CORPORATIVO RF LP - RESP LTDA</t>
+          <t>CAIXA FIF DIAMANTE CORP RF CRED PRIV LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>11/05/2009</t>
+          <t>06/11/2019</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>5,06553900</t>
+          <t>1.965,25360300</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>10,40</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>14,38</t>
+          <t>14,86</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.198,527</t>
+          <t>17.008,892</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -35082,22 +35082,22 @@
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>PJ | TODOS</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/referenciados/fi-safira-corporativo-rf-lp</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/empresa/renda-fixa/credito-privado/caixa-fi-diamante-corporativo-rf-cred-priv-lp</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>10.384.413/0001-70</t>
+          <t>29.157.520/0001-94</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="S136" s="2" t="inlineStr">
@@ -35107,7 +35107,7 @@
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="U136" s="2" t="inlineStr">
@@ -35152,7 +35152,7 @@
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>RF 100% TPF - Longo Prazo</t>
+          <t>RF Crédito Privado permite Risco Mercado</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
@@ -35167,7 +35167,7 @@
       </c>
       <c r="AF136" s="2" t="inlineStr">
         <is>
-          <t>GERAL</t>
+          <t>PROFISSIONAL</t>
         </is>
       </c>
       <c r="AG136" s="2" t="inlineStr">
@@ -35182,7 +35182,7 @@
       </c>
       <c r="AI136" s="2" t="inlineStr">
         <is>
-          <t>Sim · Automatico · 90%</t>
+          <t>Sim · Automatico · 95%</t>
         </is>
       </c>
       <c r="AJ136" s="2" t="inlineStr">
@@ -35192,17 +35192,17 @@
       </c>
       <c r="AK136" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AL136" s="2" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AM136" s="2" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AN136" s="2" t="inlineStr">
@@ -35223,49 +35223,49 @@
       </c>
       <c r="AR136" s="2" t="inlineStr">
         <is>
-          <t>CAIXA SAFIRA CORPORATIVO FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA DIAMANTE CORPORATIVO FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CRÉDITO PRIVADO LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS136" s="2" t="inlineStr"/>
       <c r="AT136" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5148.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6445.pdf</t>
         </is>
       </c>
       <c r="AU136" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5148.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6445.pdf</t>
         </is>
       </c>
       <c r="AV136" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5148.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6445.pdf</t>
         </is>
       </c>
       <c r="AW136" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5148.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6445.pdf</t>
         </is>
       </c>
       <c r="AX136" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5148.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6445.pdf</t>
         </is>
       </c>
       <c r="AY136" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5148.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6445.pdf</t>
         </is>
       </c>
       <c r="AZ136" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5148.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6445.pdf</t>
         </is>
       </c>
       <c r="BA136" s="2" t="inlineStr"/>
       <c r="BB136" s="2" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/edcf6e85-7c1c-4dd4-9cc1-599dd69841dc?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/513ae285-b3cb-42e6-a51a-984face9af08?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -35287,42 +35287,42 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1,60883589</t>
+          <t>1,61127202</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>9,90</t>
+          <t>10,06</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>382,365</t>
+          <t>371,220</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -35531,42 +35531,42 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>5,32283100</t>
+          <t>5,33087700</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>14,49</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>297,114</t>
+          <t>297,563</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -35788,42 +35788,42 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>18,60505100</t>
+          <t>18,63239800</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>10,05</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>4.880,152</t>
+          <t>4.886,862</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -36032,42 +36032,42 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>9,04503400</t>
+          <t>9,05846200</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>14,35</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.862,160</t>
+          <t>3.870,146</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -36310,12 +36310,12 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -36536,42 +36536,42 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2,92292200</t>
+          <t>2,92688100</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>8,90</t>
+          <t>9,04</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>12,97</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>13.703,520</t>
+          <t>13.395,025</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -36797,42 +36797,42 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>4,60027700</t>
+          <t>4,60728800</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>14,54</t>
+          <t>14,52</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>16.998,313</t>
+          <t>17.198,610</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -37057,7 +37057,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1,42852600</t>
+          <t>1,43074800</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -37067,32 +37067,32 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>10,29</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>3.419,589</t>
+          <t>3.469,746</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -37313,42 +37313,42 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1.840,55768200</t>
+          <t>1.843,34693200</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>10,00</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,34</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>1.522,584</t>
+          <t>1.531,653</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -37573,22 +37573,22 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1,34878900</t>
+          <t>1,35044700</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,040</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>7,97</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -37598,17 +37598,17 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>33.733,571</t>
+          <t>33.311,559</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -37832,42 +37832,42 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>9,71923400</t>
+          <t>9,73210400</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>8,72</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>12,47</t>
+          <t>12,46</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>2.800,715</t>
+          <t>2.839,844</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -38091,7 +38091,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2,55950600</t>
+          <t>2,56290400</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -38101,12 +38101,12 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>8,57</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -38116,17 +38116,17 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>17.153,886</t>
+          <t>16.943,657</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -38352,42 +38352,42 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,65720500</t>
+          <t>4,66535800</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,062</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,20</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.893,191</t>
+          <t>11.992,596</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -38615,42 +38615,42 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,77496200</t>
+          <t>3,79548600</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>0,185</t>
+          <t>0,291</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>8,72</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>1.658,382</t>
+          <t>1.666,864</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -38878,42 +38878,42 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>2,48641100</t>
+          <t>2,49348900</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,135</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>8,26</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>11,79</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>3.313,370</t>
+          <t>3.296,314</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -39143,42 +39143,42 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>3,09689800</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>0,096</t>
+          <t>3,10630300</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>-0,039</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>9,81</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>13,19</t>
+          <t>13,69</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>37,561</t>
+          <t>37,675</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -39399,42 +39399,42 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1.699,88229400</t>
+          <t>1.702,98724500</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,070</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>8,51</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,30</t>
+          <t>12,47</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>450,710</t>
+          <t>451,534</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -39659,42 +39659,42 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>3,96149200</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>0,068</t>
+          <t>3,97473400</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>-0,023</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>10,41</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>13,89</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>3.153,814</t>
+          <t>3.168,865</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -39922,42 +39922,42 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>5,32615700</t>
+          <t>5,34712600</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,219</t>
+          <t>0,131</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>8,32</t>
+          <t>8,74</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>12,32</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>2.345,907</t>
+          <t>2.358,354</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -40184,42 +40184,42 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>5,38530500</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>0,098</t>
+          <t>5,40224400</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>-0,026</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,50</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>10,31</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>13,59</t>
+          <t>14,08</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>5.814,707</t>
+          <t>5.836,017</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -40446,42 +40446,42 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>4,92352700</t>
+          <t>4,93766300</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>0,116</t>
+          <t>0,118</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>13,42</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>485,342</t>
+          <t>481,736</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -40708,42 +40708,42 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>8,24743700</t>
+          <t>8,25879100</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>9,91</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>168,520</t>
+          <t>168,821</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -40828,42 +40828,42 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>3,55950200</t>
+          <t>3,57476900</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>0,285</t>
+          <t>0,220</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>7,14</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>10,07</t>
+          <t>10,81</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>691,410</t>
+          <t>694,376</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -41090,42 +41090,42 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>3,91143400</t>
+          <t>3,93700200</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>0,229</t>
+          <t>0,361</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>2,10</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>8,26</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>11,19</t>
+          <t>11,86</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>635,112</t>
+          <t>639,264</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -41353,42 +41353,42 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>2,70891900</t>
+          <t>2,71293300</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>9,99</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>8.624,775</t>
+          <t>8.804,053</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -41617,42 +41617,42 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>7,44577300</t>
+          <t>7,45640400</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,98</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>14,31</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>12.594,775</t>
+          <t>12.703,000</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -41882,42 +41882,42 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>7,77705300</t>
+          <t>7,78876900</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>14,25</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>3.756,251</t>
+          <t>3.800,794</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -42142,42 +42142,42 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1,50614200</t>
+          <t>1,51325400</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>0,069</t>
+          <t>0,250</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>8,52</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>12,04</t>
+          <t>12,50</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>163,671</t>
+          <t>164,483</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -42398,42 +42398,42 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,25245500</t>
+          <t>3,25712000</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>9,41</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>13,45</t>
+          <t>13,44</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>2.001,592</t>
+          <t>2.029,816</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -42686,12 +42686,12 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -42942,12 +42942,12 @@
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -43198,12 +43198,12 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -43454,12 +43454,12 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -43702,12 +43702,12 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -43958,12 +43958,12 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -44184,42 +44184,42 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>6,98353200</t>
+          <t>6,99431800</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>10,20</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,59</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>22.434,369</t>
+          <t>22.281,222</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -44304,42 +44304,42 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>5,70982100</t>
+          <t>5,73292800</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>0,210</t>
+          <t>0,112</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>9,07</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>12,12</t>
+          <t>12,74</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>591,569</t>
+          <t>593,963</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -44595,12 +44595,12 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -44817,42 +44817,42 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>4,15364700</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr">
-        <is>
-          <t>-0,520</t>
+          <t>4,17610100</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>0,715</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>4,43</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>14,72</t>
+          <t>15,34</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>28,13</t>
+          <t>27,26</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>304,436</t>
+          <t>306,088</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -45077,42 +45077,42 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>3,81761000</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>-0,393</t>
+          <t>3,83405300</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>0,680</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>14,50</t>
+          <t>14,99</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>27,74</t>
+          <t>26,69</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>7,957</t>
+          <t>7,992</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -45337,42 +45337,42 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>11,63079677</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>-0,207</t>
-        </is>
-      </c>
-      <c r="F177" s="7" t="inlineStr">
-        <is>
-          <t>-1,54</t>
+          <t>11,96906203</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>1,295</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>13,64</t>
+          <t>15,42</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>2.324,576</t>
+          <t>2.391,027</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -45597,42 +45597,42 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>2,11090100</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>-0,720</t>
+          <t>2,12733400</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>0,943</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>12,23</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>22,07</t>
+          <t>21,65</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>206,154</t>
+          <t>207,759</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -45853,42 +45853,42 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>2,07266800</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>-0,062</t>
+          <t>2,09152100</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>2,134</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>6,23</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="inlineStr">
-        <is>
-          <t>-0,02</t>
+          <t>7,20</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>0,88</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>753,507</t>
+          <t>757,447</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -46113,42 +46113,42 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>3,63608719</t>
-        </is>
-      </c>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>-0,234</t>
+          <t>3,64997942</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>0,704</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>4,72</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>11,76</t>
+          <t>12,19</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>21,18</t>
+          <t>19,80</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>1.378,231</t>
+          <t>1.365,247</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -46365,42 +46365,42 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>2,62067199</t>
-        </is>
-      </c>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>-0,324</t>
+          <t>2,64355639</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>1,085</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>5,60</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>11,84</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>19,79</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>801,114</t>
+          <t>801,179</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -46617,42 +46617,42 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>3,89626300</t>
+          <t>3,90298500</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>0,037</t>
+          <t>0,060</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>4.627,515</t>
+          <t>4.508,283</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -814,22 +814,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,34037900</t>
+          <t>2,34137300</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,042</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>8,91</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>402,540</t>
+          <t>402,631</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,68473500</t>
+          <t>5,68718600</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1084,32 +1084,32 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>8,79</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>12,30</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.521,597</t>
+          <t>6.500,477</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,87030500</t>
+          <t>2,87154200</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>8,78</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>744,567</t>
+          <t>742,838</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-movimentacoes-automaticas-rf-simples/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-movimentacoes-automaticas-curto-prazo/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1593,42 +1593,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,62139000</t>
+          <t>3,62262500</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,034</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>10,00</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>14,00</t>
+          <t>13,98</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>120,022</t>
+          <t>120,042</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1856,42 +1856,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,05362100</t>
+          <t>10,05735300</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>9,29</t>
+          <t>9,33</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>13,04</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>591,015</t>
+          <t>590,897</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>3,46000400</t>
+          <t>3,46159100</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>9,81</t>
+          <t>9,86</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12,453</t>
+          <t>12,459</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20,65824900</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>-0,085</t>
+          <t>20,69867500</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>0,195</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>1,70</t>
+          <t>1,90</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>7,78</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>11,18</t>
+          <t>11,51</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>116,030</t>
+          <t>116,214</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2640,42 +2640,42 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,48489000</t>
+          <t>3,48629100</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,040</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>9,91</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>13,92</t>
+          <t>13,91</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>64,647</t>
+          <t>64,360</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2896,42 +2896,42 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1.910,07540400</t>
+          <t>1.910,57920900</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,032</t>
+          <t>0,026</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>14,37</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,728</t>
+          <t>97,722</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-plus-rf-credito-privado-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-plus-mm-credito-privado-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3152,42 +3152,42 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>3,11784600</t>
+          <t>3,11936000</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>10,37</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>14,50</t>
+          <t>14,49</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>1.715,707</t>
+          <t>1.716,347</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3524,42 +3524,42 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>13,97388200</t>
+          <t>13,99262900</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,134</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>8,81</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>11,77</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>28,020</t>
+          <t>28,062</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3846,11 +3846,7 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-smart-infraestrutura-debincentivadas-cdi-rf-cred-priv-lp-subclasse-varejo/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>67.702.501/0001-90</t>
@@ -4040,42 +4036,42 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>47,80952500</t>
+          <t>47,82721300</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,036</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>9,30</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>13,00</t>
+          <t>12,99</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>41,550</t>
+          <t>41,560</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4301,42 +4297,42 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20,92213700</t>
+          <t>20,93075700</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>12,74</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,428</t>
+          <t>59,449</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4561,42 +4557,42 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>15,49231400</t>
+          <t>15,49809700</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>13,10</t>
+          <t>13,09</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>28,133</t>
+          <t>28,144</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4821,42 +4817,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,26667500</t>
+          <t>3,27120100</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,138</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>13,00</t>
+          <t>13,24</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,318</t>
+          <t>77,437</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5085,42 +5081,42 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,10408000</t>
+          <t>3,10519300</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>9,03</t>
+          <t>9,07</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>12,69</t>
+          <t>12,68</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1,664</t>
+          <t>1,665</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -5341,42 +5337,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,45147000</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>-0,057</t>
+          <t>3,45792500</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0,187</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>1,67</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>8,49</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>11,85</t>
+          <t>12,15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>125,242</t>
+          <t>125,376</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5605,42 +5601,42 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,46432000</t>
+          <t>3,47114200</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,020</t>
+          <t>0,196</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>8,70</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>11,93</t>
+          <t>12,16</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>64,629</t>
+          <t>64,555</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -5865,42 +5861,42 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34,00427000</t>
+          <t>34,01742200</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>9,64</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>13,48</t>
+          <t>13,47</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2.207,604</t>
+          <t>2.207,119</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -6125,42 +6121,42 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3,16163400</t>
+          <t>3,16316000</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>10,30</t>
+          <t>10,35</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,46</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>1.803,638</t>
+          <t>1.802,114</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -6379,42 +6375,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,42810600</t>
+          <t>3,42943300</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>13,50</t>
+          <t>13,49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,015</t>
+          <t>13,019</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -6644,42 +6640,42 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>19,76190000</t>
+          <t>19,76853200</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>13,86</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>969,204</t>
+          <t>969,167</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -6904,7 +6900,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,08012400</t>
+          <t>1,08056700</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -6914,12 +6910,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>10,20</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -6929,17 +6925,17 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,556</t>
+          <t>22,565</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -7152,42 +7148,42 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.906,90358500</t>
+          <t>1.907,61798800</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,036</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>10,34</t>
+          <t>10,39</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>183,763</t>
+          <t>183,939</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -7412,7 +7408,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,29055500</t>
+          <t>1,29105800</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -7422,32 +7418,32 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,222</t>
+          <t>75,243</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7470,11 +7466,7 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-vinland-debenture-incentivado/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>58.113.332/0001-62</t>
@@ -7664,42 +7656,42 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,14652167</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>0,032</t>
+          <t>1,14513172</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>7,84</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>196,421</t>
+          <t>196,137</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -7722,11 +7714,7 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-arx-ipca-deb-incentivadas-rf-cred-priv-lp/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P29" s="4" t="inlineStr"/>
       <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>60.138.811/0001-85</t>
@@ -7950,12 +7938,12 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8168,42 +8156,42 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>5,14529800</t>
+          <t>5,14778200</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>10,30</t>
+          <t>10,35</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>14,46</t>
+          <t>14,45</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>3.482,874</t>
+          <t>3.483,444</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -8428,42 +8416,42 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11,01612000</t>
+          <t>11,02000900</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>10,20</t>
+          <t>10,24</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2.440,528</t>
+          <t>2.444,498</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8688,7 +8676,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1,21928600</t>
+          <t>1,21973900</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -8698,32 +8686,32 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>9,80</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>13,66</t>
+          <t>13,62</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>63,672</t>
+          <t>63,696</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -8940,7 +8928,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1,09821987</t>
+          <t>1,09656875</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -8950,12 +8938,12 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -8965,17 +8953,17 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>303,718</t>
+          <t>303,060</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -8998,11 +8986,7 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-rb-asset-deb-incentivadas-cdi-rf-cred-priv/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>62.890.286/0001-85</t>
@@ -9192,42 +9176,42 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1,32165100</t>
+          <t>1,32230200</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>10,49</t>
+          <t>10,54</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,73</t>
+          <t>14,72</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>490,075</t>
+          <t>489,096</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -9252,7 +9236,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-unique-private-cred-priv-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-unique-private-cred-priv-lp</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -9452,42 +9436,42 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,25341900</t>
+          <t>1,25467900</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,064</t>
+          <t>0,100</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>11,52</t>
+          <t>11,64</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>14,98</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,654</t>
+          <t>41,695</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9512,7 +9496,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fif-inflacao-2027/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fif-inflacao-2027</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9712,42 +9696,42 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>5,73919500</t>
+          <t>5,74145100</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>10,35</t>
+          <t>10,39</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>571,638</t>
+          <t>571,598</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -9973,22 +9957,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5,34659600</t>
+          <t>5,34929200</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>10,33</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -9998,17 +9982,17 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>859,208</t>
+          <t>859,301</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10033,7 +10017,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-plus-qualificado-rf-credito-privado-lp/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-qualificado-rf-credito-privado-longo-prazo</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10233,7 +10217,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>30,29977600</t>
+          <t>30,31362100</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10243,32 +10227,32 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>28,61</t>
+          <t>28,60</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>21,650</t>
+          <t>21,659</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -10481,42 +10465,42 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>31,81136100</t>
+          <t>31,82235800</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,034</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,14</t>
+          <t>14,12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3.144,329</t>
+          <t>3.144,324</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -10737,42 +10721,42 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>3,35145400</t>
+          <t>3,35303600</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>10,33</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>14,46</t>
+          <t>14,45</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>685,731</t>
+          <t>688,804</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -10997,42 +10981,42 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1.836,53532700</t>
+          <t>1.837,38820700</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,031</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>9,03</t>
+          <t>9,08</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>117,493</t>
+          <t>117,649</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -11057,7 +11041,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-renda-fixa-ativa-lp/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-renda-fixa-ativa-lp</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11253,42 +11237,42 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>6,42697500</t>
+          <t>6,42914100</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>13,89</t>
+          <t>13,87</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>122,517</t>
+          <t>122,549</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -11514,42 +11498,42 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3,71499800</t>
+          <t>3,71682000</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,51</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>14,69</t>
+          <t>14,68</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16.916,142</t>
+          <t>16.927,342</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -11778,22 +11762,22 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>5,52352000</t>
+          <t>5,52638900</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>10,62</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -11803,17 +11787,17 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>1.575,893</t>
+          <t>1.576,624</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -12039,42 +12023,42 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>31,40969900</t>
+          <t>31,42265000</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>9,15</t>
+          <t>9,20</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>12,88</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>168,781</t>
+          <t>168,749</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -12333,12 +12317,12 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -12555,42 +12539,42 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3,74597300</t>
+          <t>3,74759600</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>14,02</t>
+          <t>14,01</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2.314,872</t>
+          <t>2.322,914</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12819,42 +12803,42 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2,90734500</t>
+          <t>2,90856700</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,042</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>9,03</t>
+          <t>9,08</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>12,71</t>
+          <t>12,70</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>6.009,739</t>
+          <t>6.000,658</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -13079,42 +13063,42 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3,31670700</t>
+          <t>3,31821600</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>10,41</t>
+          <t>10,46</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>14,64</t>
+          <t>14,63</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>14.813,537</t>
+          <t>14.831,334</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -13339,42 +13323,42 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1,34184700</t>
+          <t>1,34247100</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>10,20</t>
+          <t>10,26</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>14,37</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>73,407</t>
+          <t>73,414</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -13599,42 +13583,42 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10,06667600</t>
+          <t>10,07107400</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>10,05</t>
+          <t>10,10</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>14,12</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>825,257</t>
+          <t>825,459</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -13864,42 +13848,42 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4,63139800</t>
+          <t>4,63352300</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,20</t>
+          <t>14,19</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>17.184,088</t>
+          <t>17.166,016</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -14124,42 +14108,42 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>5,30789000</t>
+          <t>5,31030900</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>10,37</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>14,50</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23.521,959</t>
+          <t>23.548,544</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -14384,42 +14368,42 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4,96702700</t>
+          <t>4,96925700</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>10,34</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,46</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>9.855,052</t>
+          <t>9.836,380</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -14648,7 +14632,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.796,46342700</t>
+          <t>1.797,33730500</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -14658,32 +14642,32 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>9,90</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>13,88</t>
+          <t>13,87</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>285,102</t>
+          <t>284,941</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -14706,11 +14690,7 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/voce/renda-fixa/caixa-turquesa-pj/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr"/>
       <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr"/>
@@ -14768,7 +14748,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1,47207400</t>
+          <t>1,47255900</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -14778,32 +14758,32 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>9,98</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>13,91</t>
+          <t>13,90</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>65,373</t>
+          <t>65,399</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -15020,17 +15000,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>13,15940500</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>-0,289</t>
+          <t>13,15933500</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -15040,7 +15020,7 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>16,75</t>
+          <t>17,03</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -15050,12 +15030,12 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -15284,42 +15264,42 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.698,83396200</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-0,011</t>
+          <t>1.700,34184600</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>0,088</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>8,51</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>12,39</t>
+          <t>12,55</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>112,085</t>
+          <t>112,184</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -15540,42 +15520,42 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.511,12156200</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>-0,314</t>
+          <t>2.512,71285000</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>0,063</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>22,25</t>
+          <t>22,33</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>25,21</t>
+          <t>26,05</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14,507</t>
+          <t>14,497</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -15826,12 +15806,12 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -16048,7 +16028,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,29587700</t>
+          <t>1,29511200</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -16058,32 +16038,32 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,50</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>6,10</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4,874</t>
+          <t>4,872</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -16108,7 +16088,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-short-mm/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-short-mm</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -16304,42 +16284,42 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1,16120700</t>
+          <t>1,15246400</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>-0,759</t>
+          <t>-0,752</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>3,67</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>0,14</t>
+          <t>2,89</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>-0,60</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>10,75</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>3,459</t>
+          <t>3,458</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -16364,7 +16344,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-long-bias-mm</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
@@ -16590,12 +16570,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -16812,42 +16792,42 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1,44618100</t>
+          <t>1,43964200</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>-0,004</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,20</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,94</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>11,234</t>
+          <t>11,181</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -16872,7 +16852,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -17098,12 +17078,12 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -17320,42 +17300,42 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1,11967700</t>
+          <t>1,12228500</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>0,276</t>
+          <t>0,232</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>-7,13</t>
+          <t>-6,91</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>-3,88</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>3,221</t>
+          <t>3,226</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -17576,42 +17556,42 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>5,56606326</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>-0,060</t>
+          <t>5,57101975</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>0,089</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>8,47</t>
+          <t>8,57</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>12,53</t>
+          <t>12,68</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>32,241</t>
+          <t>32,281</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -17836,7 +17816,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1.249,34615200</t>
+          <t>1.256,37714800</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -17846,32 +17826,32 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>-0,43</t>
+          <t>-2,49</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>0,12</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>4,20</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>37,487</t>
+          <t>37,701</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -18106,42 +18086,42 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>4,57411500</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>-0,400</t>
+          <t>4,60126600</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>0,593</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-2,76</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>21,04</t>
+          <t>21,55</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>512,844</t>
+          <t>515,693</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -18366,7 +18346,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2,95615700</t>
+          <t>2,94990600</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -18376,32 +18356,32 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>68,451</t>
+          <t>68,298</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -18622,42 +18602,42 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1.705,74240500</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>0,585</t>
+          <t>1.703,97874100</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>-0,103</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-0,70</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>11,68</t>
+          <t>11,38</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>30,460</t>
+          <t>30,428</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -18882,42 +18862,42 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>3,99555400</t>
+          <t>4,01600800</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>0,008</t>
+          <t>0,511</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>18,77</t>
+          <t>19,38</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>26,34</t>
+          <t>27,56</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2.459,339</t>
+          <t>2.472,467</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -19142,42 +19122,42 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1,97355400</t>
+          <t>1,97451800</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>8,56</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>12,18</t>
+          <t>12,27</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20,147</t>
+          <t>20,108</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -19402,42 +19382,42 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1.725,46715400</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>-0,007</t>
+          <t>1.727,04728200</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>0,091</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>9,10</t>
+          <t>9,20</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,52</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>15,082</t>
+          <t>15,091</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -19658,42 +19638,42 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>5,85322700</t>
+          <t>5,85784500</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>0,009</t>
+          <t>0,078</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>14,08</t>
+          <t>14,17</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>906,212</t>
+          <t>906,289</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -19918,7 +19898,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0,62138850</t>
+          <t>0,62695839</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -19928,12 +19908,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>7,61</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>-13,94</t>
+          <t>-13,17</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -19943,17 +19923,17 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>12,712</t>
+          <t>12,847</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -20185,42 +20165,42 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3,78629800</t>
+          <t>3,78820400</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>0,008</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>12,59</t>
+          <t>12,68</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>700,535</t>
+          <t>700,722</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -20441,42 +20421,42 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,41183900</t>
+          <t>1,41274100</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>0,034</t>
+          <t>0,063</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-1,10</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>4,10</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>7,62</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>72,349</t>
+          <t>72,395</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -20501,7 +20481,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa_fic_fim_cap_protegido_cesta_agro/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa_fic_fim_cap_protegido_cesta_agro</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -20709,42 +20689,42 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1,53748600</t>
+          <t>1,53812100</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>11,39</t>
+          <t>11,22</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>82,575</t>
+          <t>82,609</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -20977,42 +20957,42 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,41619700</t>
+          <t>3,41992600</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,090</t>
+          <t>0,109</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>162,708</t>
+          <t>162,886</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -21243,42 +21223,42 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1,61199600</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>-0,140</t>
+          <t>1,61352900</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>0,095</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>18,72</t>
+          <t>19,58</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>15,186</t>
+          <t>15,200</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -21509,7 +21489,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>6,98268400</t>
+          <t>6,99063500</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -21519,32 +21499,32 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>8,57</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>13,63</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>124,598</t>
+          <t>124,739</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -21765,42 +21745,42 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,86371200</t>
+          <t>1,86434600</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>-0,002</t>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>5,50</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>169,184</t>
+          <t>169,244</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -22021,7 +22001,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1,42673000</t>
+          <t>1,41601400</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -22031,32 +22011,32 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>7,83</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>275,967</t>
+          <t>273,895</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -22282,42 +22262,42 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1,40187200</t>
+          <t>1,39617600</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>-0,001</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>8,77</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>6,54</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>12,272</t>
+          <t>12,221</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -22542,42 +22522,42 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3,91472500</t>
+          <t>3,91577800</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>0,410</t>
+          <t>0,026</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-2,58</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>97,942</t>
+          <t>97,955</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -22832,12 +22812,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -22860,11 +22840,7 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fic-fif-quantitativo-low-vol/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P88" s="2" t="inlineStr"/>
       <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr"/>
       <c r="S88" s="2" t="inlineStr"/>
@@ -22922,42 +22898,42 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1,33823700</t>
+          <t>1,34395700</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>0,490</t>
+          <t>0,427</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>10,58</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>18,89</t>
+          <t>20,28</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>4,052</t>
+          <t>4,069</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -22982,7 +22958,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIA-Institucional-BDR-nivel-I/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fic-fia-compromisso-bdr-nivel-i</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -23178,42 +23154,42 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2,72809900</t>
+          <t>2,72084500</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>-0,972</t>
+          <t>-0,265</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,24</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>13,08</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>24,39</t>
+          <t>25,06</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>13,314</t>
+          <t>13,263</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -23238,7 +23214,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-etf-bovespa/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-ibovespa</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -23438,42 +23414,42 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1.990,32450200</t>
+          <t>1.978,32013200</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>-0,857</t>
+          <t>-0,603</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>5,77</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>0,26</t>
+          <t>5,14</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>10,71</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>9,613</t>
+          <t>9,555</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -23687,42 +23663,42 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>10,76272900</t>
+          <t>10,79478800</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>0,604</t>
+          <t>0,297</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>8,69</t>
+          <t>9,01</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>15,99</t>
+          <t>16,12</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>277,356</t>
+          <t>278,153</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -23947,42 +23923,42 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1,40889300</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>-0,351</t>
+          <t>1,40897800</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>-7,58</t>
+          <t>-7,57</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>-6,68</t>
+          <t>-5,07</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>406,438</t>
+          <t>406,368</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -24207,42 +24183,42 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1,07847700</t>
+          <t>1,07776500</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>-0,682</t>
+          <t>-0,066</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-7,34</t>
+          <t>-7,40</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>-4,51</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>52,935</t>
+          <t>52,849</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -24467,42 +24443,42 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,77259900</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>-1,063</t>
+          <t>1,77297800</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>0,021</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>9,59</t>
+          <t>11,23</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>2,070</t>
+          <t>2,071</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -24727,42 +24703,42 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>5,40254500</t>
+          <t>5,29739800</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>-0,842</t>
+          <t>-1,946</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>71,55</t>
+          <t>68,21</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>60,02</t>
+          <t>59,66</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>88,080</t>
+          <t>86,348</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -24987,42 +24963,42 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>9,10945100</t>
+          <t>9,08482900</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>-0,976</t>
+          <t>-0,270</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>12,51</t>
+          <t>12,20</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>23,09</t>
+          <t>23,75</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>91,045</t>
+          <t>90,845</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -25247,42 +25223,42 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,33522300</t>
+          <t>1,32365000</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>-0,035</t>
+          <t>-0,037</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>4,50</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>297,199</t>
+          <t>294,619</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -25507,42 +25483,42 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1,72884900</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>-0,341</t>
+          <t>1,73502300</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>0,357</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>-0,70</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>-9,07</t>
+          <t>-8,75</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>-7,56</t>
+          <t>-5,79</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>102,362</t>
+          <t>102,633</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -25767,42 +25743,42 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>3,00191300</t>
+          <t>2,98977500</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>-0,113</t>
+          <t>-0,404</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>10,14</t>
+          <t>9,69</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>14,87</t>
+          <t>15,49</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>124,066</t>
+          <t>123,580</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -26027,42 +26003,42 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1,92668000</t>
+          <t>1,91504600</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>-0,857</t>
+          <t>-0,603</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,03</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>9,45</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>49,464</t>
+          <t>49,152</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -26291,42 +26267,42 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>7,83767400</t>
+          <t>7,64247900</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>-0,664</t>
+          <t>-2,490</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>8,97</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>67,10</t>
+          <t>62,94</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>62,57</t>
+          <t>59,77</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>124,408</t>
+          <t>121,368</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -26551,42 +26527,42 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1.362,76854300</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>-2,839</t>
+          <t>1.365,84146000</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>0,225</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>4,40</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>-0,30</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="inlineStr">
-        <is>
-          <t>-1,02</t>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>0,65</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>42,207</t>
+          <t>42,329</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -26611,7 +26587,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/Caixa-FI-Acoes-Banco-do-Brasil-Plus/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/Caixa-FI-Acoes-Banco-do-Brasil-Plus/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q103" s="4" t="inlineStr">
@@ -26811,42 +26787,42 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>34,10952900</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>-1,151</t>
+          <t>34,16008700</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>0,148</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>-9,35</t>
+          <t>-9,22</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>28,10</t>
+          <t>27,60</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>579,500</t>
+          <t>583,425</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -27071,42 +27047,42 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>3,14599800</t>
+          <t>3,17517800</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>1,436</t>
+          <t>0,927</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>29,87</t>
+          <t>31,07</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>49,96</t>
+          <t>55,04</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>518,747</t>
+          <t>521,380</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -27335,42 +27311,42 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>4,98629700</t>
+          <t>4,97785000</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>-0,861</t>
+          <t>-0,169</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>11,10</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>21,14</t>
+          <t>21,94</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>23,868</t>
+          <t>23,828</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -27595,42 +27571,42 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1.634,26669800</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>-1,329</t>
+          <t>1.642,59765300</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>0,509</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>6,98</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>12,29</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>20,79</t>
+          <t>22,82</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>32,569</t>
+          <t>32,664</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -27855,42 +27831,42 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>1,95923300</t>
+          <t>1,94968500</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>-1,018</t>
+          <t>-0,487</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-4,16</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>3,51</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>1,741</t>
+          <t>1,733</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -28107,42 +28083,42 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>6,20743500</t>
+          <t>6,18756900</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>-0,884</t>
+          <t>-0,320</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>15,39</t>
+          <t>15,02</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>26,51</t>
+          <t>27,14</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>44,885</t>
+          <t>44,738</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -28359,17 +28335,17 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2,29458400</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>-0,880</t>
+          <t>2,29473900</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>3,58</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -28379,22 +28355,22 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>19,14</t>
+          <t>20,14</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>34,710</t>
+          <t>34,711</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -28619,42 +28595,42 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>50,12366300</t>
+          <t>49,14774000</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>-0,843</t>
+          <t>-1,947</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>71,68</t>
+          <t>68,34</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>60,16</t>
+          <t>59,81</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>934,305</t>
+          <t>917,066</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -28879,42 +28855,42 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,55497600</t>
+          <t>1,56936000</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>1,432</t>
+          <t>0,925</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>29,86</t>
+          <t>31,06</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>49,91</t>
+          <t>54,98</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>20,366</t>
+          <t>20,549</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -28937,11 +28913,7 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="P112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-seguridade/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P112" s="2" t="inlineStr"/>
       <c r="Q112" s="2" t="inlineStr">
         <is>
           <t>59.815.671/0001-53</t>
@@ -29139,42 +29111,42 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1,84403000</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>-1,586</t>
+          <t>1,84669800</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>0,144</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>2,50</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>7,42</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>38,19</t>
+          <t>39,21</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>272,762</t>
+          <t>273,150</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -29403,42 +29375,42 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>0,90281700</t>
+          <t>0,90189000</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>-1,080</t>
+          <t>-0,102</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>-6,21</t>
+          <t>-6,30</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>-6,66</t>
+          <t>-5,05</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2,825</t>
+          <t>2,822</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -29659,42 +29631,42 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>6,99248500</t>
+          <t>6,96613700</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>-0,825</t>
+          <t>-0,376</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>9,83</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>20,26</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>336,745</t>
+          <t>335,419</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -29919,7 +29891,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1.057,47905000</t>
+          <t>1.048,40721700</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -29929,32 +29901,32 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>4,90</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>15,54</t>
+          <t>15,39</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>8,346</t>
+          <t>8,273</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -30179,7 +30151,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1.562,69834000</t>
+          <t>1.550,04614200</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -30189,32 +30161,32 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>5,79</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>3,62</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>9,75</t>
+          <t>9,69</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>22,172</t>
+          <t>21,997</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -30435,42 +30407,42 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>179,23217978</t>
+          <t>178,75762154</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>-0,973</t>
+          <t>-0,264</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>3,50</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>13,44</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>24,98</t>
+          <t>25,65</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>17,925</t>
+          <t>17,877</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -30695,42 +30667,42 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1,88183900</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>-1,576</t>
+          <t>1,88455200</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>0,144</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>38,26</t>
+          <t>39,28</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>5,611</t>
+          <t>5,619</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -30952,42 +30924,42 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1,83798600</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>-1,584</t>
+          <t>1,84067200</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>0,146</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>7,36</t>
+          <t>7,52</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>38,43</t>
+          <t>39,46</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>1.645,424</t>
+          <t>1.647,729</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -31205,42 +31177,42 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>55,83581900</t>
+          <t>54,75117000</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>-0,840</t>
+          <t>-1,942</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>72,39</t>
+          <t>69,05</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>61,04</t>
+          <t>60,69</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>780,541</t>
+          <t>762,473</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -31449,42 +31421,42 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>37,85573500</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>-1,149</t>
+          <t>37,91242200</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>0,149</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>-9,32</t>
+          <t>-9,18</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>28,79</t>
+          <t>28,29</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>663,298</t>
+          <t>664,212</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -31693,42 +31665,42 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>17,04776900</t>
+          <t>16,91981200</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>-0,759</t>
+          <t>-0,750</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>11,78</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>112,828</t>
+          <t>111,981</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -31946,42 +31918,42 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>31,68400500</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>-1,146</t>
+          <t>31,73065900</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>0,147</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>-9,32</t>
+          <t>-9,19</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>27,98</t>
+          <t>27,48</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>10,740</t>
+          <t>10,743</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -32195,42 +32167,42 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>49,28459400</t>
+          <t>48,32654200</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>-0,841</t>
+          <t>-1,943</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>71,90</t>
+          <t>68,56</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>60,39</t>
+          <t>60,03</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>675,439</t>
+          <t>662,309</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -32444,42 +32416,42 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>32,54305200</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>-1,151</t>
+          <t>32,59132700</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>0,148</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>-9,35</t>
+          <t>-9,21</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>28,16</t>
+          <t>27,65</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>400,972</t>
+          <t>401,567</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -32688,42 +32660,42 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>52,42524200</t>
+          <t>51,40686900</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>-0,840</t>
+          <t>-1,942</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>72,15</t>
+          <t>68,81</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>60,69</t>
+          <t>60,34</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>767,778</t>
+          <t>752,864</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -32936,7 +32908,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1,16594200</t>
+          <t>1,16646100</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -32946,12 +32918,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>8,97</t>
+          <t>9,02</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -32961,17 +32933,17 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>65,441</t>
+          <t>65,668</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -32994,11 +32966,7 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="P128" s="2" t="inlineStr">
-        <is>
-          <t>http://site.extra.caixa.gov.br/fundos-investimento/fundo-simples/fic-azulzinha-rf-simples/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P128" s="2" t="inlineStr"/>
       <c r="Q128" s="2" t="inlineStr">
         <is>
           <t>61.160.298/0001-91</t>
@@ -33197,7 +33165,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1,40727300</t>
+          <t>1,40790100</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -33207,32 +33175,32 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>9,04</t>
+          <t>9,09</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>12,73</t>
+          <t>12,72</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>191,916</t>
+          <t>174,123</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -33257,7 +33225,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-ametista-pj/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-ametista-corporativo-rf-simples</t>
         </is>
       </c>
       <c r="Q129" s="4" t="inlineStr">
@@ -33462,42 +33430,42 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>6,11938600</t>
+          <t>6,12139300</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,032</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,80</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>9,70</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>13,64</t>
+          <t>13,62</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>43,139</t>
+          <t>43,128</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -33723,42 +33691,42 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,34750800</t>
+          <t>3,34901700</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>13,72</t>
+          <t>13,71</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>23,645</t>
+          <t>23,677</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -33985,42 +33953,42 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>5,33259600</t>
+          <t>5,33498800</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>14,18</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>813,489</t>
+          <t>829,104</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -34242,42 +34210,42 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>24,74847800</t>
+          <t>24,78344700</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,141</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>10,69</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>13,79</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>95,472</t>
+          <t>95,607</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -34506,22 +34474,22 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>3,40478700</t>
+          <t>3,40636600</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>9,90</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -34531,17 +34499,17 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>7.768,247</t>
+          <t>7.742,520</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -34767,7 +34735,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1.968,23068700</t>
+          <t>1.969,16787000</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -34777,32 +34745,32 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>10,57</t>
+          <t>10,62</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>17.083,029</t>
+          <t>17.070,257</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -35027,22 +34995,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>5,07990700</t>
+          <t>5,08228000</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>10,22</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -35052,17 +35020,17 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.196,890</t>
+          <t>3.162,254</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -35287,42 +35255,42 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1,61366483</t>
+          <t>1,61444903</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>10,28</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,41</t>
+          <t>14,40</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>379,507</t>
+          <t>379,011</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -35347,7 +35315,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-institucional-soberano-plus-rf-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-institucional-soberano-plus-rf-lp</t>
         </is>
       </c>
       <c r="Q137" s="4" t="inlineStr">
@@ -35531,42 +35499,42 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>5,33875400</t>
+          <t>5,34122900</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>10,33</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,46</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>298,003</t>
+          <t>298,141</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -35788,7 +35756,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>18,65896200</t>
+          <t>18,66798300</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -35798,12 +35766,12 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>10,21</t>
+          <t>10,26</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -35813,17 +35781,17 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>4.889,392</t>
+          <t>4.891,756</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -36032,22 +36000,22 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>9,07132500</t>
+          <t>9,07564600</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>10,20</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -36057,17 +36025,17 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.873,535</t>
+          <t>3.876,464</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -36310,12 +36278,12 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -36338,11 +36306,7 @@
           <t>PJ | RPPS</t>
         </is>
       </c>
-      <c r="P141" s="4" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/caixa-brasil-esmeralda-rf-ref/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P141" s="4" t="inlineStr"/>
       <c r="Q141" s="4" t="inlineStr">
         <is>
           <t>68.375.792/0001-12</t>
@@ -36536,42 +36500,42 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2,93079700</t>
+          <t>2,93205400</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,042</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>9,19</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>12,94</t>
+          <t>12,93</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>13.467,439</t>
+          <t>13.468,430</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -36797,42 +36761,42 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>4,61414500</t>
+          <t>4,61629500</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>10,30</t>
+          <t>10,35</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>14,50</t>
+          <t>14,49</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>17.331,918</t>
+          <t>17.233,803</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -37057,22 +37021,22 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1,43294800</t>
+          <t>1,43369500</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,51</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -37082,17 +37046,17 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>3.476,636</t>
+          <t>3.455,714</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -37313,7 +37277,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1.846,12416300</t>
+          <t>1.847,05087200</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -37323,32 +37287,32 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>10,16</t>
+          <t>10,22</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>14,32</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>1.532,071</t>
+          <t>1.535,426</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -37573,7 +37537,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1,35209900</t>
+          <t>1,35264900</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -37583,12 +37547,12 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,70</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>8,28</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -37598,17 +37562,17 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>33.492,174</t>
+          <t>32.786,670</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -37633,7 +37597,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -37832,42 +37796,42 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>9,74493300</t>
+          <t>9,74920800</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>8,87</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>12,46</t>
+          <t>12,45</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>2.865,026</t>
+          <t>2.755,390</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -38091,22 +38055,22 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2,56628800</t>
+          <t>2,56739400</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,80</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>8,90</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -38116,17 +38080,17 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>17.169,276</t>
+          <t>17.117,249</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -38352,42 +38316,42 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,67126200</t>
+          <t>4,67408500</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,031</t>
+          <t>0,060</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.926,276</t>
+          <t>11.963,080</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -38615,42 +38579,42 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,79346200</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>-0,054</t>
+          <t>3,80066400</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>0,189</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>8,87</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,38</t>
+          <t>12,68</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>1.662,040</t>
+          <t>1.663,299</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -38878,42 +38842,42 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>2,49422500</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>-0,013</t>
+          <t>2,49607300</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>0,074</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>8,30</t>
+          <t>8,38</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>12,17</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>3.277,181</t>
+          <t>3.267,271</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -39143,42 +39107,42 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>3,10706200</t>
+          <t>3,11141300</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,140</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>10,33</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>13,60</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>37,684</t>
+          <t>37,737</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -39399,42 +39363,42 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1.704,65676300</t>
+          <t>1.705,59488800</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,019</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>8,61</t>
+          <t>8,67</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>12,44</t>
+          <t>12,55</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>451,976</t>
+          <t>452,225</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -39459,7 +39423,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-brasil-renda-fixa-ativa-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q153" s="4" t="inlineStr">
@@ -39659,42 +39623,42 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>3,97693100</t>
+          <t>3,98163000</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,118</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>10,47</t>
+          <t>10,60</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,86</t>
+          <t>14,06</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>3.171,422</t>
+          <t>3.166,380</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -39922,42 +39886,42 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>5,35512100</t>
+          <t>5,36541900</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,028</t>
+          <t>0,192</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>2,20</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>8,91</t>
+          <t>9,11</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>12,58</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>2.361,109</t>
+          <t>2.365,223</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -40184,42 +40148,42 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>5,40342300</t>
+          <t>5,41108600</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,141</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>10,68</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>13,98</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>5.848,137</t>
+          <t>5.856,593</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -40446,42 +40410,42 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>4,94281600</t>
+          <t>4,94817700</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>0,021</t>
+          <t>0,108</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>9,50</t>
+          <t>9,62</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>13,50</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>482,699</t>
+          <t>483,722</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -40708,22 +40672,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>8,27015100</t>
+          <t>8,27393700</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -40733,17 +40697,17 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>169,137</t>
+          <t>169,211</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -40828,42 +40792,42 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>3,58335500</t>
+          <t>3,59152000</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>0,014</t>
+          <t>0,227</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>7,40</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>10,88</t>
+          <t>11,15</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>696,043</t>
+          <t>697,629</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -41090,42 +41054,42 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>3,93252700</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>-0,082</t>
+          <t>3,94158200</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>0,230</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>8,39</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>11,70</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>638,189</t>
+          <t>639,658</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -41353,42 +41317,42 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>2,71686800</t>
+          <t>2,71806800</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,90</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>10,31</t>
+          <t>10,36</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>14,50</t>
+          <t>14,49</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>8.726,920</t>
+          <t>8.714,786</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -41413,7 +41377,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-matriz-rf/Paginas/default.aspx</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-matriz-rf/</t>
         </is>
       </c>
       <c r="Q161" s="4" t="inlineStr">
@@ -41617,22 +41581,22 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>7,46688100</t>
+          <t>7,47030300</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>10,13</t>
+          <t>10,18</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -41642,17 +41606,17 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>12.319,686</t>
+          <t>12.304,809</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -41882,7 +41846,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>7,80043600</t>
+          <t>7,80432800</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -41892,32 +41856,32 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>10,10</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>14,23</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>3.833,739</t>
+          <t>3.836,611</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -42142,42 +42106,42 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1,51156900</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>-0,085</t>
+          <t>1,51348700</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>0,126</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>8,40</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>163,063</t>
+          <t>163,270</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -42398,42 +42362,42 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,26176800</t>
+          <t>3,26329000</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>9,62</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>13,43</t>
+          <t>13,42</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>2.202,595</t>
+          <t>2.000,065</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -42686,12 +42650,12 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -42942,12 +42906,12 @@
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -43198,12 +43162,12 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -43454,12 +43418,12 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -43702,12 +43666,12 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -43958,12 +43922,12 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -44184,42 +44148,42 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>7,00494100</t>
+          <t>7,00811400</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>10,37</t>
+          <t>10,42</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>14,56</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>22.374,949</t>
+          <t>22.246,913</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -44304,42 +44268,42 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>5,73958900</t>
+          <t>5,75103200</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>0,023</t>
+          <t>0,199</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>9,19</t>
+          <t>9,41</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>12,63</t>
+          <t>12,85</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>594,653</t>
+          <t>595,838</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -44595,12 +44559,12 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -44625,7 +44589,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/rpps/brasil-estrategia-livre-mm-lp</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -44817,42 +44781,42 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>4,11927400</t>
+          <t>4,10832500</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>-0,975</t>
+          <t>-0,265</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>13,77</t>
+          <t>13,47</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>25,00</t>
+          <t>25,67</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>301,844</t>
+          <t>301,072</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -45077,42 +45041,42 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>3,78119000</t>
+          <t>3,77194600</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>-0,911</t>
+          <t>-0,244</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>13,13</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>24,61</t>
+          <t>25,16</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>7,881</t>
+          <t>7,862</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -45337,42 +45301,42 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>12,09632760</t>
+          <t>12,13291673</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>0,610</t>
+          <t>0,302</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>2,70</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>9,30</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>16,91</t>
+          <t>17,05</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>2.416,123</t>
+          <t>2.423,404</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -45597,42 +45561,42 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>2,10180000</t>
+          <t>2,09716100</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>-0,763</t>
+          <t>-0,220</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>3,51</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>10,88</t>
+          <t>10,64</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>19,71</t>
+          <t>20,42</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>205,265</t>
+          <t>204,812</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -45853,42 +45817,42 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>2,06199100</t>
+          <t>2,04952500</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>-0,858</t>
+          <t>-0,604</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>8,72</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>727,748</t>
+          <t>723,348</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -46113,42 +46077,42 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>3,58923016</t>
+          <t>3,57652429</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>-0,981</t>
+          <t>-0,353</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>9,93</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>17,79</t>
+          <t>18,58</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>1.342,524</t>
+          <t>1.337,772</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -46365,42 +46329,42 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>2,60331845</t>
+          <t>2,59377275</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>-1,027</t>
+          <t>-0,366</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>3,62</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>10,14</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>18,07</t>
+          <t>18,63</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>787,938</t>
+          <t>785,049</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -46617,42 +46581,42 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>3,90795900</t>
+          <t>3,91040500</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>0,033</t>
+          <t>0,062</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>14,18</t>
+          <t>14,20</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>4.520,312</t>
+          <t>4.526,162</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y3" s="4" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-movimentacoes-automaticas-curto-prazo/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-movimentacoes-automaticas-rf-simples/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-plus-mm-credito-privado-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-plus-rf-credito-privado-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>09.548.729/0001-71</t>
+          <t>03.191.874/0001-61</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>46</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
@@ -3604,27 +3604,27 @@
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
+          <t>100000.0</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Y13" s="4" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB13" s="4" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>IPCA+6%</t>
         </is>
       </c>
       <c r="AC13" s="4" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>["Pessoa Física"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AM13" s="4" t="inlineStr">
         <is>
-          <t>["Pessoa Física"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AN13" s="4" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AR13" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FOCO ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA PATRIMÔNIO ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
         </is>
       </c>
       <c r="AS13" s="4" t="inlineStr">
@@ -3730,43 +3730,43 @@
       </c>
       <c r="AT13" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5414.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0046.pdf</t>
         </is>
       </c>
       <c r="AU13" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5414.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0046.pdf</t>
         </is>
       </c>
       <c r="AV13" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0046.pdf</t>
         </is>
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_46.pdf</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_46.pdf</t>
         </is>
       </c>
       <c r="AY13" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_46.pdf</t>
         </is>
       </c>
       <c r="AZ13" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5414.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0046.pdf</t>
         </is>
       </c>
       <c r="BA13" s="4" t="inlineStr"/>
       <c r="BB13" s="4" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/a5ab94de-1f04-4f00-87d2-ffa0c6babbaf?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/140b7682-00df-491d-b451-73ae70a040fa?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,11 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-smart-infraestrutura-debincentivadas-cdi-rf-cred-priv-lp-subclasse-varejo/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>67.702.501/0001-90</t>
@@ -7466,15 +7470,19 @@
           <t>PF | PJ | RPPS</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-vinland-debenture-incentivado/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>58.113.332/0001-62</t>
+          <t>10.646.888/0001-98</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -7484,7 +7492,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7514,22 +7522,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>D+13 (du)</t>
+          <t>D+0 (du)</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>D+15 (du)</t>
+          <t>D+00 (du)</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>RF Crédito Privado permite Risco Mercado</t>
+          <t>RF Crédito Privado sem Risco Mercado</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -7549,33 +7557,37 @@
       </c>
       <c r="AG28" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AH28" s="2" t="inlineStr">
         <is>
-          <t>13h00</t>
+          <t>17h00</t>
         </is>
       </c>
       <c r="AI28" s="2" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Sim · Automatico · 90%</t>
         </is>
       </c>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
-        </is>
-      </c>
-      <c r="AK28" s="2" t="inlineStr"/>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AL28" s="2" t="inlineStr">
         <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+          <t>["Pessoa Física", "PJ Varejo", "Private"]</t>
         </is>
       </c>
       <c r="AM28" s="2" t="inlineStr">
         <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+          <t>["Pessoa Física", "PJ Varejo", "Private"]</t>
         </is>
       </c>
       <c r="AN28" s="2" t="inlineStr">
@@ -7596,43 +7608,47 @@
       </c>
       <c r="AR28" s="2" t="inlineStr">
         <is>
-          <t>CAIXA EXPERT SULAMÉRICA CRÉDITO ATIVO FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CRÉDITO PRIVADO LONGO PR</t>
-        </is>
-      </c>
-      <c r="AS28" s="2" t="inlineStr"/>
+          <t>CAIXA EXPERTISE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CRÉDITO PRIVADO LONGO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS28" s="2" t="inlineStr">
+        <is>
+          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
       <c r="AT28" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7931.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5156.pdf</t>
         </is>
       </c>
       <c r="AU28" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7931.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5156.pdf</t>
         </is>
       </c>
       <c r="AV28" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7931.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5156.pdf</t>
         </is>
       </c>
       <c r="AW28" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7931.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5156.pdf</t>
         </is>
       </c>
       <c r="AX28" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7931.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5156.pdf</t>
         </is>
       </c>
       <c r="AY28" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7931.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5156.pdf</t>
         </is>
       </c>
       <c r="AZ28" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7931.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5156.pdf</t>
         </is>
       </c>
       <c r="BA28" s="2" t="inlineStr"/>
@@ -7714,7 +7730,11 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-arx-ipca-deb-incentivadas-rf-cred-priv-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>60.138.811/0001-85</t>
@@ -8986,7 +9006,11 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/debentures-incentivadas/caixa-expert-rb-asset-deb-incentivadas-cdi-rf-cred-priv/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>62.890.286/0001-85</t>
@@ -9236,7 +9260,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-unique-private-cred-priv-lp</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-unique-private-cred-priv-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -9496,7 +9520,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fif-inflacao-2027</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fif-inflacao-2027/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10017,7 +10041,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-qualificado-rf-credito-privado-longo-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-plus-qualificado-rf-credito-privado-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10920,11 +10944,7 @@
           <t>CAIXA INDEXA TESOURO SELIC FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO – RESP LIMITADA</t>
         </is>
       </c>
-      <c r="AS41" s="4" t="inlineStr">
-        <is>
-          <t>OBS: Limite máximo por CPF - R$ 100.000,00</t>
-        </is>
-      </c>
+      <c r="AS41" s="4" t="inlineStr"/>
       <c r="AT41" s="4" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5940.pdf</t>
@@ -11041,7 +11061,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-renda-fixa-ativa-lp</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-renda-fixa-ativa-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11963,8 +11983,7 @@
       </c>
       <c r="AS45" s="4" t="inlineStr">
         <is>
-          <t>Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social). Há incidência de taxa de saída no Fundo, conforme exposto no Regulamento.
-Aberto para novas aplicações a partir de 01/12/2025, inclusive.</t>
+          <t>Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social). Há incidência de taxa de saída no Fundo, conforme exposto no Regulamento.</t>
         </is>
       </c>
       <c r="AT45" s="4" t="inlineStr">
@@ -12903,7 +12922,7 @@
       </c>
       <c r="X49" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y49" s="4" t="inlineStr">
@@ -13383,17 +13402,17 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/referenciados/fic-sigma-ref-di-longo-prazo</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-omega-private-ref-di-longo-prazo</t>
         </is>
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>10.731.794/0001-17</t>
+          <t>55.036.101/0001-04</t>
         </is>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="S51" s="4" t="inlineStr">
@@ -13403,12 +13422,12 @@
       </c>
       <c r="T51" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="U51" s="4" t="inlineStr">
         <is>
-          <t>50000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="V51" s="4" t="inlineStr">
@@ -13423,7 +13442,7 @@
       </c>
       <c r="X51" s="4" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="Y51" s="4" t="inlineStr">
@@ -13443,7 +13462,7 @@
       </c>
       <c r="AB51" s="4" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>OUTROS</t>
         </is>
       </c>
       <c r="AC51" s="4" t="inlineStr">
@@ -13493,12 +13512,12 @@
       </c>
       <c r="AL51" s="4" t="inlineStr">
         <is>
-          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+          <t>["Private"]</t>
         </is>
       </c>
       <c r="AM51" s="4" t="inlineStr">
         <is>
-          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+          <t>["Private"]</t>
         </is>
       </c>
       <c r="AN51" s="4" t="inlineStr">
@@ -13519,51 +13538,52 @@
       </c>
       <c r="AR51" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SIGMA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS51" s="4" t="inlineStr"/>
+          <t>CAIXA SIGMA PRIVATE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REF DI LONGO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS51" s="4" t="inlineStr">
+        <is>
+          <t>A movimentação do fundo é feita exclusivamente pela plataforma.caixa ou IBC/APP.
+Fundo teve alteração de nomenclatura a partir de 21/09/2026 de CAIXA ÔMEGA PRIVATE para CAIXA SIGMA PRIVATE.</t>
+        </is>
+      </c>
       <c r="AT51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5171.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7914.pdf</t>
         </is>
       </c>
       <c r="AU51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5171.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7914.pdf</t>
         </is>
       </c>
       <c r="AV51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5171.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7914.pdf</t>
         </is>
       </c>
       <c r="AW51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5171.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7914.pdf</t>
         </is>
       </c>
       <c r="AX51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5171.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7914.pdf</t>
         </is>
       </c>
       <c r="AY51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5171.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7914.pdf</t>
         </is>
       </c>
       <c r="AZ51" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5171.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7914.pdf</t>
         </is>
       </c>
       <c r="BA51" s="4" t="inlineStr"/>
-      <c r="BB51" s="4" t="inlineStr">
-        <is>
-          <t>https://web.microsoftstream.com/video/4be15710-4acb-4afd-a959-c6ed0d090cac?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
-        </is>
-      </c>
+      <c r="BB51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -14044,10 +14064,14 @@
       </c>
       <c r="AR53" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SIGMA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS53" s="4" t="inlineStr"/>
+          <t>CAIXA SIGMA SINGULAR FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REF DI LONGO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS53" s="4" t="inlineStr">
+        <is>
+          <t>Fundo teve alteração de nomenclatura a partir de 21/09/2026 de CAIXA SIGMA para CAIXA SIGMA SINGULAR</t>
+        </is>
+      </c>
       <c r="AT53" s="4" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5171.pdf</t>
@@ -14690,7 +14714,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/voce/renda-fixa/caixa-turquesa-pj/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q56" s="2" t="inlineStr"/>
       <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr"/>
@@ -16088,7 +16116,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-short-mm</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-short-mm/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -16344,7 +16372,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-long-bias-mm</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
@@ -16852,7 +16880,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -19440,19 +19468,15 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P75" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
-        </is>
-      </c>
+      <c r="P75" s="4" t="inlineStr"/>
       <c r="Q75" s="4" t="inlineStr">
         <is>
-          <t>34.660.333/0001-69</t>
+          <t>35.536.472/0001-48</t>
         </is>
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="S75" s="4" t="inlineStr">
@@ -19462,7 +19486,7 @@
       </c>
       <c r="T75" s="4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="U75" s="4" t="inlineStr">
@@ -19550,16 +19574,8 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AL75" s="4" t="inlineStr">
-        <is>
-          <t>["Pessoa Física", "Private"]</t>
-        </is>
-      </c>
-      <c r="AM75" s="4" t="inlineStr">
-        <is>
-          <t>["Pessoa Física", "Private"]</t>
-        </is>
-      </c>
+      <c r="AL75" s="4" t="inlineStr"/>
+      <c r="AM75" s="4" t="inlineStr"/>
       <c r="AN75" s="4" t="inlineStr">
         <is>
           <t>Não</t>
@@ -19578,43 +19594,47 @@
       </c>
       <c r="AR75" s="4" t="inlineStr">
         <is>
-          <t>CAIXA ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITA</t>
-        </is>
-      </c>
-      <c r="AS75" s="4" t="inlineStr"/>
+          <t>CAIXA FUNCIONÁRIOS ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABI</t>
+        </is>
+      </c>
+      <c r="AS75" s="4" t="inlineStr">
+        <is>
+          <t>Fundo destinado a Funcionários e aposentados da Caixa Econômica Federal. Disponível para aplicação somente via conta corrente marcada como conta-salário empregado CAIXA.</t>
+        </is>
+      </c>
       <c r="AT75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6440.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6479.pdf</t>
         </is>
       </c>
       <c r="AU75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6440.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6479.pdf</t>
         </is>
       </c>
       <c r="AV75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6440.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6479.pdf</t>
         </is>
       </c>
       <c r="AW75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6440.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6479.pdf</t>
         </is>
       </c>
       <c r="AX75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6440.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6479.pdf</t>
         </is>
       </c>
       <c r="AY75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6440.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6479.pdf</t>
         </is>
       </c>
       <c r="AZ75" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6440.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6479.pdf</t>
         </is>
       </c>
       <c r="BA75" s="4" t="inlineStr"/>
@@ -20481,7 +20501,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa_fic_fim_cap_protegido_cesta_agro</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa_fic_fim_cap_protegido_cesta_agro/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -20606,7 +20626,7 @@
       </c>
       <c r="AO79" s="4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AP79" s="4" t="inlineStr">
@@ -22840,7 +22860,11 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fic-fif-quantitativo-low-vol/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr"/>
       <c r="S88" s="2" t="inlineStr"/>
@@ -22958,7 +22982,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fic-fia-compromisso-bdr-nivel-i</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/FIA-Institucional-BDR-nivel-I/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -23214,7 +23238,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-ibovespa</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fi-acoes-brasil-etf-bovespa/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -26587,7 +26611,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/Caixa-FI-Acoes-Banco-do-Brasil-Plus/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/Caixa-FI-Acoes-Banco-do-Brasil-Plus/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q103" s="4" t="inlineStr">
@@ -28913,7 +28937,11 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="P112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/fia-caixa-seguridade/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
           <t>59.815.671/0001-53</t>
@@ -31481,17 +31509,17 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-1</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>04.885.818/0001-90</t>
+          <t>04.885.824/0001-47</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
@@ -31501,12 +31529,12 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="U122" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="V122" s="2" t="inlineStr">
@@ -31601,7 +31629,7 @@
       </c>
       <c r="AR122" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - VALE DO RIO DOCE I - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - VALE DO RIO DOCE II - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS122" s="2" t="inlineStr">
@@ -31611,37 +31639,37 @@
       </c>
       <c r="AT122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5206.pdf</t>
         </is>
       </c>
       <c r="AU122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5206.pdf</t>
         </is>
       </c>
       <c r="AV122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5206.pdf</t>
         </is>
       </c>
       <c r="AW122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5206.pdf</t>
         </is>
       </c>
       <c r="AX122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5206.pdf</t>
         </is>
       </c>
       <c r="AY122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
       <c r="AZ122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5206.pdf</t>
         </is>
       </c>
       <c r="BA122" s="2" t="inlineStr"/>
@@ -32476,17 +32504,17 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-1</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>04.885.818/0001-90</t>
+          <t>04.885.824/0001-47</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="S126" s="2" t="inlineStr">
@@ -32496,12 +32524,12 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="U126" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="V126" s="2" t="inlineStr">
@@ -32596,7 +32624,7 @@
       </c>
       <c r="AR126" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - VALE DO RIO DOCE I - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - VALE DO RIO DOCE II - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS126" s="2" t="inlineStr">
@@ -32606,37 +32634,37 @@
       </c>
       <c r="AT126" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5206.pdf</t>
         </is>
       </c>
       <c r="AU126" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5206.pdf</t>
         </is>
       </c>
       <c r="AV126" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5206.pdf</t>
         </is>
       </c>
       <c r="AW126" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5206.pdf</t>
         </is>
       </c>
       <c r="AX126" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5206.pdf</t>
         </is>
       </c>
       <c r="AY126" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
       <c r="AZ126" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5206.pdf</t>
         </is>
       </c>
       <c r="BA126" s="2" t="inlineStr"/>
@@ -32966,7 +32994,11 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="P128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>http://site.extra.caixa.gov.br/fundos-investimento/fundo-simples/fic-azulzinha-rf-simples/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
           <t>61.160.298/0001-91</t>
@@ -33225,7 +33257,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-ametista-corporativo-rf-simples</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundo-simples/fic-ametista-pj/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q129" s="4" t="inlineStr">
@@ -33631,8 +33663,7 @@
       </c>
       <c r="AS130" s="2" t="inlineStr">
         <is>
-          <t>*Nome alterado de CAIXA FIC FORTALECER RF LONGO PRAZO para CAIXA FIC EQUILIBRIO MPE RF LONGO PRAZO, em 15 JAN 2024, conforme aprovado em Assembleia Geral de Cotistas.
-Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+          <t>Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
         </is>
       </c>
       <c r="AT130" s="2" t="inlineStr">
@@ -34574,7 +34605,7 @@
       </c>
       <c r="X134" s="2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y134" s="2" t="inlineStr">
@@ -35315,7 +35346,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-institucional-soberano-plus-rf-lp</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fic-institucional-soberano-plus-rf-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q137" s="4" t="inlineStr">
@@ -36306,7 +36337,11 @@
           <t>PJ | RPPS</t>
         </is>
       </c>
-      <c r="P141" s="4" t="inlineStr"/>
+      <c r="P141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/caixa-brasil-esmeralda-rf-ref/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q141" s="4" t="inlineStr">
         <is>
           <t>68.375.792/0001-12</t>
@@ -36600,7 +36635,7 @@
       </c>
       <c r="X142" s="2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y142" s="2" t="inlineStr">
@@ -36846,7 +36881,7 @@
       </c>
       <c r="U143" s="4" t="inlineStr">
         <is>
-          <t>3000000.0</t>
+          <t>1000000.0</t>
         </is>
       </c>
       <c r="V143" s="4" t="inlineStr">
@@ -36861,7 +36896,7 @@
       </c>
       <c r="X143" s="4" t="inlineStr">
         <is>
-          <t>300000.0</t>
+          <t>100000.0</t>
         </is>
       </c>
       <c r="Y143" s="4" t="inlineStr">
@@ -36960,7 +36995,15 @@
           <t>CAIXA TOPÁZIO CORPORATIVO FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
-      <c r="AS143" s="4" t="inlineStr"/>
+      <c r="AS143" s="4" t="inlineStr">
+        <is>
+          <t>Fundo em Campanha - Período 21/09/2026 à 30/12/2026
+Redução de Ticket
+Aplicação Inicial: De R$ 3.000.000,00 Para R$ 1.000.000,00
+Saldo Mínimo: De R$ 300.000,00 Para R$ 100.000,00
+"Fundos de Investimento que estiveram em Campanha, após a Campanha, voltam aos parâmetros originais. Saldo abaixo do mínimo pode impedir resgates parciais (somente total)."</t>
+        </is>
+      </c>
       <c r="AT143" s="4" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5189.pdf</t>
@@ -37447,12 +37490,12 @@
       </c>
       <c r="AL145" s="4" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado"]</t>
+          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
         </is>
       </c>
       <c r="AM145" s="4" t="inlineStr">
         <is>
-          <t>["Institucional", "PJ Atacado"]</t>
+          <t>["Institucional", "PJ Atacado", "PJ Varejo"]</t>
         </is>
       </c>
       <c r="AN145" s="4" t="inlineStr">
@@ -37597,7 +37640,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -38381,12 +38424,12 @@
       </c>
       <c r="Q149" s="4" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="R149" s="4" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="S149" s="4" t="inlineStr">
@@ -38436,7 +38479,7 @@
       </c>
       <c r="AB149" s="4" t="inlineStr">
         <is>
-          <t>IRF-M TOTAL</t>
+          <t>IRF-M 1</t>
         </is>
       </c>
       <c r="AC149" s="4" t="inlineStr">
@@ -38461,17 +38504,17 @@
       </c>
       <c r="AG149" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AH149" s="4" t="inlineStr">
         <is>
-          <t>16h00</t>
+          <t>17h00</t>
         </is>
       </c>
       <c r="AI149" s="4" t="inlineStr">
         <is>
-          <t>Sim · Automatico · 90%</t>
+          <t>Sim · Automatico · 95%</t>
         </is>
       </c>
       <c r="AJ149" s="4" t="inlineStr">
@@ -38481,7 +38524,7 @@
       </c>
       <c r="AK149" s="4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AL149" s="4" t="inlineStr">
@@ -38512,54 +38555,58 @@
       </c>
       <c r="AR149" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IRF-M TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA BRASIL IRF-M 1 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS149" s="4" t="inlineStr">
         <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Renda Fixa de Mercado (IRF-M).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.
+          <t>1.O Fundo tem como parâmetro de rentabilidade o Índice de Renda Fixa de Mercado 1 (IRF-M 1).
+2.Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
+3.O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.
 ¹Condições excepcionais de estorno e movimentação retroativa estão descritas no TE099.</t>
         </is>
       </c>
       <c r="AT149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="AU149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="AV149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="AW149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="AX149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="AY149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
       <c r="AZ149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5464.pdf</t>
         </is>
       </c>
       <c r="BA149" s="4" t="inlineStr"/>
-      <c r="BB149" s="4" t="inlineStr"/>
+      <c r="BB149" s="4" t="inlineStr">
+        <is>
+          <t>https://web.microsoftstream.com/video/e092ed57-1ff7-4570-9897-57fc78b1a0c8?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -38644,12 +38691,12 @@
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="R150" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="S150" s="2" t="inlineStr">
@@ -38699,7 +38746,7 @@
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>IRF-M TOTAL</t>
+          <t>IRF-M 1</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
@@ -38724,17 +38771,17 @@
       </c>
       <c r="AG150" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AH150" s="2" t="inlineStr">
         <is>
-          <t>16h00</t>
+          <t>17h00</t>
         </is>
       </c>
       <c r="AI150" s="2" t="inlineStr">
         <is>
-          <t>Sim · Automatico · 90%</t>
+          <t>Sim · Automatico · 95%</t>
         </is>
       </c>
       <c r="AJ150" s="2" t="inlineStr">
@@ -38744,7 +38791,7 @@
       </c>
       <c r="AK150" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AL150" s="2" t="inlineStr">
@@ -38775,54 +38822,58 @@
       </c>
       <c r="AR150" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IRF-M TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA BRASIL IRF-M 1 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS150" s="2" t="inlineStr">
         <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Renda Fixa de Mercado (IRF-M).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.
+          <t>1.O Fundo tem como parâmetro de rentabilidade o Índice de Renda Fixa de Mercado 1 (IRF-M 1).
+2.Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
+3.O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.
 ¹Condições excepcionais de estorno e movimentação retroativa estão descritas no TE099.</t>
         </is>
       </c>
       <c r="AT150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="AU150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="AV150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="AW150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="AX150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="AY150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
       <c r="AZ150" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5464.pdf</t>
         </is>
       </c>
       <c r="BA150" s="2" t="inlineStr"/>
-      <c r="BB150" s="2" t="inlineStr"/>
+      <c r="BB150" s="2" t="inlineStr">
+        <is>
+          <t>https://web.microsoftstream.com/video/e092ed57-1ff7-4570-9897-57fc78b1a0c8?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -39423,7 +39474,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/caixa-fic-brasil-renda-fixa-ativa-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/brasil-IPCA/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q153" s="4" t="inlineStr">
@@ -39951,12 +40002,12 @@
       </c>
       <c r="Q155" s="4" t="inlineStr">
         <is>
-          <t>10.577.503/0001-88</t>
+          <t>11.060.913/0001-10</t>
         </is>
       </c>
       <c r="R155" s="4" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="S155" s="4" t="inlineStr">
@@ -40006,7 +40057,7 @@
       </c>
       <c r="AB155" s="4" t="inlineStr">
         <is>
-          <t>IMA-B 5+</t>
+          <t>IMA-B 5</t>
         </is>
       </c>
       <c r="AC155" s="4" t="inlineStr">
@@ -40082,49 +40133,43 @@
       </c>
       <c r="AR155" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IMA B 5+ TITULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS155" s="4" t="inlineStr">
-        <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Mercado da ANBIMA B 5 (IMA-B 5).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
-        </is>
-      </c>
+          <t>CAIXA BRASIL IMA-B 5 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS155" s="4" t="inlineStr"/>
       <c r="AT155" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5187.pdf</t>
         </is>
       </c>
       <c r="AU155" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5187.pdf</t>
         </is>
       </c>
       <c r="AV155" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5187.pdf</t>
         </is>
       </c>
       <c r="AW155" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5187.pdf</t>
         </is>
       </c>
       <c r="AX155" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5187.pdf</t>
         </is>
       </c>
       <c r="AY155" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5187.pdf</t>
         </is>
       </c>
       <c r="AZ155" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5187.pdf</t>
         </is>
       </c>
       <c r="BA155" s="4" t="inlineStr"/>
@@ -40213,12 +40258,12 @@
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>10.577.503/0001-88</t>
+          <t>11.060.913/0001-10</t>
         </is>
       </c>
       <c r="R156" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="S156" s="2" t="inlineStr">
@@ -40268,7 +40313,7 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>IMA-B 5+</t>
+          <t>IMA-B 5</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
@@ -40344,49 +40389,43 @@
       </c>
       <c r="AR156" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IMA B 5+ TITULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS156" s="2" t="inlineStr">
-        <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Mercado da ANBIMA B 5 (IMA-B 5).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
-        </is>
-      </c>
+          <t>CAIXA BRASIL IMA-B 5 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS156" s="2" t="inlineStr"/>
       <c r="AT156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5187.pdf</t>
         </is>
       </c>
       <c r="AU156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5187.pdf</t>
         </is>
       </c>
       <c r="AV156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5187.pdf</t>
         </is>
       </c>
       <c r="AW156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5187.pdf</t>
         </is>
       </c>
       <c r="AX156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5187.pdf</t>
         </is>
       </c>
       <c r="AY156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5187.pdf</t>
         </is>
       </c>
       <c r="AZ156" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5187.pdf</t>
         </is>
       </c>
       <c r="BA156" s="2" t="inlineStr"/>
@@ -40857,12 +40896,12 @@
       </c>
       <c r="Q159" s="4" t="inlineStr">
         <is>
-          <t>10.577.503/0001-88</t>
+          <t>11.060.913/0001-10</t>
         </is>
       </c>
       <c r="R159" s="4" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="S159" s="4" t="inlineStr">
@@ -40912,7 +40951,7 @@
       </c>
       <c r="AB159" s="4" t="inlineStr">
         <is>
-          <t>IMA-B 5+</t>
+          <t>IMA-B 5</t>
         </is>
       </c>
       <c r="AC159" s="4" t="inlineStr">
@@ -40988,49 +41027,43 @@
       </c>
       <c r="AR159" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IMA B 5+ TITULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS159" s="4" t="inlineStr">
-        <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Mercado da ANBIMA B 5 (IMA-B 5).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
-        </is>
-      </c>
+          <t>CAIXA BRASIL IMA-B 5 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS159" s="4" t="inlineStr"/>
       <c r="AT159" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5187.pdf</t>
         </is>
       </c>
       <c r="AU159" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5187.pdf</t>
         </is>
       </c>
       <c r="AV159" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5187.pdf</t>
         </is>
       </c>
       <c r="AW159" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5187.pdf</t>
         </is>
       </c>
       <c r="AX159" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5187.pdf</t>
         </is>
       </c>
       <c r="AY159" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5187.pdf</t>
         </is>
       </c>
       <c r="AZ159" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5187.pdf</t>
         </is>
       </c>
       <c r="BA159" s="4" t="inlineStr"/>
@@ -41119,12 +41152,12 @@
       </c>
       <c r="Q160" s="2" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="R160" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="S160" s="2" t="inlineStr">
@@ -41174,7 +41207,7 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>IRF-M TOTAL</t>
+          <t>IRF-M 1</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
@@ -41199,17 +41232,17 @@
       </c>
       <c r="AG160" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AH160" s="2" t="inlineStr">
         <is>
-          <t>16h00</t>
+          <t>17h00</t>
         </is>
       </c>
       <c r="AI160" s="2" t="inlineStr">
         <is>
-          <t>Sim · Automatico · 90%</t>
+          <t>Sim · Automatico · 95%</t>
         </is>
       </c>
       <c r="AJ160" s="2" t="inlineStr">
@@ -41219,7 +41252,7 @@
       </c>
       <c r="AK160" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AL160" s="2" t="inlineStr">
@@ -41250,54 +41283,58 @@
       </c>
       <c r="AR160" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IRF-M TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA BRASIL IRF-M 1 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS160" s="2" t="inlineStr">
         <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Renda Fixa de Mercado (IRF-M).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.
+          <t>1.O Fundo tem como parâmetro de rentabilidade o Índice de Renda Fixa de Mercado 1 (IRF-M 1).
+2.Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
+3.O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.
 ¹Condições excepcionais de estorno e movimentação retroativa estão descritas no TE099.</t>
         </is>
       </c>
       <c r="AT160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="AU160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="AV160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="AW160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="AX160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="AY160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
       <c r="AZ160" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5464.pdf</t>
         </is>
       </c>
       <c r="BA160" s="2" t="inlineStr"/>
-      <c r="BB160" s="2" t="inlineStr"/>
+      <c r="BB160" s="2" t="inlineStr">
+        <is>
+          <t>https://web.microsoftstream.com/video/e092ed57-1ff7-4570-9897-57fc78b1a0c8?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -41377,7 +41414,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-matriz-rf/</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-brasil-matriz-rf/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q161" s="4" t="inlineStr">
@@ -41646,12 +41683,12 @@
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t>03.737.206/0001-97</t>
+          <t>05.164.356/0001-84</t>
         </is>
       </c>
       <c r="R162" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="S162" s="2" t="inlineStr">
@@ -41706,7 +41743,7 @@
       </c>
       <c r="AC162" s="2" t="inlineStr">
         <is>
-          <t>RF DI até 49% Crédito Privado</t>
+          <t>RF 100% TPF - Longo Prazo</t>
         </is>
       </c>
       <c r="AD162" s="2" t="inlineStr">
@@ -41777,54 +41814,53 @@
       </c>
       <c r="AR162" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA BRASIL TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS162" s="2" t="inlineStr">
         <is>
-          <t>1. Para aplicação por meio de conta operação 003, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-2. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 003, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
+          <t>Para aplicação no fundo é necessário o cadastramento prévio de cotistas, conforme descrito no FI657. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação, mesmo para os clientes que já realizaram o cadsatramento anteriormente.</t>
         </is>
       </c>
       <c r="AT162" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5404.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5462.pdf</t>
         </is>
       </c>
       <c r="AU162" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5404.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5462.pdf</t>
         </is>
       </c>
       <c r="AV162" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5462.pdf</t>
         </is>
       </c>
       <c r="AW162" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5462.pdf</t>
         </is>
       </c>
       <c r="AX162" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5462.pdf</t>
         </is>
       </c>
       <c r="AY162" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5462.pdf</t>
         </is>
       </c>
       <c r="AZ162" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5462.pdf</t>
         </is>
       </c>
       <c r="BA162" s="2" t="inlineStr"/>
       <c r="BB162" s="2" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/f88f1fc7-aac3-44df-a2a5-ce3ac05edfb3?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/91aaf70b-85c2-4cf1-b537-e42b3bd894ec?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -42691,7 +42727,7 @@
       </c>
       <c r="S166" s="2" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="T166" s="2" t="inlineStr">
@@ -42947,7 +42983,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="T167" s="4" t="inlineStr">
@@ -43203,7 +43239,7 @@
       </c>
       <c r="S168" s="2" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="T168" s="2" t="inlineStr">
@@ -43548,8 +43584,16 @@
         </is>
       </c>
       <c r="AK169" s="4" t="inlineStr"/>
-      <c r="AL169" s="4" t="inlineStr"/>
-      <c r="AM169" s="4" t="inlineStr"/>
+      <c r="AL169" s="4" t="inlineStr">
+        <is>
+          <t>["GOV", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AM169" s="4" t="inlineStr">
+        <is>
+          <t>["GOV", "RPPS"]</t>
+        </is>
+      </c>
       <c r="AN169" s="4" t="inlineStr">
         <is>
           <t>Não</t>
@@ -43707,7 +43751,7 @@
       </c>
       <c r="S170" s="2" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="T170" s="2" t="inlineStr">
@@ -43963,7 +44007,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>Conservador</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="T171" s="4" t="inlineStr">
@@ -44589,7 +44633,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/rpps/brasil-estrategia-livre-mm-lp</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -44846,12 +44890,12 @@
       </c>
       <c r="Q175" s="4" t="inlineStr">
         <is>
-          <t>15.154.236/0001-50</t>
+          <t>13.058.816/0001-18</t>
         </is>
       </c>
       <c r="R175" s="4" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="S175" s="4" t="inlineStr">
@@ -44911,7 +44955,7 @@
       </c>
       <c r="AD175" s="4" t="inlineStr">
         <is>
-          <t>Fechado para captação</t>
+          <t>Aberto para captação</t>
         </is>
       </c>
       <c r="AE175" s="4" t="inlineStr">
@@ -44977,47 +45021,43 @@
       </c>
       <c r="AR175" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL ETF IBOVESPA FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS175" s="4" t="inlineStr">
-        <is>
-          <t>Fundo fechado para novas aplicações, a novos investidores e cotistas atuais a partir de 03/04/2023 (inclusive)</t>
-        </is>
-      </c>
+          <t>CAIXA BRASIL INDEXA IBOVESPA FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS175" s="4" t="inlineStr"/>
       <c r="AT175" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5842.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5445.pdf</t>
         </is>
       </c>
       <c r="AU175" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5842.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5445.pdf</t>
         </is>
       </c>
       <c r="AV175" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5445.pdf</t>
         </is>
       </c>
       <c r="AW175" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5445.pdf</t>
         </is>
       </c>
       <c r="AX175" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5445.pdf</t>
         </is>
       </c>
       <c r="AY175" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5445.pdf</t>
         </is>
       </c>
       <c r="AZ175" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5445.pdf</t>
         </is>
       </c>
       <c r="BA175" s="4" t="inlineStr"/>

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -814,42 +814,42 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,35259400</t>
+          <t>2,35355700</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,040</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>9,52</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,42</t>
+          <t>12,41</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>400,300</t>
+          <t>400,654</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1074,42 +1074,42 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,71420300</t>
+          <t>5,71667400</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>12,20</t>
+          <t>12,19</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.555,517</t>
+          <t>6.568,202</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -1334,42 +1334,42 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,88518200</t>
+          <t>2,88643000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>9,30</t>
+          <t>9,35</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>12,19</t>
+          <t>12,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>746,059</t>
+          <t>816,720</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1593,42 +1593,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,64063300</t>
+          <t>3,64201300</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>10,58</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>13,82</t>
+          <t>13,80</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>119,934</t>
+          <t>119,840</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1856,42 +1856,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,10522300</t>
+          <t>10,10863000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,037</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>12,90</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>592,023</t>
+          <t>591,643</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2116,42 +2116,42 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>3,47994500</t>
+          <t>3,48156500</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>10,44</t>
+          <t>10,49</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>13,65</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12,569</t>
+          <t>12,587</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21,46113900</t>
+          <t>21,45930200</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>-0,482</t>
+          <t>-0,008</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>11,97</t>
+          <t>11,96</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>15,39</t>
+          <t>15,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>119,202</t>
+          <t>119,345</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2640,42 +2640,42 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,50407100</t>
+          <t>3,50536000</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,040</t>
+          <t>0,036</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>10,51</t>
+          <t>10,55</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>13,76</t>
+          <t>13,74</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>64,146</t>
+          <t>64,092</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2896,42 +2896,42 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1.921,36994700</t>
+          <t>1.922,33730500</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>10,93</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,624</t>
+          <t>98,727</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3156,42 +3156,42 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>3,13703400</t>
+          <t>3,13856300</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>11,00</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>14,39</t>
+          <t>14,38</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>1.728,465</t>
+          <t>1.729,427</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3528,42 +3528,42 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>14,32405700</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>-0,072</t>
+          <t>14,32995300</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>11,39</t>
+          <t>11,43</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>14,51</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>28,596</t>
+          <t>28,609</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4044,42 +4044,42 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>48,05415800</t>
+          <t>48,07030000</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>0,037</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,86</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,84</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>41,682</t>
+          <t>41,696</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4305,42 +4305,42 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21,03024800</t>
+          <t>21,03660600</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,030</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>12,62</t>
+          <t>12,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,357</t>
+          <t>59,373</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4565,42 +4565,42 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>15,57220100</t>
+          <t>15,57748400</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,037</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,93</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>12,95</t>
+          <t>12,93</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>28,251</t>
+          <t>28,259</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4825,42 +4825,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,34985600</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>-0,069</t>
+          <t>3,35132700</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>12,78</t>
+          <t>12,83</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>15,88</t>
+          <t>15,90</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,342</t>
+          <t>79,377</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5089,42 +5089,42 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,11954000</t>
+          <t>3,12055300</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,036</t>
+          <t>0,032</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>12,54</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1,671</t>
+          <t>1,672</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,57861800</t>
+          <t>3,57840400</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>-0,455</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -5360,27 +5360,27 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>12,28</t>
+          <t>12,27</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>15,78</t>
+          <t>15,64</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>130,120</t>
+          <t>130,210</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5609,42 +5609,42 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,66275900</t>
+          <t>3,65161400</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-0,350</t>
+          <t>-0,304</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>14,92</t>
+          <t>14,57</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>19,12</t>
+          <t>18,74</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>69,366</t>
+          <t>69,146</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -5869,42 +5869,42 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34,18515500</t>
+          <t>34,19721200</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>10,22</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>13,33</t>
+          <t>13,31</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2.242,565</t>
+          <t>2.241,076</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3,18074700</t>
+          <t>3,18228800</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>10,97</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -6154,17 +6154,17 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>1.822,964</t>
+          <t>1.823,912</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -6383,42 +6383,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,44636100</t>
+          <t>3,44757900</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>13,35</t>
+          <t>13,33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,968</t>
+          <t>12,698</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -6648,42 +6648,42 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>19,86565400</t>
+          <t>19,87307900</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0,040</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>10,47</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>13,68</t>
+          <t>13,66</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>971,224</t>
+          <t>971,404</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,08660500</t>
+          <t>1,08714500</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>10,81</t>
+          <t>10,87</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -6933,17 +6933,17 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,582</t>
+          <t>22,592</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -7156,42 +7156,42 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.918,35717200</t>
+          <t>1.919,32487700</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>11,01</t>
+          <t>11,06</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>14,41</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>185,249</t>
+          <t>185,424</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,29759100</t>
+          <t>1,29811900</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -7426,32 +7426,32 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>14,06</t>
+          <t>14,04</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,896</t>
+          <t>75,936</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,17406381</t>
+          <t>1,17176150</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -7686,32 +7686,32 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>9,81</t>
+          <t>9,44</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>199,033</t>
+          <t>198,620</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,03615496</t>
+          <t>1,03334579</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -7940,34 +7940,34 @@
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,387</t>
+          <t>22,338</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8180,42 +8180,42 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>5,17644500</t>
+          <t>5,17898100</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>10,97</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>3.523,362</t>
+          <t>3.525,261</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -8440,42 +8440,42 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11,07626500</t>
+          <t>11,08059700</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>10,80</t>
+          <t>10,85</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,17</t>
+          <t>14,15</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2.448,941</t>
+          <t>2.451,331</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1,22586800</t>
+          <t>1,22641700</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -8710,32 +8710,32 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>10,39</t>
+          <t>10,44</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>13,48</t>
+          <t>13,47</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>63,459</t>
+          <t>63,487</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1,08696577</t>
+          <t>1,08645520</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -8977,17 +8977,17 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>292,767</t>
+          <t>291,915</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9204,42 +9204,42 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1,32980600</t>
+          <t>1,33047000</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>11,23</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>493,628</t>
+          <t>493,806</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -9464,42 +9464,42 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,26462500</t>
+          <t>1,26528200</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,076</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>12,58</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>15,71</t>
+          <t>15,75</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,531</t>
+          <t>42,553</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9724,42 +9724,42 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>5,77188300</t>
+          <t>5,77418000</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>10,97</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>14,38</t>
+          <t>14,35</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>560,384</t>
+          <t>561,083</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5,37928000</t>
+          <t>5,38182700</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -9995,32 +9995,32 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>11,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,36</t>
+          <t>14,34</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>863,020</t>
+          <t>862,990</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>30,46634800</t>
+          <t>30,48027000</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,91</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -10270,17 +10270,17 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>21,750</t>
+          <t>21,760</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -10493,42 +10493,42 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>31,98223900</t>
+          <t>31,99451700</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>10,65</t>
+          <t>10,69</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>13,94</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3.142,164</t>
+          <t>3.150,254</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -10749,42 +10749,42 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>3,37120200</t>
+          <t>3,37242500</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,036</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>10,93</t>
+          <t>10,97</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>14,31</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>698,661</t>
+          <t>698,382</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -11005,42 +11005,42 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1.850,15236800</t>
+          <t>1.850,79507300</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,037</t>
+          <t>0,034</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>9,87</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>13,12</t>
+          <t>13,06</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>117,774</t>
+          <t>117,815</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -11261,42 +11261,42 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>6,46081700</t>
+          <t>6,46324000</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,037</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,50</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>13,71</t>
+          <t>13,69</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>122,641</t>
+          <t>122,675</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -11522,22 +11522,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3,73784100</t>
+          <t>3,73970100</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,19</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -11547,17 +11547,17 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17.075,341</t>
+          <t>17.091,549</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -11786,42 +11786,42 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>5,55871600</t>
+          <t>5,56154300</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>11,26</t>
+          <t>11,32</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>14,74</t>
+          <t>14,73</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>1.578,699</t>
+          <t>1.579,496</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -12046,42 +12046,42 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>31,57211700</t>
+          <t>31,58167200</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,030</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,75</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>12,72</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>169,155</t>
+          <t>169,217</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -12310,17 +12310,17 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1,06900000</t>
+          <t>1,06937900</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -12335,17 +12335,17 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>132,314</t>
+          <t>134,074</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -12562,42 +12562,42 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3,76775300</t>
+          <t>3,76949000</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>10,62</t>
+          <t>10,67</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>13,89</t>
+          <t>13,88</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2.336,005</t>
+          <t>2.341,416</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12826,42 +12826,42 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2,92261300</t>
+          <t>2,92377900</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>9,60</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>12,59</t>
+          <t>12,58</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>6.072,390</t>
+          <t>6.083,612</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -13086,42 +13086,42 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3,33686200</t>
+          <t>3,33847300</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>11,09</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>14,50</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>14.933,095</t>
+          <t>14.930,712</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -13346,42 +13346,42 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1,34964100</t>
+          <t>1,35012000</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>10,84</t>
+          <t>10,88</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>14,20</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>73,072</t>
+          <t>73,101</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -13607,42 +13607,42 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10,12565900</t>
+          <t>10,13036500</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>10,70</t>
+          <t>10,75</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>14,00</t>
+          <t>13,99</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>824,919</t>
+          <t>824,931</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -13872,42 +13872,42 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4,65794600</t>
+          <t>4,65957300</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,034</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>10,71</t>
+          <t>10,75</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,05</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>17.068,516</t>
+          <t>17.099,838</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -14136,22 +14136,22 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>5,33981200</t>
+          <t>5,34240000</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>10,99</t>
+          <t>11,04</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -14161,17 +14161,17 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23.732,372</t>
+          <t>23.782,647</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -14396,42 +14396,42 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4,99685100</t>
+          <t>4,99923300</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>10,96</t>
+          <t>11,01</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>9.870,483</t>
+          <t>9.858,895</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.806,97754500</t>
+          <t>1.807,85631000</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -14670,32 +14670,32 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>10,49</t>
+          <t>10,55</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>13,76</t>
+          <t>13,75</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>288,727</t>
+          <t>290,526</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -14780,12 +14780,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>5,60027197</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>0,047</t>
+          <t>5,60007238</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -14795,27 +14795,27 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>12,70</t>
+          <t>12,64</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>31,579</t>
+          <t>31,588</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -15040,27 +15040,27 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>13,71785600</t>
+          <t>13,71167200</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>-0,242</t>
+          <t>-0,045</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,61</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>15,56</t>
+          <t>15,51</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>22,32</t>
+          <t>22,24</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -15070,12 +15070,12 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.725,02574200</t>
+          <t>1.724,91882400</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>-0,048</t>
+          <t>-0,006</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -15324,22 +15324,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>13,66</t>
+          <t>13,60</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>112,983</t>
+          <t>113,074</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -15560,42 +15560,42 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2.610,71065300</t>
+          <t>2.605,14401100</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>-0,616</t>
+          <t>-0,213</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>27,10</t>
+          <t>26,83</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>31,79</t>
+          <t>31,76</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>15,299</t>
+          <t>15,270</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,05412800</t>
+          <t>1,05367500</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -15841,17 +15841,17 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>3,039</t>
+          <t>3,037</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -16068,42 +16068,42 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,34259600</t>
+          <t>1,33506400</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>-0,006</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>14,02</t>
+          <t>13,44</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>5,053</t>
+          <t>5,025</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-short-mm/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-short-mm</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -16324,42 +16324,42 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1,42077900</t>
+          <t>1,41264700</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>-2,472</t>
+          <t>-0,572</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>19,73</t>
+          <t>19,05</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>22,53</t>
+          <t>21,83</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>41,73</t>
+          <t>41,29</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>4,310</t>
+          <t>4,286</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/fundos-de-acoes/CAIXA-Expert-Verde-Am-Long-Bias-FIC-Acoes/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,00846900</t>
+          <t>1,00744100</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -16605,17 +16605,17 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1,315</t>
+          <t>1,314</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1,61945300</t>
+          <t>1,59461500</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -16842,32 +16842,32 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>11,94</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>18,63</t>
+          <t>16,81</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>26,03</t>
+          <t>24,52</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>12,220</t>
+          <t>12,028</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fof-smart-long-bias-mm</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,06696000</t>
+          <t>1,06706500</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -17113,17 +17113,17 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>12,727</t>
+          <t>12,729</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -17340,42 +17340,42 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1,06914100</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>0,647</t>
+          <t>1,06731100</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-0,171</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>-3,80</t>
+          <t>-3,96</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>-11,32</t>
+          <t>-11,47</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>-9,05</t>
+          <t>-9,76</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>3,054</t>
+          <t>3,020</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1,48034600</t>
+          <t>1,48110900</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -17606,32 +17606,32 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>10,62</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>13,90</t>
+          <t>13,92</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>68,113</t>
+          <t>68,152</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1.217,07124200</t>
+          <t>1.226,21306200</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -17858,32 +17858,32 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>-2,58</t>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>-3,00</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>36,441</t>
+          <t>36,715</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -18118,42 +18118,42 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>4,46827900</t>
+          <t>4,39508200</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>-0,882</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>0,10</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>0,56</t>
+          <t>-1,638</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>4,27</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>495,800</t>
+          <t>486,678</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,09550600</t>
+          <t>3,06993500</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -18388,32 +18388,32 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>10,82</t>
+          <t>9,91</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>14,11</t>
+          <t>13,15</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>71,218</t>
+          <t>70,630</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -18634,42 +18634,42 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1.667,75922800</t>
+          <t>1.674,16242000</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,318</t>
+          <t>0,383</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,00</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>8,47</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>29,731</t>
+          <t>29,823</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -18894,42 +18894,42 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>4,05991600</t>
+          <t>4,01452200</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>-0,024</t>
+          <t>-1,118</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>19,34</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>27,60</t>
+          <t>26,27</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>2.492,138</t>
+          <t>2.464,931</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -19154,42 +19154,42 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1,99395600</t>
+          <t>1,99458400</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0,032</t>
+          <t>0,031</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>9,68</t>
+          <t>9,72</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>12,73</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20,436</t>
+          <t>20,442</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -19414,12 +19414,12 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1.752,68145700</t>
+          <t>1.752,62782700</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>-0,045</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -19434,22 +19434,22 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,57</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>14,722</t>
+          <t>14,740</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -19662,42 +19662,42 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>5,93396200</t>
+          <t>5,92813800</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>-0,013</t>
+          <t>-0,098</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>11,36</t>
+          <t>11,26</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>15,02</t>
+          <t>14,84</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>891,334</t>
+          <t>890,394</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -19922,42 +19922,42 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0,58283144</t>
+          <t>0,58824360</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>-0,004</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>-6,16</t>
+          <t>-5,29</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>-19,28</t>
+          <t>-18,53</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>-40,02</t>
+          <t>-38,17</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>19,969</t>
+          <t>20,085</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -20189,42 +20189,42 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3,82613400</t>
+          <t>3,82739600</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>0,034</t>
+          <t>0,032</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>13,21</t>
+          <t>13,15</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>700,372</t>
+          <t>700,393</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -20445,12 +20445,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,41949900</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>0,044</t>
+          <t>1,41944400</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -20460,27 +20460,27 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>9,30</t>
+          <t>8,93</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>60,834</t>
+          <t>60,704</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -20709,17 +20709,17 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1,54571300</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>0,041</t>
+          <t>1,54564900</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -20729,22 +20729,22 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>10,64</t>
+          <t>10,81</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>78,599</t>
+          <t>78,596</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -20977,42 +20977,42 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,41601900</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>0,082</t>
+          <t>3,41582000</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>7,21</t>
+          <t>7,20</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>9,41</t>
+          <t>9,33</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>162,700</t>
+          <t>162,690</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -21243,12 +21243,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1,63472500</t>
+          <t>1,63465200</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>-0,230</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -21258,27 +21258,27 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>9,47</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>23,65</t>
+          <t>23,70</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>15,400</t>
+          <t>15,399</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>7,27948600</t>
+          <t>7,25177000</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -21519,32 +21519,32 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>13,18</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>18,94</t>
+          <t>18,08</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>129,901</t>
+          <t>129,415</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,89818000</t>
+          <t>1,89214100</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -21775,32 +21775,32 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>169,870</t>
+          <t>168,362</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1,42125700</t>
+          <t>1,42508200</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -22031,32 +22031,32 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>7,11</t>
+          <t>7,20</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>281,634</t>
+          <t>282,323</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1,34259600</t>
+          <t>1,34518000</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -22292,32 +22292,32 @@
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>-3,13</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>4,60</t>
+          <t>4,80</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>11,625</t>
+          <t>11,647</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -22542,42 +22542,42 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3,79666400</t>
+          <t>3,80763200</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>0,704</t>
+          <t>0,288</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>-2,70</t>
+          <t>-2,41</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>-5,55</t>
+          <t>-5,27</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-3,87</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>87,394</t>
+          <t>87,599</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -22832,12 +22832,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -22922,42 +22922,42 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1,43843500</t>
+          <t>1,43491100</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>-1,152</t>
+          <t>-0,244</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>18,86</t>
+          <t>18,57</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>30,47</t>
+          <t>29,23</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>4,408</t>
+          <t>4,427</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -23178,42 +23178,42 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>3,05918500</t>
+          <t>3,05410600</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>-1,018</t>
+          <t>-0,166</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>10,75</t>
+          <t>10,57</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>27,14</t>
+          <t>26,93</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>44,06</t>
+          <t>43,92</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>14,827</t>
+          <t>14,953</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -23438,42 +23438,42 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2.488,68141300</t>
+          <t>2.469,84504300</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>-3,104</t>
+          <t>-0,756</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>21,97</t>
+          <t>21,04</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>25,36</t>
+          <t>24,41</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>44,97</t>
+          <t>44,34</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>11,892</t>
+          <t>11,815</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -23687,42 +23687,42 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>10,54769700</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>0,737</t>
+          <t>10,40904100</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>-1,314</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-2,73</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,05</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>270,645</t>
+          <t>267,394</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -23947,42 +23947,42 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1,72617600</t>
+          <t>1,70785300</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>-3,625</t>
+          <t>-1,061</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>20,92</t>
+          <t>19,63</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>13,23</t>
+          <t>12,03</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>22,14</t>
+          <t>20,95</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>503,949</t>
+          <t>498,067</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -24207,42 +24207,42 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1,29819100</t>
+          <t>1,28683800</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>-2,893</t>
+          <t>-0,874</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>17,69</t>
+          <t>16,66</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>11,53</t>
+          <t>10,55</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>24,07</t>
+          <t>22,88</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>63,509</t>
+          <t>62,932</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -24467,42 +24467,42 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>2,04847300</t>
+          <t>2,04036800</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>-2,340</t>
+          <t>-0,395</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>13,53</t>
+          <t>13,08</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>20,17</t>
+          <t>19,69</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>33,75</t>
+          <t>33,41</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>1,936</t>
+          <t>1,813</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -24727,42 +24727,42 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>6,33627900</t>
+          <t>6,45619100</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>1,108</t>
+          <t>1,892</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>17,83</t>
+          <t>20,06</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>101,20</t>
+          <t>105,01</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>108,46</t>
+          <t>112,54</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>103,046</t>
+          <t>104,994</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -24987,42 +24987,42 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>10,20993800</t>
+          <t>10,19251600</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>-1,023</t>
+          <t>-0,170</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>10,72</t>
+          <t>10,53</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>26,10</t>
+          <t>25,88</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>42,56</t>
+          <t>42,43</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>102,386</t>
+          <t>101,777</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -25247,42 +25247,42 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,59440000</t>
+          <t>1,55875100</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>-0,017</t>
+          <t>-0,019</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>18,40</t>
+          <t>15,76</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>23,87</t>
+          <t>21,10</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>35,59</t>
+          <t>33,04</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>354,544</t>
+          <t>346,622</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -25507,42 +25507,42 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>2,16063000</t>
+          <t>2,10935600</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>-3,630</t>
+          <t>-2,373</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>23,04</t>
+          <t>20,12</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>13,63</t>
+          <t>10,93</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>26,32</t>
+          <t>24,33</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>126,261</t>
+          <t>122,759</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -25767,42 +25767,42 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>3,51988400</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>-1,107</t>
+          <t>3,52315100</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>0,092</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>15,79</t>
+          <t>15,90</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>29,14</t>
+          <t>29,26</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>41,31</t>
+          <t>42,08</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>144,947</t>
+          <t>145,050</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -26027,42 +26027,42 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>2,40570600</t>
+          <t>2,38744600</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>-3,100</t>
+          <t>-0,759</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>21,83</t>
+          <t>20,90</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>24,16</t>
+          <t>23,21</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>43,20</t>
+          <t>42,58</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>64,276</t>
+          <t>63,810</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -26291,42 +26291,42 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>9,00291400</t>
+          <t>9,19689700</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>1,474</t>
+          <t>2,154</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>15,19</t>
+          <t>17,67</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>91,94</t>
+          <t>96,08</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>101,21</t>
+          <t>106,95</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>154,856</t>
+          <t>157,865</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -26551,42 +26551,42 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1.532,54420100</t>
+          <t>1.528,67786500</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>-1,584</t>
+          <t>-0,252</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>12,10</t>
+          <t>11,82</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>17,93</t>
+          <t>18,66</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>49,671</t>
+          <t>49,554</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -26811,42 +26811,42 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>32,39426800</t>
+          <t>32,18062900</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>-1,091</t>
+          <t>-0,659</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>-4,61</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-6,23</t>
+          <t>-6,85</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>18,00</t>
+          <t>17,24</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>558,875</t>
+          <t>555,200</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -27071,42 +27071,42 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>3,21339200</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>-0,143</t>
+          <t>3,21490500</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>32,65</t>
+          <t>32,71</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>50,83</t>
+          <t>51,00</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>524,613</t>
+          <t>524,962</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -27335,42 +27335,42 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,56916700</t>
+          <t>5,53410300</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>-1,561</t>
+          <t>-0,629</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>10,63</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>24,09</t>
+          <t>23,31</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>39,59</t>
+          <t>38,69</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>26,439</t>
+          <t>25,309</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -27595,42 +27595,42 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1.954,08560300</t>
+          <t>1.928,73629600</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>-1,350</t>
+          <t>-1,297</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>15,32</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>34,27</t>
+          <t>32,53</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>49,19</t>
+          <t>47,52</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>38,835</t>
+          <t>38,360</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -27855,42 +27855,42 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2,25704400</t>
+          <t>2,25168300</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>-1,871</t>
+          <t>-0,237</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>14,11</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>10,94</t>
+          <t>10,67</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>24,38</t>
+          <t>24,30</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2,072</t>
+          <t>2,067</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -28107,42 +28107,42 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>6,96875700</t>
+          <t>6,95545300</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>-0,867</t>
+          <t>-0,190</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,62</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>29,54</t>
+          <t>29,29</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>46,64</t>
+          <t>46,60</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>49,393</t>
+          <t>49,287</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -28359,42 +28359,42 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2,59500900</t>
+          <t>2,58080800</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>-1,356</t>
+          <t>-0,547</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>11,52</t>
+          <t>10,91</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>23,67</t>
+          <t>23,00</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>39,30</t>
+          <t>38,54</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>36,714</t>
+          <t>36,729</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -28619,42 +28619,42 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>58,78200900</t>
+          <t>59,89376400</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>1,107</t>
+          <t>1,891</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>17,83</t>
+          <t>20,06</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>101,34</t>
+          <t>105,15</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>108,62</t>
+          <t>112,71</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>1.088,171</t>
+          <t>1.107,548</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -28879,42 +28879,42 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,58813100</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>-0,144</t>
+          <t>1,58886500</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>32,62</t>
+          <t>32,69</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>50,77</t>
+          <t>50,94</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>20,708</t>
+          <t>20,718</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -29139,42 +29139,42 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1,99168800</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>-1,651</t>
+          <t>2,02732700</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>1,789</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>6,30</t>
+          <t>8,20</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>15,86</t>
+          <t>17,93</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>45,49</t>
+          <t>48,63</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>288,825</t>
+          <t>294,147</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -29403,42 +29403,42 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1,05365200</t>
+          <t>1,04565800</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>-2,008</t>
+          <t>-0,758</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>15,49</t>
+          <t>14,61</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>18,61</t>
+          <t>17,66</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>3,202</t>
+          <t>3,184</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -29659,42 +29659,42 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>7,77578500</t>
+          <t>7,77308400</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-0,034</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>22,60</t>
+          <t>22,55</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>36,72</t>
+          <t>36,79</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>375,569</t>
+          <t>375,547</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1.267,84467200</t>
+          <t>1.242,89980600</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -29929,32 +29929,32 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>19,28</t>
+          <t>16,93</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>29,32</t>
+          <t>26,78</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>42,65</t>
+          <t>40,10</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>9,970</t>
+          <t>9,774</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -30179,7 +30179,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1.859,88974500</t>
+          <t>1.822,03115500</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -30189,32 +30189,32 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>17,87</t>
+          <t>15,47</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>24,34</t>
+          <t>21,81</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>36,95</t>
+          <t>34,38</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>26,212</t>
+          <t>25,696</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -30435,42 +30435,42 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>200,94672273</t>
+          <t>200,60782742</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>-1,022</t>
+          <t>-0,168</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>10,73</t>
+          <t>10,54</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>27,52</t>
+          <t>27,30</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>44,67</t>
+          <t>44,53</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>20,096</t>
+          <t>20,062</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -30695,42 +30695,42 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>2,03141500</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>-1,641</t>
+          <t>2,06766100</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>1,784</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>15,70</t>
+          <t>17,76</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>45,50</t>
+          <t>48,64</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>6,057</t>
+          <t>6,165</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -30952,42 +30952,42 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1,98539000</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>-1,649</t>
+          <t>2,02101900</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>1,794</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>6,30</t>
+          <t>8,21</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>15,97</t>
+          <t>18,05</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>45,74</t>
+          <t>48,90</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>1.771,004</t>
+          <t>1.802,044</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -31205,42 +31205,42 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>65,54456300</t>
+          <t>66,78638200</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>1,109</t>
+          <t>1,894</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>17,92</t>
+          <t>20,16</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>102,37</t>
+          <t>106,21</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>109,92</t>
+          <t>114,04</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>895,948</t>
+          <t>912,468</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -31449,42 +31449,42 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>35,96233900</t>
+          <t>35,72548100</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>-1,092</t>
+          <t>-0,658</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>-3,96</t>
+          <t>-4,59</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-6,46</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>18,64</t>
+          <t>17,87</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>628,079</t>
+          <t>623,558</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -31693,42 +31693,42 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>21,19641100</t>
+          <t>21,04060900</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>-3,047</t>
+          <t>-0,735</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>21,64</t>
+          <t>20,74</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>25,67</t>
+          <t>24,75</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>46,18</t>
+          <t>45,48</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>139,994</t>
+          <t>138,931</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -31946,42 +31946,42 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>30,09904700</t>
+          <t>29,90052100</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>-1,091</t>
+          <t>-0,659</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>-3,96</t>
+          <t>-4,59</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>-6,19</t>
+          <t>-6,81</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>17,96</t>
+          <t>17,19</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>10,073</t>
+          <t>10,007</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -32195,42 +32195,42 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>57,81685100</t>
+          <t>58,90923600</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>1,109</t>
+          <t>1,889</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>17,86</t>
+          <t>20,09</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>101,66</t>
+          <t>105,47</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>109,00</t>
+          <t>113,09</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>786,812</t>
+          <t>801,441</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -32444,42 +32444,42 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>30,90744300</t>
+          <t>30,70333000</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>-1,094</t>
+          <t>-0,660</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>-4,61</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>-6,20</t>
+          <t>-6,82</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>18,06</t>
+          <t>17,29</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>379,353</t>
+          <t>376,678</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -32688,42 +32688,42 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>61,51568600</t>
+          <t>62,67932700</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>1,110</t>
+          <t>1,891</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>17,89</t>
+          <t>20,12</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>102,01</t>
+          <t>105,83</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>109,41</t>
+          <t>113,51</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>888,432</t>
+          <t>903,083</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1,17217700</t>
+          <t>1,17270000</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -32946,32 +32946,32 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>9,60</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>12,54</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>68,049</t>
+          <t>68,824</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -33197,7 +33197,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1,41482500</t>
+          <t>1,41546000</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -33207,12 +33207,12 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>9,62</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -33222,17 +33222,17 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>245,816</t>
+          <t>244,338</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -33462,42 +33462,42 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>6,15095500</t>
+          <t>6,15320800</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>0,040</t>
+          <t>0,036</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>10,26</t>
+          <t>10,31</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>13,46</t>
+          <t>13,44</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>43,588</t>
+          <t>43,536</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -33722,42 +33722,42 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,36636800</t>
+          <t>3,36751600</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,034</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>10,45</t>
+          <t>10,49</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>13,61</t>
+          <t>13,59</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>21,642</t>
+          <t>23,513</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -33984,42 +33984,42 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>5,36350800</t>
+          <t>5,36572900</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>10,72</t>
+          <t>10,76</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>14,05</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>855,538</t>
+          <t>855,197</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -34241,42 +34241,42 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>25,38697300</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr">
-        <is>
-          <t>-0,066</t>
+          <t>25,39882000</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>13,39</t>
+          <t>13,44</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>16,68</t>
+          <t>16,70</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>97,899</t>
+          <t>97,944</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -34505,42 +34505,42 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>3,42445000</t>
+          <t>3,42596500</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>10,53</t>
+          <t>10,58</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>13,81</t>
+          <t>13,80</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>7.955,835</t>
+          <t>7.989,743</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -34766,42 +34766,42 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,10834900</t>
+          <t>5,11004700</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,033</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>14,18</t>
+          <t>14,15</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>3.166,151</t>
+          <t>3.181,282</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -35026,42 +35026,42 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1.979,93434600</t>
+          <t>1.980,84760300</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>11,22</t>
+          <t>11,27</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>14,66</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>17.023,448</t>
+          <t>16.848,055</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -35286,42 +35286,42 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1,62317154</t>
+          <t>1,62394652</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>10,88</t>
+          <t>10,93</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>14,26</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>609,519</t>
+          <t>359,810</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -35530,42 +35530,42 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>5,37043400</t>
+          <t>5,37265300</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>10,93</t>
+          <t>10,98</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>14,31</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>297,749</t>
+          <t>297,872</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -35787,42 +35787,42 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>18,76764000</t>
+          <t>18,77479800</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>10,89</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>14,24</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>4.820,633</t>
+          <t>4.764,103</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -36031,22 +36031,22 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>9,12236000</t>
+          <t>9,12734900</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,021</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>10,77</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -36056,17 +36056,17 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2.375,120</t>
+          <t>2.376,135</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -36309,12 +36309,12 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -36535,42 +36535,42 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2,94647200</t>
+          <t>2,94767100</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,040</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>12,81</t>
+          <t>12,80</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>13.754,315</t>
+          <t>13.897,450</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -36796,42 +36796,42 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>4,64116000</t>
+          <t>4,64294300</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,038</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>10,94</t>
+          <t>10,98</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>17.698,984</t>
+          <t>17.795,175</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -37064,42 +37064,42 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1,44180900</t>
+          <t>1,44256700</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,20</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,60</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>3.515,141</t>
+          <t>3.817,329</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -37320,7 +37320,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1.857,27691100</t>
+          <t>1.858,20910000</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -37330,12 +37330,12 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,88</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -37345,17 +37345,17 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>1.539,353</t>
+          <t>1.539,231</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1,35870800</t>
+          <t>1,35925900</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -37590,12 +37590,12 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>8,81</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -37605,17 +37605,17 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>30.936,930</t>
+          <t>31.048,832</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>9,79627800</t>
+          <t>9,80056000</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -37849,32 +37849,32 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>12,37</t>
+          <t>12,36</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>2.688,201</t>
+          <t>2.650,616</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -38098,7 +38098,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2,57978700</t>
+          <t>2,58091800</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -38108,12 +38108,12 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>9,48</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -38123,17 +38123,17 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>16.716,320</t>
+          <t>16.714,130</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -38359,42 +38359,42 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,70523300</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>0,000</t>
+          <t>4,70707600</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>10,89</t>
+          <t>10,93</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,21</t>
+          <t>14,19</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.902,982</t>
+          <t>11.900,266</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -38626,17 +38626,17 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,93443200</t>
+          <t>3,93434800</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>-0,451</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -38646,22 +38646,22 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>16,34</t>
+          <t>16,21</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>1.733,499</t>
+          <t>1.734,169</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -38893,42 +38893,42 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>2,53296700</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>-0,037</t>
+          <t>2,53388700</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>0,036</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>3.210,703</t>
+          <t>3.211,673</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -39158,22 +39158,22 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>3,18705400</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>-0,066</t>
+          <t>3,18854100</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>13,06</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
@@ -39183,17 +39183,17 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>38,655</t>
+          <t>38,673</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -39414,42 +39414,42 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1.719,75729700</t>
-        </is>
-      </c>
-      <c r="E153" s="7" t="inlineStr">
-        <is>
-          <t>-0,002</t>
+          <t>1.720,36844600</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>13,15</t>
+          <t>13,10</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>430,508</t>
+          <t>430,661</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -39674,42 +39674,42 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,06649400</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="inlineStr">
-        <is>
-          <t>-0,079</t>
+          <t>4,06957500</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>0,075</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>13,05</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>16,24</t>
+          <t>16,31</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>3.232,513</t>
+          <t>3.235,801</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -39936,42 +39936,42 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>5,65976100</t>
+          <t>5,64397300</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>-0,331</t>
+          <t>-0,278</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>19,57</t>
+          <t>19,22</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>2.505,861</t>
+          <t>2.499,283</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -40198,42 +40198,42 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>5,54329200</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>-0,079</t>
+          <t>5,54583800</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>13,55</t>
+          <t>13,60</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>16,88</t>
+          <t>16,89</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>6.032,395</t>
+          <t>6.037,421</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -40460,42 +40460,42 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>5,06009200</t>
+          <t>5,05795300</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>-0,147</t>
+          <t>-0,042</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>12,10</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>15,79</t>
+          <t>15,68</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>495,406</t>
+          <t>495,197</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -40722,42 +40722,42 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>8,31489500</t>
+          <t>8,31749800</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,037</t>
+          <t>0,031</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>10,66</t>
+          <t>10,69</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,01</t>
+          <t>13,98</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>166,391</t>
+          <t>166,256</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -40842,42 +40842,42 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>3,84701500</t>
+          <t>3,82956300</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>-0,486</t>
+          <t>-0,453</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>15,30</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>20,61</t>
+          <t>20,07</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>856,122</t>
+          <t>852,238</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -41104,42 +41104,42 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>4,10572800</t>
+          <t>4,10511800</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>-0,565</t>
+          <t>-0,014</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>12,90</t>
+          <t>12,88</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>16,70</t>
+          <t>16,52</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>675,761</t>
+          <t>675,661</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -41371,42 +41371,42 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>2,73246100</t>
+          <t>2,73354600</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,041</t>
+          <t>0,039</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>10,99</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>8.620,300</t>
+          <t>8.631,254</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -41635,42 +41635,42 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>7,50884700</t>
+          <t>7,51128200</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,032</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,40</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>10,75</t>
+          <t>10,78</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>14,11</t>
+          <t>14,08</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>11.909,446</t>
+          <t>11.862,285</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -41899,7 +41899,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>7,84726800</t>
+          <t>7,85118300</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -41909,12 +41909,12 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>10,76</t>
+          <t>10,82</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -41924,17 +41924,17 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>3.753,916</t>
+          <t>3.700,830</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -42159,42 +42159,42 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1,55698300</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>-0,330</t>
+          <t>1,55769400</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>11,66</t>
+          <t>11,71</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>15,05</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>167,506</t>
+          <t>167,582</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -42415,22 +42415,22 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,28032200</t>
+          <t>3,28187600</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>10,24</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -42440,17 +42440,17 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>1.785,715</t>
+          <t>1.789,089</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -42703,12 +42703,12 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -42959,12 +42959,12 @@
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -43215,12 +43215,12 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -43471,12 +43471,12 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -43727,12 +43727,12 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -43983,12 +43983,12 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -44209,42 +44209,42 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>7,04734200</t>
+          <t>7,05073000</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>11,04</t>
+          <t>11,09</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>22.265,423</t>
+          <t>22.285,412</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -44329,42 +44329,42 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>6,07011100</t>
+          <t>6,05179200</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>-0,347</t>
+          <t>-0,301</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>15,48</t>
+          <t>15,13</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>19,86</t>
+          <t>19,48</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>623,716</t>
+          <t>621,834</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -44620,12 +44620,12 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -44650,7 +44650,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/rpps/brasil-estrategia-livre-mm-lp/Paginas/default.aspx</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -44842,42 +44842,42 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>4,62236100</t>
+          <t>4,61472200</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>-1,020</t>
+          <t>-0,165</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>10,82</t>
+          <t>10,63</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>27,66</t>
+          <t>27,45</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>44,85</t>
+          <t>44,71</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>338,988</t>
+          <t>338,175</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -45102,42 +45102,42 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>4,23490400</t>
+          <t>4,22879900</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>-1,110</t>
+          <t>-0,144</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>10,69</t>
+          <t>10,53</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>27,01</t>
+          <t>26,83</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>43,98</t>
+          <t>43,88</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>8,827</t>
+          <t>8,814</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -45362,42 +45362,42 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>11,85766114</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>0,744</t>
+          <t>11,70137617</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>-1,318</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-2,72</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>7,14</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>10,70</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>2.367,348</t>
+          <t>2.336,454</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -45622,42 +45622,42 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>2,39140200</t>
+          <t>2,38531000</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>-1,243</t>
+          <t>-0,254</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>12,03</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>26,16</t>
+          <t>25,84</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>41,19</t>
+          <t>40,88</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>233,548</t>
+          <t>232,953</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -45878,42 +45878,42 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>2,57550600</t>
+          <t>2,55590500</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>-3,108</t>
+          <t>-0,761</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>21,86</t>
+          <t>20,94</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>24,22</t>
+          <t>23,27</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>43,29</t>
+          <t>42,66</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>885,331</t>
+          <t>878,593</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -46138,42 +46138,42 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>4,08174981</t>
+          <t>4,06755317</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>-1,275</t>
+          <t>-0,347</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>11,62</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>25,46</t>
+          <t>25,02</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>38,88</t>
+          <t>38,49</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>1.524,880</t>
+          <t>1.519,576</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -46390,42 +46390,42 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>2,99932690</t>
+          <t>2,98692819</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>-1,439</t>
+          <t>-0,413</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>13,51</t>
+          <t>13,04</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>26,89</t>
+          <t>26,37</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>41,72</t>
+          <t>41,37</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>907,797</t>
+          <t>904,044</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -46642,42 +46642,42 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>3,93992800</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>-0,016</t>
+          <t>3,94111500</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>0,030</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>10,96</t>
+          <t>10,99</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>14,30</t>
+          <t>14,26</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>4.565,042</t>
+          <t>4.519,313</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -2178,12 +2178,12 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>40.194.314/0001-97</t>
+          <t>40.194.309/0001-84</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="S7" s="4" t="inlineStr">
@@ -2193,27 +2193,27 @@
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>10000.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AF7" s="4" t="inlineStr">
         <is>
-          <t>QUALIFICADO</t>
+          <t>GERAL</t>
         </is>
       </c>
       <c r="AG7" s="4" t="inlineStr">
@@ -2309,47 +2309,43 @@
       </c>
       <c r="AR7" s="4" t="inlineStr">
         <is>
-          <t>CAIXA PLUS QUALIFICADO FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CRÉDITO PRIVADO LP - RESP LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS7" s="4" t="inlineStr">
-        <is>
-          <t>OBS: Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
-        </is>
-      </c>
+          <t>CAIXA PLUS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CRÉDITO PRIVADO LONGO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS7" s="4" t="inlineStr"/>
       <c r="AT7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6533.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6532.pdf</t>
         </is>
       </c>
       <c r="AU7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6533.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6532.pdf</t>
         </is>
       </c>
       <c r="AV7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6533.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6532.pdf</t>
         </is>
       </c>
       <c r="AW7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6533.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6532.pdf</t>
         </is>
       </c>
       <c r="AX7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6533.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6532.pdf</t>
         </is>
       </c>
       <c r="AY7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6533.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6532.pdf</t>
         </is>
       </c>
       <c r="AZ7" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6533.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6532.pdf</t>
         </is>
       </c>
       <c r="BA7" s="4" t="inlineStr"/>
@@ -2632,7 +2628,11 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>17h00</t>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>03.218.183/0001-04</t>
+          <t>03.191.874/0001-61</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>46</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -3193,27 +3193,27 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100000.0</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>["Pessoa Física"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>["Pessoa Física"]</t>
+          <t>["Institucional", "PJ Atacado"]</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>CAIXA CAPITAL ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
+          <t>CAIXA PATRIMÔNIO ÍNDICE DE PREÇOS FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESP LIMITADA</t>
         </is>
       </c>
       <c r="AS12" s="2" t="inlineStr">
@@ -3319,43 +3319,43 @@
       </c>
       <c r="AT12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0046.pdf</t>
         </is>
       </c>
       <c r="AU12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0046.pdf</t>
         </is>
       </c>
       <c r="AV12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0087.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0046.pdf</t>
         </is>
       </c>
       <c r="AW12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_46.pdf</t>
         </is>
       </c>
       <c r="AX12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_46.pdf</t>
         </is>
       </c>
       <c r="AY12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_46.pdf</t>
         </is>
       </c>
       <c r="AZ12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0087.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0046.pdf</t>
         </is>
       </c>
       <c r="BA12" s="2" t="inlineStr"/>
       <c r="BB12" s="2" t="inlineStr">
         <is>
-          <t>https://web.microsoftstream.com/video/32d65536-1de1-4f2f-a9b8-0fbb0d9347fc?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+          <t>https://web.microsoftstream.com/video/140b7682-00df-491d-b451-73ae70a040fa?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="U45" s="4" t="inlineStr">
         <is>
-          <t>100000.0</t>
+          <t>50000.0</t>
         </is>
       </c>
       <c r="V45" s="4" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="X45" s="4" t="inlineStr">
         <is>
-          <t>10000.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="Y45" s="4" t="inlineStr">
@@ -11839,7 +11839,14 @@
       </c>
       <c r="AS45" s="4" t="inlineStr">
         <is>
-          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).
+Campanha "Semana do Consumidor" de 26/10/2026 a 30/10/2026
+Redução de Tickets
+Aplicação Inicial:
+De: R$ 100.000,00 para R$ 50.000,00
+Saldo Mínimo: 
+De: R$ 10.000,00 para R$ 5.000,00
+"Fundos de Investimento que estiveram em Campanha, após a Campanha, voltam aos parâmetros originais. Saldo abaixo do mínimo pode impedir resgates parciais (somente total)."</t>
         </is>
       </c>
       <c r="AT45" s="4" t="inlineStr">
@@ -12220,19 +12227,15 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P47" s="4" t="inlineStr">
-        <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/referenciados/fic-sigma-ref-di-longo-prazo</t>
-        </is>
-      </c>
+      <c r="P47" s="4" t="inlineStr"/>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>10.731.794/0001-17</t>
+          <t>69.516.203/0001-31</t>
         </is>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="S47" s="4" t="inlineStr">
@@ -12242,27 +12245,27 @@
       </c>
       <c r="T47" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="U47" s="4" t="inlineStr">
         <is>
-          <t>50000.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="X47" s="4" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Y47" s="4" t="inlineStr">
@@ -12332,12 +12335,12 @@
       </c>
       <c r="AL47" s="4" t="inlineStr">
         <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+          <t>["Pessoa Física", "Private"]</t>
         </is>
       </c>
       <c r="AM47" s="4" t="inlineStr">
         <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+          <t>["Pessoa Física", "Private"]</t>
         </is>
       </c>
       <c r="AN47" s="4" t="inlineStr">
@@ -12358,55 +12361,47 @@
       </c>
       <c r="AR47" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SIGMA SINGULAR FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REF DI LONGO PRAZO - RESP LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS47" s="4" t="inlineStr">
-        <is>
-          <t>Fundo teve alteração de nomenclatura a partir de 21/09/2026 de CAIXA SIGMA para CAIXA SIGMA SINGULAR</t>
-        </is>
-      </c>
+          <t>CAIXA SIGMA FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS47" s="4" t="inlineStr"/>
       <c r="AT47" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5171.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7989.pdf</t>
         </is>
       </c>
       <c r="AU47" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5171.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7989.pdf</t>
         </is>
       </c>
       <c r="AV47" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5171.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7989.pdf</t>
         </is>
       </c>
       <c r="AW47" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5171.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_7989.pdf</t>
         </is>
       </c>
       <c r="AX47" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5171.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7989.pdf</t>
         </is>
       </c>
       <c r="AY47" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5171.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7989.pdf</t>
         </is>
       </c>
       <c r="AZ47" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5171.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7989.pdf</t>
         </is>
       </c>
       <c r="BA47" s="4" t="inlineStr"/>
-      <c r="BB47" s="4" t="inlineStr">
-        <is>
-          <t>https://web.microsoftstream.com/video/4be15710-4acb-4afd-a959-c6ed0d090cac?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
-        </is>
-      </c>
+      <c r="BB47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -14601,7 +14596,7 @@
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>100000.0</t>
+          <t>50000.0</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -14616,7 +14611,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>10000.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -14715,7 +14710,17 @@
           <t>CAIXA MEGA FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA REFERENCIADO DI LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
-      <c r="AS56" s="2" t="inlineStr"/>
+      <c r="AS56" s="2" t="inlineStr">
+        <is>
+          <t>Campanha "Semana do Consumidor" de 26/10/2026 a 30/10/2026
+Redução de Tickets
+Aplicação Inicial:
+De: R$ 100.000,00 para R$ 50.000,00
+Saldo Mínimo: 
+De: R$ 10.000,00 para R$ 5.000,00
+"Fundos de Investimento que estiveram em Campanha, após a Campanha, voltam aos parâmetros originais. Saldo abaixo do mínimo pode impedir resgates parciais (somente total)."</t>
+        </is>
+      </c>
       <c r="AT56" s="2" t="inlineStr">
         <is>
           <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5411.pdf</t>
@@ -15098,43 +15103,187 @@
           <t>PF | PJ</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="2" t="inlineStr"/>
-      <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="2" t="inlineStr"/>
-      <c r="T58" s="2" t="inlineStr"/>
-      <c r="U58" s="2" t="inlineStr"/>
-      <c r="V58" s="2" t="inlineStr"/>
-      <c r="W58" s="2" t="inlineStr"/>
-      <c r="X58" s="2" t="inlineStr"/>
-      <c r="Y58" s="2" t="inlineStr"/>
-      <c r="Z58" s="2" t="inlineStr"/>
-      <c r="AA58" s="2" t="inlineStr"/>
-      <c r="AB58" s="2" t="inlineStr"/>
-      <c r="AC58" s="2" t="inlineStr"/>
-      <c r="AD58" s="2" t="inlineStr"/>
-      <c r="AE58" s="2" t="inlineStr"/>
-      <c r="AF58" s="2" t="inlineStr"/>
-      <c r="AG58" s="2" t="inlineStr"/>
-      <c r="AH58" s="2" t="inlineStr"/>
-      <c r="AI58" s="2" t="inlineStr"/>
-      <c r="AJ58" s="2" t="inlineStr"/>
-      <c r="AK58" s="2" t="inlineStr"/>
-      <c r="AL58" s="2" t="inlineStr"/>
-      <c r="AM58" s="2" t="inlineStr"/>
-      <c r="AN58" s="2" t="inlineStr"/>
-      <c r="AO58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/voce/renda-fixa/caixa-fic-rf-curto-prazo</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>39.594.941/0001-36</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>RF 100% TPF - Curto Prazo</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="AE58" s="2" t="inlineStr">
+        <is>
+          <t>CURTO PRAZO</t>
+        </is>
+      </c>
+      <c r="AF58" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AG58" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AH58" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AI58" s="2" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AJ58" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AK58" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AL58" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AM58" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AN58" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AO58" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AP58" s="2" t="inlineStr"/>
-      <c r="AQ58" s="2" t="inlineStr"/>
-      <c r="AR58" s="2" t="inlineStr"/>
-      <c r="AS58" s="2" t="inlineStr"/>
-      <c r="AT58" s="2" t="inlineStr"/>
-      <c r="AU58" s="2" t="inlineStr"/>
-      <c r="AV58" s="2" t="inlineStr"/>
-      <c r="AW58" s="2" t="inlineStr"/>
-      <c r="AX58" s="2" t="inlineStr"/>
-      <c r="AY58" s="2" t="inlineStr"/>
-      <c r="AZ58" s="2" t="inlineStr"/>
+      <c r="AQ58" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AR58" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA TURQUESA PJ FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA CURTO PRAZO - RESP LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS58" s="2" t="inlineStr">
+        <is>
+          <t>*Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
+      <c r="AT58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AU58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AV58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AW58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AX58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AY58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
+        </is>
+      </c>
+      <c r="AZ58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6520.pdf</t>
+        </is>
+      </c>
       <c r="BA58" s="2" t="inlineStr"/>
       <c r="BB58" s="2" t="inlineStr"/>
     </row>
@@ -19848,15 +19997,19 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="P77" s="4" t="inlineStr"/>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="Q77" s="4" t="inlineStr">
         <is>
-          <t>35.536.472/0001-48</t>
+          <t>34.660.333/0001-69</t>
         </is>
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="S77" s="4" t="inlineStr">
@@ -19866,7 +20019,7 @@
       </c>
       <c r="T77" s="4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="U77" s="4" t="inlineStr">
@@ -19954,8 +20107,16 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AL77" s="4" t="inlineStr"/>
-      <c r="AM77" s="4" t="inlineStr"/>
+      <c r="AL77" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "Private"]</t>
+        </is>
+      </c>
+      <c r="AM77" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "Private"]</t>
+        </is>
+      </c>
       <c r="AN77" s="4" t="inlineStr">
         <is>
           <t>Não</t>
@@ -19974,47 +20135,43 @@
       </c>
       <c r="AR77" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FUNCIONÁRIOS ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABI</t>
-        </is>
-      </c>
-      <c r="AS77" s="4" t="inlineStr">
-        <is>
-          <t>Fundo destinado a Funcionários e aposentados da Caixa Econômica Federal. Disponível para aplicação somente via conta corrente marcada como conta-salário empregado CAIXA.</t>
-        </is>
-      </c>
+          <t>CAIXA ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITA</t>
+        </is>
+      </c>
+      <c r="AS77" s="4" t="inlineStr"/>
       <c r="AT77" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6479.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6440.pdf</t>
         </is>
       </c>
       <c r="AU77" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6479.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6440.pdf</t>
         </is>
       </c>
       <c r="AV77" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6440.pdf</t>
         </is>
       </c>
       <c r="AW77" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6440.pdf</t>
         </is>
       </c>
       <c r="AX77" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6440.pdf</t>
         </is>
       </c>
       <c r="AY77" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6440.pdf</t>
         </is>
       </c>
       <c r="AZ77" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6440.pdf</t>
         </is>
       </c>
       <c r="BA77" s="4" t="inlineStr"/>
@@ -31885,17 +32042,17 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-1</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>04.885.818/0001-90</t>
+          <t>04.885.824/0001-47</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="S124" s="2" t="inlineStr">
@@ -31905,12 +32062,12 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="U124" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="V124" s="2" t="inlineStr">
@@ -32005,7 +32162,7 @@
       </c>
       <c r="AR124" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - VALE DO RIO DOCE I - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - VALE DO RIO DOCE II - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS124" s="2" t="inlineStr">
@@ -32015,37 +32172,37 @@
       </c>
       <c r="AT124" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5206.pdf</t>
         </is>
       </c>
       <c r="AU124" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5206.pdf</t>
         </is>
       </c>
       <c r="AV124" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5206.pdf</t>
         </is>
       </c>
       <c r="AW124" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5206.pdf</t>
         </is>
       </c>
       <c r="AX124" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5206.pdf</t>
         </is>
       </c>
       <c r="AY124" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
       <c r="AZ124" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5206.pdf</t>
         </is>
       </c>
       <c r="BA124" s="2" t="inlineStr"/>
@@ -32880,17 +33037,17 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-1</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>04.885.818/0001-90</t>
+          <t>04.885.824/0001-47</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="S128" s="2" t="inlineStr">
@@ -32900,12 +33057,12 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="V128" s="2" t="inlineStr">
@@ -33000,7 +33157,7 @@
       </c>
       <c r="AR128" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - VALE DO RIO DOCE I - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - VALE DO RIO DOCE II - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AS128" s="2" t="inlineStr">
@@ -33010,37 +33167,37 @@
       </c>
       <c r="AT128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5206.pdf</t>
         </is>
       </c>
       <c r="AU128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5206.pdf</t>
         </is>
       </c>
       <c r="AV128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5206.pdf</t>
         </is>
       </c>
       <c r="AW128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5206.pdf</t>
         </is>
       </c>
       <c r="AX128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5206.pdf</t>
         </is>
       </c>
       <c r="AY128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
       <c r="AZ128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5206.pdf</t>
         </is>
       </c>
       <c r="BA128" s="2" t="inlineStr"/>
@@ -40377,12 +40534,12 @@
       </c>
       <c r="Q157" s="4" t="inlineStr">
         <is>
-          <t>10.577.503/0001-88</t>
+          <t>11.060.913/0001-10</t>
         </is>
       </c>
       <c r="R157" s="4" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="S157" s="4" t="inlineStr">
@@ -40432,7 +40589,7 @@
       </c>
       <c r="AB157" s="4" t="inlineStr">
         <is>
-          <t>IMA-B 5+</t>
+          <t>IMA-B 5</t>
         </is>
       </c>
       <c r="AC157" s="4" t="inlineStr">
@@ -40508,49 +40665,43 @@
       </c>
       <c r="AR157" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IMA B 5+ TITULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS157" s="4" t="inlineStr">
-        <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Mercado da ANBIMA B 5 (IMA-B 5).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
-        </is>
-      </c>
+          <t>CAIXA BRASIL IMA-B 5 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS157" s="4" t="inlineStr"/>
       <c r="AT157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5187.pdf</t>
         </is>
       </c>
       <c r="AU157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5187.pdf</t>
         </is>
       </c>
       <c r="AV157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5187.pdf</t>
         </is>
       </c>
       <c r="AW157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5187.pdf</t>
         </is>
       </c>
       <c r="AX157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5187.pdf</t>
         </is>
       </c>
       <c r="AY157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5187.pdf</t>
         </is>
       </c>
       <c r="AZ157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5187.pdf</t>
         </is>
       </c>
       <c r="BA157" s="4" t="inlineStr"/>
@@ -40639,12 +40790,12 @@
       </c>
       <c r="Q158" s="2" t="inlineStr">
         <is>
-          <t>10.577.503/0001-88</t>
+          <t>11.060.913/0001-10</t>
         </is>
       </c>
       <c r="R158" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="S158" s="2" t="inlineStr">
@@ -40694,7 +40845,7 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>IMA-B 5+</t>
+          <t>IMA-B 5</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
@@ -40770,49 +40921,43 @@
       </c>
       <c r="AR158" s="2" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IMA B 5+ TITULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS158" s="2" t="inlineStr">
-        <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Mercado da ANBIMA B 5 (IMA-B 5).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
-        </is>
-      </c>
+          <t>CAIXA BRASIL IMA-B 5 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS158" s="2" t="inlineStr"/>
       <c r="AT158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5187.pdf</t>
         </is>
       </c>
       <c r="AU158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5187.pdf</t>
         </is>
       </c>
       <c r="AV158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5187.pdf</t>
         </is>
       </c>
       <c r="AW158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5187.pdf</t>
         </is>
       </c>
       <c r="AX158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5187.pdf</t>
         </is>
       </c>
       <c r="AY158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5187.pdf</t>
         </is>
       </c>
       <c r="AZ158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5187.pdf</t>
         </is>
       </c>
       <c r="BA158" s="2" t="inlineStr"/>
@@ -41283,12 +41428,12 @@
       </c>
       <c r="Q161" s="4" t="inlineStr">
         <is>
-          <t>10.577.503/0001-88</t>
+          <t>11.060.913/0001-10</t>
         </is>
       </c>
       <c r="R161" s="4" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="S161" s="4" t="inlineStr">
@@ -41338,7 +41483,7 @@
       </c>
       <c r="AB161" s="4" t="inlineStr">
         <is>
-          <t>IMA-B 5+</t>
+          <t>IMA-B 5</t>
         </is>
       </c>
       <c r="AC161" s="4" t="inlineStr">
@@ -41414,49 +41559,43 @@
       </c>
       <c r="AR161" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL IMA B 5+ TITULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS161" s="4" t="inlineStr">
-        <is>
-          <t>1. O Fundo tem como parâmetro de rentabilidade o Índice de Mercado da ANBIMA B 5 (IMA-B 5).
-2. Para aplicação por meio de conta operação 1292, é necessário o cadastramento prévio de cotistas, conforme descrito no item Adesão, do FI612.
-3. O procedimento de inclusão da conta deverá ser realizado sempre que houver qualquer aplicação por meio de conta operação 1292, mesmo para os clientes que já realizaram o cadastramento anteriormente.</t>
-        </is>
-      </c>
+          <t>CAIXA BRASIL IMA-B 5 TÍTULOS PÚBLICOS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS161" s="4" t="inlineStr"/>
       <c r="AT161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5187.pdf</t>
         </is>
       </c>
       <c r="AU161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5568.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5187.pdf</t>
         </is>
       </c>
       <c r="AV161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5187.pdf</t>
         </is>
       </c>
       <c r="AW161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5187.pdf</t>
         </is>
       </c>
       <c r="AX161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5187.pdf</t>
         </is>
       </c>
       <c r="AY161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5187.pdf</t>
         </is>
       </c>
       <c r="AZ161" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5568.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5187.pdf</t>
         </is>
       </c>
       <c r="BA161" s="4" t="inlineStr"/>
@@ -45283,12 +45422,12 @@
       </c>
       <c r="Q177" s="4" t="inlineStr">
         <is>
-          <t>15.154.236/0001-50</t>
+          <t>13.058.816/0001-18</t>
         </is>
       </c>
       <c r="R177" s="4" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="S177" s="4" t="inlineStr">
@@ -45348,7 +45487,7 @@
       </c>
       <c r="AD177" s="4" t="inlineStr">
         <is>
-          <t>Fechado para captação</t>
+          <t>Aberto para captação</t>
         </is>
       </c>
       <c r="AE177" s="4" t="inlineStr">
@@ -45414,47 +45553,43 @@
       </c>
       <c r="AR177" s="4" t="inlineStr">
         <is>
-          <t>CAIXA BRASIL ETF IBOVESPA FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
-        </is>
-      </c>
-      <c r="AS177" s="4" t="inlineStr">
-        <is>
-          <t>Fundo fechado para novas aplicações, a novos investidores e cotistas atuais a partir de 03/04/2023 (inclusive)</t>
-        </is>
-      </c>
+          <t>CAIXA BRASIL INDEXA IBOVESPA FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AS177" s="4" t="inlineStr"/>
       <c r="AT177" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5842.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5445.pdf</t>
         </is>
       </c>
       <c r="AU177" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5842.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5445.pdf</t>
         </is>
       </c>
       <c r="AV177" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5445.pdf</t>
         </is>
       </c>
       <c r="AW177" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5445.pdf</t>
         </is>
       </c>
       <c r="AX177" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5445.pdf</t>
         </is>
       </c>
       <c r="AY177" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5445.pdf</t>
         </is>
       </c>
       <c r="AZ177" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5842.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5445.pdf</t>
         </is>
       </c>
       <c r="BA177" s="4" t="inlineStr"/>

--- a/dados_atuais.xlsx
+++ b/dados_atuais.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,36381100</t>
+          <t>2,36482600</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -824,32 +824,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>10,05</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>12,36</t>
+          <t>12,35</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>398,997</t>
+          <t>399,953</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,74138600</t>
+          <t>5,74386500</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>9,88</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.562,227</t>
+          <t>6.609,749</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,89890400</t>
+          <t>2,90015500</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1344,32 +1344,32 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,87</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>12,14</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>756,249</t>
+          <t>761,433</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1593,22 +1593,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>20,41911000</t>
+          <t>20,40795700</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>-0,248</t>
+          <t>-0,054</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>6,47</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -1618,17 +1618,17 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>113,274</t>
+          <t>113,026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1857,42 +1857,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,15347500</t>
+          <t>3,15507500</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>11,64</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,30</t>
+          <t>14,31</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1.769,891</t>
+          <t>1.769,418</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2113,42 +2113,42 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.931,43330800</t>
+          <t>1.932,36212700</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>11,46</t>
+          <t>11,51</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>97,898</t>
+          <t>97,787</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2485,42 +2485,42 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,52253700</t>
+          <t>3,52434600</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>11,09</t>
+          <t>11,15</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>13,70</t>
+          <t>13,71</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>63,560</t>
+          <t>63,553</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3113,42 +3113,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14,08131700</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>-0,020</t>
+          <t>14,10306600</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0,154</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>9,50</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>11,66</t>
+          <t>11,88</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,044</t>
+          <t>28,078</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3377,42 +3377,42 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>10,15503900</t>
+          <t>10,15994100</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,036</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>10,39</t>
+          <t>10,45</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>12,83</t>
+          <t>12,84</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>589,052</t>
+          <t>590,538</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -3637,22 +3637,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,66049000</t>
+          <t>3,66229100</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,20</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -3662,17 +3662,17 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>119,635</t>
+          <t>119,708</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,49746900</t>
+          <t>3,49913600</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>10,99</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -3925,17 +3925,17 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12,475</t>
+          <t>12,518</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -4160,42 +4160,42 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21,12747000</t>
+          <t>21,13673400</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,040</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>10,20</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>12,53</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,539</t>
+          <t>59,563</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4420,42 +4420,42 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>48,29036600</t>
+          <t>48,31361300</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,036</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>10,36</t>
+          <t>10,41</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>12,80</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>41,788</t>
+          <t>41,807</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15,64931400</t>
+          <t>15,65690000</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0,037</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>10,44</t>
+          <t>10,49</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,348</t>
+          <t>28,354</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4941,42 +4941,42 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,29318500</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>-0,018</t>
+          <t>3,29844500</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0,159</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>13,03</t>
+          <t>13,24</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>77,743</t>
+          <t>77,855</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -5205,22 +5205,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,13449000</t>
+          <t>3,13596400</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,035</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>10,10</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,667</t>
+          <t>1,663</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,19770400</t>
+          <t>3,19930200</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>11,56</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -5486,17 +5486,17 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>1.842,987</t>
+          <t>1.845,084</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -5715,42 +5715,42 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,41857700</t>
+          <t>3,41640900</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-0,248</t>
+          <t>-0,063</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,40</t>
+          <t>9,38</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>123,734</t>
+          <t>123,559</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -5979,22 +5979,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>34,35953100</t>
+          <t>34,37664900</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>10,74</t>
+          <t>10,80</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -6004,17 +6004,17 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>2.218,097</t>
+          <t>2.217,975</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -6239,42 +6239,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,46395900</t>
+          <t>3,46568600</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>10,76</t>
+          <t>10,81</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>13,28</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,717</t>
+          <t>12,603</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -6504,42 +6504,42 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3,47217600</t>
+          <t>3,46891400</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>-0,236</t>
+          <t>-0,093</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>8,84</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>11,35</t>
+          <t>11,33</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>63,711</t>
+          <t>63,378</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -6764,22 +6764,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19,97285400</t>
+          <t>19,98257900</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>11,08</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -6789,17 +6789,17 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>972,124</t>
+          <t>972,536</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,02363029</t>
+          <t>1,02447190</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -7049,17 +7049,17 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>22,110</t>
+          <t>22,128</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,30358300</t>
+          <t>1,30420100</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -7282,32 +7282,32 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>11,30</t>
+          <t>11,35</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>13,94</t>
+          <t>13,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,713</t>
+          <t>76,756</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,23171200</t>
+          <t>1,23221100</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -7542,32 +7542,32 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>10,92</t>
+          <t>10,96</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>13,52</t>
+          <t>13,53</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>63,679</t>
+          <t>63,938</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,09251073</t>
+          <t>1,09522626</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -7794,32 +7794,32 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>8,65</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>265,002</t>
+          <t>265,665</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8036,22 +8036,22 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1,33699800</t>
+          <t>1,33768000</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>11,77</t>
+          <t>11,83</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -8061,17 +8061,17 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>495,342</t>
+          <t>496,307</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -8296,42 +8296,42 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,27128300</t>
+          <t>1,27353200</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,133</t>
+          <t>0,176</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>1,20</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>13,11</t>
+          <t>13,31</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>15,54</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,856</t>
+          <t>42,931</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8556,22 +8556,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>5,80540300</t>
+          <t>5,80845000</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>11,62</t>
+          <t>11,68</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>566,777</t>
+          <t>567,073</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -8817,42 +8817,42 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>5,20388900</t>
+          <t>5,20649400</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>11,55</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>14,28</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3.540,706</t>
+          <t>3.537,486</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9077,42 +9077,42 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1,14083365</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>-0,001</t>
+          <t>1,14233617</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>190,271</t>
+          <t>190,522</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,09222700</t>
+          <t>1,09281900</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>11,45</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,124</t>
+          <t>20,077</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9581,42 +9581,42 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>11,13816200</t>
+          <t>11,14377900</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0,040</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>11,42</t>
+          <t>11,48</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>14,14</t>
+          <t>14,15</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>2.448,866</t>
+          <t>2.458,324</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -9841,22 +9841,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1.928,55963700</t>
+          <t>1.929,54327700</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>11,60</t>
+          <t>11,65</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>186,450</t>
+          <t>186,597</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10101,22 +10101,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>5,40727800</t>
+          <t>5,41002200</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>11,53</t>
+          <t>11,58</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -10126,17 +10126,17 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>863,822</t>
+          <t>863,146</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>30,61985900</t>
+          <t>30,63385400</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -10371,32 +10371,32 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>10,41</t>
+          <t>10,46</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>28,41</t>
+          <t>28,40</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,826</t>
+          <t>21,836</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -10609,22 +10609,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>32,15838600</t>
+          <t>32,17436900</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>11,26</t>
+          <t>11,31</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -10634,17 +10634,17 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>3.143,057</t>
+          <t>3.136,992</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -10865,42 +10865,42 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1.855,23037500</t>
+          <t>1.856,29952600</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,025</t>
+          <t>0,057</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>10,14</t>
+          <t>10,20</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>12,47</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>116,664</t>
+          <t>116,736</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -11121,22 +11121,22 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>3,38902700</t>
+          <t>3,39071700</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>11,52</t>
+          <t>11,57</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -11146,17 +11146,17 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>695,512</t>
+          <t>695,137</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -11377,22 +11377,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>6,49577300</t>
+          <t>6,49894400</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>11,05</t>
+          <t>11,11</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -11402,17 +11402,17 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>122,571</t>
+          <t>122,568</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>3,75798300</t>
+          <t>3,75989500</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -11648,12 +11648,12 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>11,74</t>
+          <t>11,79</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -11663,17 +11663,17 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>17.212,667</t>
+          <t>17.240,483</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -11909,22 +11909,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>5,58814800</t>
+          <t>5,59114200</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>11,85</t>
+          <t>11,91</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -11934,17 +11934,17 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1.583,938</t>
+          <t>1.584,985</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -12421,17 +12421,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,07455600</t>
+          <t>1,07508300</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12446,17 +12446,17 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>162,295</t>
+          <t>163,967</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12673,22 +12673,22 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>31,71818300</t>
+          <t>31,73210200</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,040</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>10,27</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -12698,17 +12698,17 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>166,796</t>
+          <t>166,905</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -12937,42 +12937,42 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3,78744400</t>
+          <t>3,78927300</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>11,19</t>
+          <t>11,25</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2.340,463</t>
+          <t>2.338,117</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -13201,42 +13201,42 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2,93660300</t>
+          <t>2,93788200</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>10,13</t>
+          <t>10,18</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>12,51</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>6.147,489</t>
+          <t>6.211,728</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3,35510400</t>
+          <t>3,35679800</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>11,75</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -13486,17 +13486,17 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>15.035,043</t>
+          <t>15.038,629</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -13721,42 +13721,42 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1,35667100</t>
+          <t>1,35733800</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>11,42</t>
+          <t>11,48</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>14,12</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>73,244</t>
+          <t>71,245</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>10,17899700</t>
+          <t>10,18395200</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -13992,12 +13992,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>11,33</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -14007,17 +14007,17 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>824,436</t>
+          <t>824,511</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -14247,42 +14247,42 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4,68189100</t>
+          <t>4,68416300</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>11,34</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>13,95</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>17.171,193</t>
+          <t>17.100,095</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -14511,22 +14511,22 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>5,36859700</t>
+          <t>5,37128500</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>11,64</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>24.066,701</t>
+          <t>24.103,287</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>5,02383600</t>
+          <t>5,02634200</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14791,12 +14791,12 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>11,56</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -14806,17 +14806,17 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>9.815,001</t>
+          <t>9.803,697</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.816,66886900</t>
+          <t>1.817,55265300</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -15055,12 +15055,12 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>11,08</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -15070,17 +15070,17 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>293,478</t>
+          <t>299,743</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -15305,42 +15305,42 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>5,51043014</t>
+          <t>5,50537846</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>-0,238</t>
+          <t>-0,091</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,29</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>9,59</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>30,727</t>
+          <t>30,725</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -15565,27 +15565,27 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>13,15365900</t>
+          <t>13,11698300</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>-0,596</t>
+          <t>-0,278</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>-0,60</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>10,80</t>
+          <t>10,50</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>15,20</t>
+          <t>14,64</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -15595,12 +15595,12 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -15829,42 +15829,42 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.694,49372700</t>
+          <t>1.693,49636800</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>-0,099</t>
+          <t>-0,058</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,50</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>10,26</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>110,672</t>
+          <t>110,436</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -16085,42 +16085,42 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2.449,64958400</t>
+          <t>2.433,79423600</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>-0,144</t>
+          <t>-0,647</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>-3,08</t>
+          <t>-3,71</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>18,48</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>20,45</t>
+          <t>19,65</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>14,325</t>
+          <t>14,242</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1,04049300</t>
+          <t>1,03794200</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -16366,17 +16366,17 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>3,011</t>
+          <t>2,794</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,28941100</t>
+          <t>1,28674900</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -16603,32 +16603,32 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>8,62</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,853</t>
+          <t>4,843</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -16849,42 +16849,42 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1,04139200</t>
+          <t>1,02081400</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>-4,529</t>
+          <t>-1,976</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>-12,23</t>
+          <t>-13,96</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-10,18</t>
+          <t>-11,95</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-3,77</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>3,398</t>
+          <t>3,331</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>0,98659200</t>
+          <t>0,98258700</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -17115,7 +17115,7 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -17130,17 +17130,17 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>1,626</t>
+          <t>1,619</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1,37186800</t>
+          <t>1,36169000</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -17367,32 +17367,32 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>-5,16</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>0,49</t>
+          <t>-5,87</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>9,831</t>
+          <t>9,758</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1,06473700</t>
+          <t>1,06403800</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -17638,17 +17638,17 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>12,667</t>
+          <t>12,658</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -17865,42 +17865,42 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1,13459000</t>
+          <t>1,14395400</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>0,371</t>
+          <t>0,825</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-5,89</t>
+          <t>-5,12</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>2,808</t>
+          <t>2,837</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1,48648800</t>
+          <t>1,48641700</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -18141,22 +18141,22 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>13,72</t>
+          <t>13,66</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>68,306</t>
+          <t>68,303</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -18373,7 +18373,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1.296,21739100</t>
+          <t>1.301,07582500</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -18383,32 +18383,32 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>3,30</t>
+          <t>3,68</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>38,626</t>
+          <t>38,772</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -18643,42 +18643,42 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>4,34531000</t>
+          <t>4,32478500</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>-0,520</t>
+          <t>-0,472</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-3,11</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>-2,20</t>
+          <t>-2,66</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>472,660</t>
+          <t>469,644</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>2,91815000</t>
+          <t>2,91833800</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -18913,32 +18913,32 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>66,999</t>
+          <t>67,002</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -19159,42 +19159,42 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1.739,55484600</t>
+          <t>1.746,06951300</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0,250</t>
+          <t>0,374</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,20</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>10,41</t>
+          <t>10,82</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>12,66</t>
+          <t>13,14</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>30,759</t>
+          <t>30,879</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -19419,42 +19419,42 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>4,04246800</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>0,325</t>
+          <t>4,02986700</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>-0,311</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,30</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>20,17</t>
+          <t>19,79</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>22,15</t>
+          <t>21,80</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>2.460,366</t>
+          <t>2.453,242</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -19679,42 +19679,42 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,99101400</t>
+          <t>1,99256700</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,078</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>9,52</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>11,72</t>
+          <t>11,80</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>20,351</t>
+          <t>20,366</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -19939,42 +19939,42 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1.723,35760500</t>
+          <t>1.722,40547300</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>-0,095</t>
+          <t>-0,055</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>8,97</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>11,34</t>
+          <t>11,28</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>14,864</t>
+          <t>14,855</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -20195,42 +20195,42 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>3,82110600</t>
+          <t>3,82414400</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>0,079</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>12,13</t>
+          <t>12,21</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>699,068</t>
+          <t>697,815</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0,59910746</t>
+          <t>0,60802063</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -20461,32 +20461,32 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-2,10</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-17,03</t>
+          <t>-15,79</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>-35,18</t>
+          <t>-32,95</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>20,428</t>
+          <t>20,735</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -20718,42 +20718,42 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,83174800</t>
+          <t>5,82729100</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>-0,141</t>
+          <t>-0,076</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>11,93</t>
+          <t>11,81</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>873,918</t>
+          <t>873,125</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -20978,42 +20978,42 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>1,55313800</t>
+          <t>1,55393500</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>64,033</t>
+          <t>64,066</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -21246,42 +21246,42 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1,58704800</t>
+          <t>1,58606700</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>-0,125</t>
+          <t>-0,061</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-1,90</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>14,951</t>
+          <t>14,942</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -21512,42 +21512,42 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>3,47760800</t>
+          <t>3,47993800</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>0,430</t>
+          <t>0,067</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>9,22</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>10,01</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>165,633</t>
+          <t>165,744</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -21778,42 +21778,42 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,42649800</t>
+          <t>1,42721000</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>8,78</t>
+          <t>8,99</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>51,288</t>
+          <t>51,313</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1,32733800</t>
+          <t>1,32837500</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -22052,32 +22052,32 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>-4,23</t>
+          <t>-4,16</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>3,49</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>11,537</t>
+          <t>11,546</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1,44315900</t>
+          <t>1,44199200</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -22312,32 +22312,32 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>285,260</t>
+          <t>285,030</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>7,02807500</t>
+          <t>7,02723800</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -22573,32 +22573,32 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>13,28</t>
+          <t>13,17</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>125,200</t>
+          <t>125,178</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -22819,7 +22819,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1,87522400</t>
+          <t>1,88068000</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -22827,34 +22827,34 @@
           <t>-0,002</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>-0,16</t>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,46</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>7,73</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>165,962</t>
+          <t>166,416</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -23075,42 +23075,42 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>4,05820300</t>
+          <t>4,08842200</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>0,223</t>
+          <t>0,744</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,70</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>90,909</t>
+          <t>91,467</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -23335,42 +23335,42 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,31531500</t>
+          <t>1,31004400</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>-1,962</t>
+          <t>-0,400</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>8,69</t>
+          <t>8,25</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>16,17</t>
+          <t>16,30</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>4,358</t>
+          <t>4,342</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -23591,42 +23591,42 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2,54015900</t>
+          <t>2,51390100</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>-2,602</t>
+          <t>-1,033</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>-8,03</t>
+          <t>-8,98</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>15,15</t>
+          <t>13,06</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>11,997</t>
+          <t>11,836</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -23851,42 +23851,42 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1.747,04723400</t>
+          <t>1.696,02701500</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>-6,289</t>
+          <t>-2,920</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>-14,37</t>
+          <t>-16,87</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>-11,99</t>
+          <t>-14,56</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-6,69</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>8,453</t>
+          <t>8,199</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -24100,42 +24100,42 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>11,00280000</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>0,543</t>
+          <t>10,85350200</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>-1,356</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>280,347</t>
+          <t>275,496</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -24360,42 +24360,42 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1,12175600</t>
+          <t>1,08891300</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>-5,161</t>
+          <t>-2,927</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>-21,41</t>
+          <t>-23,71</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>-26,41</t>
+          <t>-28,57</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>-23,87</t>
+          <t>-26,32</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>307,514</t>
+          <t>298,445</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -24620,42 +24620,42 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>0,95123400</t>
+          <t>0,92063200</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-3,230</t>
+          <t>-3,217</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>-13,76</t>
+          <t>-16,53</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-18,27</t>
+          <t>-20,90</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>-13,34</t>
+          <t>-16,28</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>46,091</t>
+          <t>44,605</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -24880,42 +24880,42 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,57940300</t>
+          <t>1,55194200</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>-3,296</t>
+          <t>-1,738</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>-12,46</t>
+          <t>-13,98</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-7,34</t>
+          <t>-8,95</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-3,50</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>1,341</t>
+          <t>1,317</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -25140,42 +25140,42 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>5,87120100</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>-1,004</t>
+          <t>5,87377000</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>9,19</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>86,44</t>
+          <t>86,52</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>94,52</t>
+          <t>94,97</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>94,397</t>
+          <t>94,410</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -25400,42 +25400,42 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>8,47290400</t>
+          <t>8,38460900</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>-2,615</t>
+          <t>-1,042</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>-8,11</t>
+          <t>-9,07</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>13,94</t>
+          <t>11,86</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>84,575</t>
+          <t>83,900</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -25660,42 +25660,42 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1,21787600</t>
+          <t>1,17538300</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>-0,046</t>
+          <t>-0,049</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>-9,55</t>
+          <t>-12,70</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-5,37</t>
+          <t>-8,67</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-4,05</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>270,622</t>
+          <t>258,180</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -25920,42 +25920,42 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1,34845400</t>
+          <t>1,27829800</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>-6,478</t>
+          <t>-5,202</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>-23,20</t>
+          <t>-27,20</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>-29,08</t>
+          <t>-32,77</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>-23,49</t>
+          <t>-28,37</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>76,300</t>
+          <t>72,345</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -26180,42 +26180,42 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>2,88775300</t>
+          <t>2,84345000</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>-2,328</t>
+          <t>-1,534</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>-5,00</t>
+          <t>-6,45</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>4,32</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>10,82</t>
+          <t>9,17</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>118,526</t>
+          <t>116,707</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -26440,42 +26440,42 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>1,68941100</t>
+          <t>1,64003200</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>-6,287</t>
+          <t>-2,922</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>-14,44</t>
+          <t>-16,94</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>-12,80</t>
+          <t>-15,35</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-7,75</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>45,478</t>
+          <t>44,112</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -26704,42 +26704,42 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>8,33181300</t>
+          <t>8,28391300</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>-0,516</t>
+          <t>-0,574</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>6,60</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>77,63</t>
+          <t>76,61</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>87,70</t>
+          <t>86,44</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>144,397</t>
+          <t>143,674</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -26964,42 +26964,42 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.063,14080500</t>
+          <t>1.042,34388100</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>-3,332</t>
+          <t>-1,956</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>-27,13</t>
+          <t>-28,55</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>-22,22</t>
+          <t>-23,74</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>-18,44</t>
+          <t>-21,01</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>34,790</t>
+          <t>34,395</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -27224,42 +27224,42 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>29,59223300</t>
+          <t>28,95095500</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>-2,570</t>
+          <t>-2,167</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>-12,28</t>
+          <t>-14,18</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-14,34</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="inlineStr">
-        <is>
-          <t>3,64</t>
+          <t>-16,19</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>509,853</t>
+          <t>498,765</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -27484,42 +27484,42 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>3,27759800</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>-1,524</t>
+          <t>3,31445700</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>1,124</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>6,90</t>
+          <t>8,10</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>35,30</t>
+          <t>36,82</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>52,93</t>
+          <t>55,17</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>532,063</t>
+          <t>538,065</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -27748,42 +27748,42 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>4,21105800</t>
+          <t>4,15706500</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>-2,846</t>
+          <t>-1,282</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>-16,34</t>
+          <t>-17,41</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-6,16</t>
+          <t>-7,36</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>2,40</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>19,047</t>
+          <t>18,786</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -28008,42 +28008,42 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>1.444,35544400</t>
+          <t>1.413,52257200</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>-4,693</t>
+          <t>-2,134</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>-14,75</t>
+          <t>-16,57</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>7,21</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>28,742</t>
+          <t>28,153</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -28268,42 +28268,42 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>1,80899600</t>
+          <t>1,78066400</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>-3,548</t>
+          <t>-1,566</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>-8,54</t>
+          <t>-9,97</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-11,08</t>
+          <t>-12,47</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>-4,12</t>
+          <t>-6,00</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>1,601</t>
+          <t>1,583</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -28520,42 +28520,42 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>5,79269300</t>
+          <t>5,73362200</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>-2,671</t>
+          <t>-1,019</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>-7,87</t>
+          <t>-8,81</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>6,58</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>15,34</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>40,728</t>
+          <t>40,313</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -28772,42 +28772,42 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>2,04992200</t>
+          <t>2,00980300</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>-3,680</t>
+          <t>-1,957</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>-11,89</t>
+          <t>-13,62</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-4,21</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>30,032</t>
+          <t>29,508</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -29032,42 +29032,42 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>54,47875800</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>-1,002</t>
+          <t>54,50256800</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>0,043</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>9,20</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>86,60</t>
+          <t>86,68</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>94,71</t>
+          <t>95,16</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>991,950</t>
+          <t>990,744</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -29412,42 +29412,42 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1,61970100</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>-1,526</t>
+          <t>1,63791500</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>1,124</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>35,26</t>
+          <t>36,78</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>52,86</t>
+          <t>55,10</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>20,892</t>
+          <t>21,124</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -29672,42 +29672,42 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>1,63304500</t>
+          <t>1,61451400</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>-5,194</t>
+          <t>-1,134</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>-12,83</t>
+          <t>-13,82</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>-5,00</t>
+          <t>-6,07</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>14,40</t>
+          <t>11,73</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>220,174</t>
+          <t>217,507</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -29936,42 +29936,42 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>0,80618800</t>
+          <t>0,79142200</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>-3,400</t>
+          <t>-1,831</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>-11,63</t>
+          <t>-13,24</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>-16,24</t>
+          <t>-17,78</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>-13,37</t>
+          <t>-14,29</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2,477</t>
+          <t>2,431</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -30192,42 +30192,42 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>6,56831900</t>
+          <t>6,48922600</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>-2,690</t>
+          <t>-1,204</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>-7,31</t>
+          <t>-8,43</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>11,66</t>
+          <t>9,62</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>316,323</t>
+          <t>312,535</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -30452,7 +30452,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>994,64983000</t>
+          <t>974,06803500</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
@@ -30462,32 +30462,32 @@
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>-6,42</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>1,45</t>
+          <t>-8,35</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>7,735</t>
+          <t>7,575</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1.464,44264700</t>
+          <t>1.423,88457500</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -30722,32 +30722,32 @@
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>-7,18</t>
+          <t>-9,75</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>-2,09</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>3,40</t>
+          <t>-4,80</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>20,663</t>
+          <t>20,091</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -30968,42 +30968,42 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>166,87241446</t>
+          <t>165,13588551</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>-2,611</t>
+          <t>-1,040</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>-8,04</t>
+          <t>-8,99</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>15,64</t>
+          <t>13,52</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>16,688</t>
+          <t>16,515</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -31228,42 +31228,42 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>1,66733600</t>
+          <t>1,64847100</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>-5,165</t>
+          <t>-1,131</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>-12,78</t>
+          <t>-13,77</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>-5,03</t>
+          <t>-6,11</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>14,55</t>
+          <t>11,89</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>4,965</t>
+          <t>4,909</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -31485,42 +31485,42 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>1,62789100</t>
+          <t>1,60936400</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>-5,195</t>
+          <t>-1,138</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>-12,83</t>
+          <t>-13,82</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>-4,90</t>
+          <t>-5,98</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>14,59</t>
+          <t>11,91</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>1.447,131</t>
+          <t>1.430,424</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -31738,42 +31738,42 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>60,74176400</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>-1,001</t>
+          <t>60,76969200</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>9,33</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>87,54</t>
+          <t>87,63</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>95,86</t>
+          <t>96,32</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>819,739</t>
+          <t>819,782</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -31982,42 +31982,42 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>32,84952800</t>
+          <t>32,13632300</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>-2,574</t>
+          <t>-2,171</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>-12,27</t>
+          <t>-14,18</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>-13,99</t>
+          <t>-15,86</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>0,10</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>571,394</t>
+          <t>558,913</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -32226,42 +32226,42 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>14,99003200</t>
+          <t>14,56872000</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>-6,056</t>
+          <t>-2,810</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>-13,97</t>
+          <t>-16,39</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>-11,12</t>
+          <t>-13,62</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>-2,03</t>
+          <t>-5,15</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>98,666</t>
+          <t>95,837</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -32479,42 +32479,42 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>27,49985800</t>
+          <t>26,90701100</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>-2,559</t>
+          <t>-2,155</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>-12,25</t>
+          <t>-14,14</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>-14,29</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>3,62</t>
+          <t>-16,14</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>-0,40</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>9,306</t>
+          <t>9,105</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -32728,42 +32728,42 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>53,56947200</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>-1,005</t>
+          <t>53,59305500</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>9,20</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>86,84</t>
+          <t>86,93</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>95,00</t>
+          <t>95,46</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>724,411</t>
+          <t>723,978</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -32977,42 +32977,42 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>28,22925200</t>
+          <t>27,61620900</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>-2,574</t>
+          <t>-2,171</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>-12,30</t>
+          <t>-14,20</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>-14,33</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>3,68</t>
+          <t>-16,19</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>345,342</t>
+          <t>337,821</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -33221,42 +33221,42 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>57,01544100</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>-1,002</t>
+          <t>57,04105600</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>87,23</t>
+          <t>87,31</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>95,43</t>
+          <t>95,89</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>810,982</t>
+          <t>810,732</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -33469,7 +33469,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1,17793200</t>
+          <t>1,17845700</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -33479,12 +33479,12 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>10,14</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
@@ -33494,17 +33494,17 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>66,471</t>
+          <t>66,487</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -33730,7 +33730,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>1,42179700</t>
+          <t>1,42243200</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -33740,12 +33740,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>10,16</t>
+          <t>10,21</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -33755,17 +33755,17 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>202,471</t>
+          <t>220,540</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -33995,22 +33995,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>3,38336900</t>
+          <t>3,38498300</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>11,01</t>
+          <t>11,07</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -34020,17 +34020,17 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>24,126</t>
+          <t>24,145</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -34257,22 +34257,22 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>6,18363400</t>
+          <t>6,18659800</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,038</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>10,90</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -34282,17 +34282,17 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>43,444</t>
+          <t>43,529</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -34517,42 +34517,42 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>5,39182500</t>
+          <t>5,39440000</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>11,30</t>
+          <t>11,35</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>13,97</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>849,279</t>
+          <t>849,684</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -34774,42 +34774,42 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>24,96515300</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>-0,015</t>
+          <t>25,00571700</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>0,162</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>11,50</t>
+          <t>11,68</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>13,82</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>96,311</t>
+          <t>96,464</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -35038,22 +35038,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>3,44248500</t>
+          <t>3,44413300</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>11,17</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -35063,17 +35063,17 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>8.039,576</t>
+          <t>8.030,605</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -35299,22 +35299,22 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1.991,05056600</t>
+          <t>1.992,10413000</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,045</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>11,85</t>
+          <t>11,91</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -35324,17 +35324,17 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>16.555,604</t>
+          <t>16.611,161</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -35559,22 +35559,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>5,13655200</t>
+          <t>5,13916300</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>0,036</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>11,40</t>
+          <t>11,46</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -35584,17 +35584,17 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>3.084,192</t>
+          <t>3.044,682</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -35819,42 +35819,42 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>1,63180737</t>
+          <t>1,63255421</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>11,47</t>
+          <t>11,52</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>14,18</t>
+          <t>14,17</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>341,192</t>
+          <t>341,349</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -36063,42 +36063,42 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>5,39922100</t>
+          <t>5,40185800</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>11,52</t>
+          <t>11,58</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>14,25</t>
+          <t>14,24</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>299,345</t>
+          <t>299,491</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -36320,22 +36320,22 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>18,87138000</t>
+          <t>18,88122600</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>0,039</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>11,46</t>
+          <t>11,52</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -36345,17 +36345,17 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>4.726,559</t>
+          <t>4.719,024</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -36564,22 +36564,22 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>9,17280700</t>
+          <t>9,17763500</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,040</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>11,44</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -36589,17 +36589,17 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2.385,674</t>
+          <t>2.387,376</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -36842,12 +36842,12 @@
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -37068,22 +37068,22 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,96083600</t>
+          <t>2,96214900</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>0,043</t>
+          <t>0,044</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>10,31</t>
+          <t>10,36</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -37093,17 +37093,17 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>14.250,031</t>
+          <t>14.332,592</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -37329,42 +37329,42 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>4,66574300</t>
+          <t>4,66805400</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>11,53</t>
+          <t>11,58</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>14,25</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>17.980,563</t>
+          <t>18.158,500</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -37597,7 +37597,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1,44992600</t>
+          <t>1,45066100</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -37607,12 +37607,12 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>11,77</t>
+          <t>11,82</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -37622,17 +37622,17 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>4.259,024</t>
+          <t>4.248,466</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>1.867,55626100</t>
+          <t>1.868,49365900</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -37863,32 +37863,32 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>11,50</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>14,15</t>
+          <t>14,14</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>1.476,319</t>
+          <t>1.479,850</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -38113,7 +38113,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1,36477100</t>
+          <t>1,36532500</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -38123,12 +38123,12 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>9,30</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -38138,17 +38138,17 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>31.416,579</t>
+          <t>31.216,204</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -38372,7 +38372,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>9,84341300</t>
+          <t>9,84771800</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -38382,32 +38382,32 @@
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>9,97</t>
+          <t>10,01</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>12,31</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>2.665,404</t>
+          <t>2.741,079</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -38631,7 +38631,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>2,59224300</t>
+          <t>2,59336000</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -38641,12 +38641,12 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>10,01</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
@@ -38656,17 +38656,17 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>16.896,048</t>
+          <t>16.843,261</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -38892,22 +38892,22 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>4,70817800</t>
+          <t>4,71079500</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>10,96</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
@@ -38917,17 +38917,17 @@
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>11.858,011</t>
+          <t>11.599,416</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -39159,42 +39159,42 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>3,75924300</t>
+          <t>3,75700100</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>-0,241</t>
+          <t>-0,059</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>7,62</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>9,91</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>1.655,729</t>
+          <t>1.654,699</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -39426,42 +39426,42 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>2,50260800</t>
+          <t>2,50427800</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>0,003</t>
+          <t>0,066</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>8,73</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>10,80</t>
+          <t>10,90</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>3.103,611</t>
+          <t>3.106,960</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -39691,42 +39691,42 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>3,13427300</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="inlineStr">
-        <is>
-          <t>-0,015</t>
+          <t>3,13933300</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>0,161</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>0,40</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,32</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>13,51</t>
+          <t>13,73</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>38,014</t>
+          <t>38,076</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -39947,42 +39947,42 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>1.708,66431600</t>
+          <t>1.709,94171500</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,028</t>
+          <t>0,074</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>8,87</t>
+          <t>8,95</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>11,31</t>
+          <t>11,41</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>427,731</t>
+          <t>428,051</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -40207,42 +40207,42 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>4,00305900</t>
+          <t>4,00899600</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>0,009</t>
+          <t>0,148</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>11,20</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>13,58</t>
+          <t>13,73</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>3.158,786</t>
+          <t>3.163,347</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -40469,22 +40469,22 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>5,37139800</t>
+          <t>5,36628300</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>-0,228</t>
+          <t>-0,095</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>-0,60</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>9,24</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -40494,17 +40494,17 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>2.377,768</t>
+          <t>2.376,073</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -40725,42 +40725,42 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>5,45124700</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
-          <t>-0,006</t>
+          <t>5,45983600</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>0,157</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>11,66</t>
+          <t>11,84</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>14,00</t>
+          <t>14,21</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>6.162,954</t>
+          <t>6.055,496</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -40981,12 +40981,12 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>4,96713100</t>
+          <t>4,96683500</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>-0,077</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
@@ -41001,22 +41001,22 @@
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>12,60</t>
+          <t>12,59</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>487,774</t>
+          <t>487,655</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -41243,22 +41243,22 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>8,36157400</t>
+          <t>8,36587900</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>0,036</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>11,34</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
@@ -41268,17 +41268,17 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>166,253</t>
+          <t>165,834</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -41363,42 +41363,42 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,57515600</t>
+          <t>3,56513400</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>-0,350</t>
+          <t>-0,280</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>775,371</t>
+          <t>773,197</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -41619,42 +41619,42 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>3,87851200</t>
+          <t>3,87500200</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>-0,324</t>
+          <t>-0,090</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>6,55</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>8,76</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>634,728</t>
+          <t>634,154</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -41886,22 +41886,22 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>2,74771000</t>
+          <t>2,74915500</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>11,57</t>
+          <t>11,63</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -41911,17 +41911,17 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>8.457,519</t>
+          <t>8.418,776</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
@@ -42150,22 +42150,22 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>7,54956200</t>
+          <t>7,55339600</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>0,036</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>11,35</t>
+          <t>11,41</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
@@ -42175,17 +42175,17 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>11.672,528</t>
+          <t>11.624,135</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -42414,7 +42414,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>7,89044500</t>
+          <t>7,89438200</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -42424,32 +42424,32 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>11,43</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>14,06</t>
+          <t>14,05</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>3.664,080</t>
+          <t>3.723,702</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
@@ -42674,42 +42674,42 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>1,50310700</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>-0,051</t>
+          <t>1,50442800</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>0,087</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>7,80</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>10,01</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>161,710</t>
+          <t>161,901</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -42930,22 +42930,22 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>3,29744800</t>
+          <t>3,29898500</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>0,90</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>10,76</t>
+          <t>10,81</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -42955,17 +42955,17 @@
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.113,947</t>
+          <t>1.503,823</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
@@ -43218,12 +43218,12 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -43474,12 +43474,12 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -43730,12 +43730,12 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -43986,12 +43986,12 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
@@ -44242,12 +44242,12 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -44498,12 +44498,12 @@
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -44724,22 +44724,22 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>7,08571500</t>
+          <t>7,08927800</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>11,70</t>
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr">
@@ -44749,17 +44749,17 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>21.827,559</t>
+          <t>21.538,852</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -44844,42 +44844,42 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>5,75585500</t>
+          <t>5,75059000</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>-0,233</t>
+          <t>-0,091</t>
         </is>
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>9,50</t>
+          <t>9,40</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>12,04</t>
+          <t>12,02</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>591,145</t>
+          <t>590,604</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -45135,12 +45135,12 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -45357,42 +45357,42 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>3,83449800</t>
+          <t>3,79450900</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>-2,626</t>
+          <t>-1,042</t>
         </is>
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>-8,06</t>
+          <t>-9,02</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>5,90</t>
+          <t>4,80</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>15,64</t>
+          <t>13,52</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>280,237</t>
+          <t>277,481</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
@@ -45613,42 +45613,42 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>3,51944600</t>
+          <t>3,48570600</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>-2,715</t>
+          <t>-0,958</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>-8,00</t>
+          <t>-8,88</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>15,19</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>7,336</t>
+          <t>7,265</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -45873,42 +45873,42 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>12,37569290</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>0,548</t>
+          <t>12,20747676</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>-1,359</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>11,82</t>
+          <t>10,30</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>12,72</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>2.460,067</t>
+          <t>2.425,642</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -46133,42 +46133,42 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>1,89496100</t>
+          <t>1,86561300</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>-3,078</t>
+          <t>-1,548</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>-10,99</t>
+          <t>-12,37</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>184,585</t>
+          <t>181,726</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -46389,42 +46389,42 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>1,80662700</t>
+          <t>1,75362600</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>-6,309</t>
+          <t>-2,933</t>
         </is>
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>-14,51</t>
+          <t>-17,02</t>
         </is>
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>-12,86</t>
+          <t>-15,41</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>-4,54</t>
+          <t>-7,81</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>619,652</t>
+          <t>595,901</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
@@ -46649,42 +46649,42 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>3,22977589</t>
+          <t>3,19813999</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr">
         <is>
-          <t>-2,513</t>
+          <t>-0,979</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>-11,36</t>
+          <t>-12,23</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>1.205,290</t>
+          <t>1.193,484</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">
@@ -46901,42 +46901,42 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>2,31724717</t>
+          <t>2,29173791</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>-2,504</t>
+          <t>-1,100</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>-12,29</t>
+          <t>-13,26</t>
         </is>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>-1,95</t>
+          <t>-3,03</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>701,354</t>
+          <t>693,633</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L183" s="4" t="inlineStr">
@@ -47153,22 +47153,22 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>3,93783300</t>
+          <t>3,94009800</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>0,044</t>
+          <t>0,057</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>10,90</t>
+          <t>10,96</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
@@ -47178,17 +47178,17 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>4.547,004</t>
+          <t>4.494,282</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
